--- a/預測結果與評估指標_kfold_mask幾何.xlsx
+++ b/預測結果與評估指標_kfold_mask幾何.xlsx
@@ -303,18 +303,18 @@
   <dimension ref="A1:L55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="46.7109375" customWidth="true"/>
-    <col min="2" max="2" width="13.140625" customWidth="true"/>
-    <col min="3" max="3" width="13.42578125" customWidth="true"/>
-    <col min="4" max="4" width="14.7109375" customWidth="true"/>
-    <col min="5" max="5" width="14.7109375" customWidth="true"/>
-    <col min="6" max="6" width="13.7109375" customWidth="true"/>
-    <col min="7" max="7" width="14.7109375" customWidth="true"/>
-    <col min="8" max="8" width="17" customWidth="true"/>
-    <col min="9" max="9" width="20.5703125" customWidth="true"/>
-    <col min="10" max="10" width="21.5703125" customWidth="true"/>
-    <col min="11" max="11" width="10.28515625" customWidth="true"/>
-    <col min="12" max="12" width="5.7109375" customWidth="true"/>
+    <col min="1" max="1" width="44.6640625" customWidth="true"/>
+    <col min="2" max="2" width="12.33203125" customWidth="true"/>
+    <col min="3" max="3" width="11.88671875" customWidth="true"/>
+    <col min="4" max="4" width="13.109375" customWidth="true"/>
+    <col min="5" max="5" width="13.109375" customWidth="true"/>
+    <col min="6" max="6" width="13.21875" customWidth="true"/>
+    <col min="7" max="7" width="13.109375" customWidth="true"/>
+    <col min="8" max="8" width="15.109375" customWidth="true"/>
+    <col min="9" max="9" width="18.44140625" customWidth="true"/>
+    <col min="10" max="10" width="19.109375" customWidth="true"/>
+    <col min="11" max="11" width="9" customWidth="true"/>
+    <col min="12" max="12" width="5" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -369,22 +369,22 @@
         <v>23</v>
       </c>
       <c r="E2" s="0">
-        <v>21.999107328228071</v>
+        <v>21.999107328227829</v>
       </c>
       <c r="F2" s="0">
-        <v>-1.0008926717719291</v>
+        <v>-1.0008926717721707</v>
       </c>
       <c r="G2" s="0">
-        <v>1.0008926717719291</v>
+        <v>1.0008926717721707</v>
       </c>
       <c r="H2" s="0">
-        <v>21.499107328228071</v>
+        <v>21.499107328227829</v>
       </c>
       <c r="I2" s="0">
-        <v>-1.5008926717719291</v>
+        <v>-1.5008926717721707</v>
       </c>
       <c r="J2" s="0">
-        <v>1.5008926717719291</v>
+        <v>1.5008926717721707</v>
       </c>
       <c r="K2" s="0" t="b">
         <v>0</v>
@@ -407,22 +407,22 @@
         <v>21</v>
       </c>
       <c r="E3" s="0">
-        <v>19.77698155189352</v>
+        <v>19.776981551893531</v>
       </c>
       <c r="F3" s="0">
-        <v>-1.2230184481064796</v>
+        <v>-1.223018448106469</v>
       </c>
       <c r="G3" s="0">
-        <v>1.2230184481064796</v>
+        <v>1.223018448106469</v>
       </c>
       <c r="H3" s="0">
-        <v>19.27698155189352</v>
+        <v>19.276981551893531</v>
       </c>
       <c r="I3" s="0">
-        <v>-1.7230184481064796</v>
+        <v>-1.723018448106469</v>
       </c>
       <c r="J3" s="0">
-        <v>1.7230184481064796</v>
+        <v>1.723018448106469</v>
       </c>
       <c r="K3" s="0" t="b">
         <v>0</v>
@@ -445,22 +445,22 @@
         <v>23.5</v>
       </c>
       <c r="E4" s="0">
-        <v>21.363793534425309</v>
+        <v>21.363793534425252</v>
       </c>
       <c r="F4" s="0">
-        <v>-2.1362064655746913</v>
+        <v>-2.1362064655747481</v>
       </c>
       <c r="G4" s="0">
-        <v>2.1362064655746913</v>
+        <v>2.1362064655747481</v>
       </c>
       <c r="H4" s="0">
-        <v>20.863793534425309</v>
+        <v>20.863793534425252</v>
       </c>
       <c r="I4" s="0">
-        <v>-2.6362064655746913</v>
+        <v>-2.6362064655747481</v>
       </c>
       <c r="J4" s="0">
-        <v>2.6362064655746913</v>
+        <v>2.6362064655747481</v>
       </c>
       <c r="K4" s="0" t="b">
         <v>0</v>
@@ -483,22 +483,22 @@
         <v>21</v>
       </c>
       <c r="E5" s="0">
-        <v>20.186188863331619</v>
+        <v>20.186188863331534</v>
       </c>
       <c r="F5" s="0">
-        <v>-0.8138111366683809</v>
+        <v>-0.81381113666846616</v>
       </c>
       <c r="G5" s="0">
-        <v>0.8138111366683809</v>
+        <v>0.81381113666846616</v>
       </c>
       <c r="H5" s="0">
-        <v>19.686188863331619</v>
+        <v>19.686188863331534</v>
       </c>
       <c r="I5" s="0">
-        <v>-1.3138111366683809</v>
+        <v>-1.3138111366684662</v>
       </c>
       <c r="J5" s="0">
-        <v>1.3138111366683809</v>
+        <v>1.3138111366684662</v>
       </c>
       <c r="K5" s="0" t="b">
         <v>0</v>
@@ -521,22 +521,22 @@
         <v>21.5</v>
       </c>
       <c r="E6" s="0">
-        <v>20.931050102647813</v>
+        <v>20.931050102647845</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.56894989735218715</v>
+        <v>-0.56894989735215518</v>
       </c>
       <c r="G6" s="0">
-        <v>0.56894989735218715</v>
+        <v>0.56894989735215518</v>
       </c>
       <c r="H6" s="0">
-        <v>20.431050102647813</v>
+        <v>20.431050102647845</v>
       </c>
       <c r="I6" s="0">
-        <v>-1.0689498973521872</v>
+        <v>-1.0689498973521552</v>
       </c>
       <c r="J6" s="0">
-        <v>1.0689498973521872</v>
+        <v>1.0689498973521552</v>
       </c>
       <c r="K6" s="0" t="b">
         <v>0</v>
@@ -559,22 +559,22 @@
         <v>22</v>
       </c>
       <c r="E7" s="0">
-        <v>23.081272631069076</v>
+        <v>23.081272631069048</v>
       </c>
       <c r="F7" s="0">
-        <v>1.0812726310690763</v>
+        <v>1.0812726310690479</v>
       </c>
       <c r="G7" s="0">
-        <v>1.0812726310690763</v>
+        <v>1.0812726310690479</v>
       </c>
       <c r="H7" s="0">
-        <v>22.581272631069076</v>
+        <v>22.581272631069048</v>
       </c>
       <c r="I7" s="0">
-        <v>0.58127263106907634</v>
+        <v>0.58127263106904792</v>
       </c>
       <c r="J7" s="0">
-        <v>0.58127263106907634</v>
+        <v>0.58127263106904792</v>
       </c>
       <c r="K7" s="0" t="b">
         <v>1</v>
@@ -597,22 +597,22 @@
         <v>25</v>
       </c>
       <c r="E8" s="0">
-        <v>21.94096205372368</v>
+        <v>21.940962053723673</v>
       </c>
       <c r="F8" s="0">
-        <v>-3.0590379462763195</v>
+        <v>-3.0590379462763266</v>
       </c>
       <c r="G8" s="0">
-        <v>3.0590379462763195</v>
+        <v>3.0590379462763266</v>
       </c>
       <c r="H8" s="0">
-        <v>21.44096205372368</v>
+        <v>21.440962053723673</v>
       </c>
       <c r="I8" s="0">
-        <v>-3.5590379462763195</v>
+        <v>-3.5590379462763266</v>
       </c>
       <c r="J8" s="0">
-        <v>3.5590379462763195</v>
+        <v>3.5590379462763266</v>
       </c>
       <c r="K8" s="0" t="b">
         <v>0</v>
@@ -635,22 +635,22 @@
         <v>20.5</v>
       </c>
       <c r="E9" s="0">
-        <v>22.999148083125572</v>
+        <v>22.99914808312565</v>
       </c>
       <c r="F9" s="0">
-        <v>2.4991480831255721</v>
+        <v>2.4991480831256503</v>
       </c>
       <c r="G9" s="0">
-        <v>2.4991480831255721</v>
+        <v>2.4991480831256503</v>
       </c>
       <c r="H9" s="0">
-        <v>22.499148083125572</v>
+        <v>22.49914808312565</v>
       </c>
       <c r="I9" s="0">
-        <v>1.9991480831255721</v>
+        <v>1.9991480831256503</v>
       </c>
       <c r="J9" s="0">
-        <v>1.9991480831255721</v>
+        <v>1.9991480831256503</v>
       </c>
       <c r="K9" s="0" t="b">
         <v>1</v>
@@ -673,22 +673,22 @@
         <v>21</v>
       </c>
       <c r="E10" s="0">
-        <v>19.938530598075275</v>
+        <v>19.938530598075321</v>
       </c>
       <c r="F10" s="0">
-        <v>-1.0614694019247253</v>
+        <v>-1.0614694019246791</v>
       </c>
       <c r="G10" s="0">
-        <v>1.0614694019247253</v>
+        <v>1.0614694019246791</v>
       </c>
       <c r="H10" s="0">
-        <v>19.438530598075275</v>
+        <v>19.438530598075321</v>
       </c>
       <c r="I10" s="0">
-        <v>-1.5614694019247253</v>
+        <v>-1.5614694019246791</v>
       </c>
       <c r="J10" s="0">
-        <v>1.5614694019247253</v>
+        <v>1.5614694019246791</v>
       </c>
       <c r="K10" s="0" t="b">
         <v>0</v>
@@ -711,22 +711,22 @@
         <v>18</v>
       </c>
       <c r="E11" s="0">
-        <v>21.139223361952556</v>
+        <v>21.139223361952549</v>
       </c>
       <c r="F11" s="0">
-        <v>3.1392233619525562</v>
+        <v>3.1392233619525491</v>
       </c>
       <c r="G11" s="0">
-        <v>3.1392233619525562</v>
+        <v>3.1392233619525491</v>
       </c>
       <c r="H11" s="0">
-        <v>20.639223361952556</v>
+        <v>20.639223361952549</v>
       </c>
       <c r="I11" s="0">
-        <v>2.6392233619525562</v>
+        <v>2.6392233619525491</v>
       </c>
       <c r="J11" s="0">
-        <v>2.6392233619525562</v>
+        <v>2.6392233619525491</v>
       </c>
       <c r="K11" s="0" t="b">
         <v>1</v>
@@ -749,22 +749,22 @@
         <v>25</v>
       </c>
       <c r="E12" s="0">
-        <v>21.340781093975643</v>
+        <v>21.340781093975799</v>
       </c>
       <c r="F12" s="0">
-        <v>-3.659218906024357</v>
+        <v>-3.6592189060242006</v>
       </c>
       <c r="G12" s="0">
-        <v>3.659218906024357</v>
+        <v>3.6592189060242006</v>
       </c>
       <c r="H12" s="0">
-        <v>20.840781093975643</v>
+        <v>20.840781093975799</v>
       </c>
       <c r="I12" s="0">
-        <v>-4.159218906024357</v>
+        <v>-4.1592189060242006</v>
       </c>
       <c r="J12" s="0">
-        <v>4.159218906024357</v>
+        <v>4.1592189060242006</v>
       </c>
       <c r="K12" s="0" t="b">
         <v>0</v>
@@ -787,22 +787,22 @@
         <v>22.5</v>
       </c>
       <c r="E13" s="0">
-        <v>20.978049923231396</v>
+        <v>20.978049923231478</v>
       </c>
       <c r="F13" s="0">
-        <v>-1.5219500767686043</v>
+        <v>-1.5219500767685226</v>
       </c>
       <c r="G13" s="0">
-        <v>1.5219500767686043</v>
+        <v>1.5219500767685226</v>
       </c>
       <c r="H13" s="0">
-        <v>20.478049923231396</v>
+        <v>20.478049923231478</v>
       </c>
       <c r="I13" s="0">
-        <v>-2.0219500767686043</v>
+        <v>-2.0219500767685226</v>
       </c>
       <c r="J13" s="0">
-        <v>2.0219500767686043</v>
+        <v>2.0219500767685226</v>
       </c>
       <c r="K13" s="0" t="b">
         <v>0</v>
@@ -825,22 +825,22 @@
         <v>20.5</v>
       </c>
       <c r="E14" s="0">
-        <v>21.09212704657039</v>
+        <v>21.092127046570496</v>
       </c>
       <c r="F14" s="0">
-        <v>0.59212704657038984</v>
+        <v>0.59212704657049642</v>
       </c>
       <c r="G14" s="0">
-        <v>0.59212704657038984</v>
+        <v>0.59212704657049642</v>
       </c>
       <c r="H14" s="0">
-        <v>20.59212704657039</v>
+        <v>20.592127046570496</v>
       </c>
       <c r="I14" s="0">
-        <v>0.092127046570389837</v>
+        <v>0.092127046570496418</v>
       </c>
       <c r="J14" s="0">
-        <v>0.092127046570389837</v>
+        <v>0.092127046570496418</v>
       </c>
       <c r="K14" s="0" t="b">
         <v>1</v>
@@ -863,22 +863,22 @@
         <v>19.5</v>
       </c>
       <c r="E15" s="0">
-        <v>20.19764748664192</v>
+        <v>20.197647486641834</v>
       </c>
       <c r="F15" s="0">
-        <v>0.69764748664191956</v>
+        <v>0.69764748664183429</v>
       </c>
       <c r="G15" s="0">
-        <v>0.69764748664191956</v>
+        <v>0.69764748664183429</v>
       </c>
       <c r="H15" s="0">
-        <v>19.69764748664192</v>
+        <v>19.697647486641834</v>
       </c>
       <c r="I15" s="0">
-        <v>0.19764748664191956</v>
+        <v>0.19764748664183429</v>
       </c>
       <c r="J15" s="0">
-        <v>0.19764748664191956</v>
+        <v>0.19764748664183429</v>
       </c>
       <c r="K15" s="0" t="b">
         <v>1</v>
@@ -901,22 +901,22 @@
         <v>19.5</v>
       </c>
       <c r="E16" s="0">
-        <v>19.980930475594931</v>
+        <v>19.980930475594946</v>
       </c>
       <c r="F16" s="0">
-        <v>0.48093047559493129</v>
+        <v>0.48093047559494551</v>
       </c>
       <c r="G16" s="0">
-        <v>0.48093047559493129</v>
+        <v>0.48093047559494551</v>
       </c>
       <c r="H16" s="0">
-        <v>19.480930475594931</v>
+        <v>19.480930475594946</v>
       </c>
       <c r="I16" s="0">
-        <v>-0.019069524405068705</v>
+        <v>-0.019069524405054494</v>
       </c>
       <c r="J16" s="0">
-        <v>0.019069524405068705</v>
+        <v>0.019069524405054494</v>
       </c>
       <c r="K16" s="0" t="b">
         <v>0</v>
@@ -939,22 +939,22 @@
         <v>18.5</v>
       </c>
       <c r="E17" s="0">
-        <v>18.024800051194681</v>
+        <v>18.02480005119472</v>
       </c>
       <c r="F17" s="0">
-        <v>-0.47519994880531868</v>
+        <v>-0.4751999488052796</v>
       </c>
       <c r="G17" s="0">
-        <v>0.47519994880531868</v>
+        <v>0.4751999488052796</v>
       </c>
       <c r="H17" s="0">
-        <v>17.524800051194681</v>
+        <v>17.52480005119472</v>
       </c>
       <c r="I17" s="0">
-        <v>-0.97519994880531868</v>
+        <v>-0.9751999488052796</v>
       </c>
       <c r="J17" s="0">
-        <v>0.97519994880531868</v>
+        <v>0.9751999488052796</v>
       </c>
       <c r="K17" s="0" t="b">
         <v>0</v>
@@ -977,22 +977,22 @@
         <v>23.75</v>
       </c>
       <c r="E18" s="0">
-        <v>20.017483819780694</v>
+        <v>20.01748381978075</v>
       </c>
       <c r="F18" s="0">
-        <v>-3.7325161802193065</v>
+        <v>-3.7325161802192497</v>
       </c>
       <c r="G18" s="0">
-        <v>3.7325161802193065</v>
+        <v>3.7325161802192497</v>
       </c>
       <c r="H18" s="0">
-        <v>19.517483819780694</v>
+        <v>19.51748381978075</v>
       </c>
       <c r="I18" s="0">
-        <v>-4.2325161802193065</v>
+        <v>-4.2325161802192497</v>
       </c>
       <c r="J18" s="0">
-        <v>4.2325161802193065</v>
+        <v>4.2325161802192497</v>
       </c>
       <c r="K18" s="0" t="b">
         <v>0</v>
@@ -1015,22 +1015,22 @@
         <v>22.25</v>
       </c>
       <c r="E19" s="0">
-        <v>21.295667519802798</v>
+        <v>21.295667519802794</v>
       </c>
       <c r="F19" s="0">
-        <v>-0.95433248019720196</v>
+        <v>-0.95433248019720551</v>
       </c>
       <c r="G19" s="0">
-        <v>0.95433248019720196</v>
+        <v>0.95433248019720551</v>
       </c>
       <c r="H19" s="0">
-        <v>20.795667519802798</v>
+        <v>20.795667519802794</v>
       </c>
       <c r="I19" s="0">
-        <v>-1.454332480197202</v>
+        <v>-1.4543324801972055</v>
       </c>
       <c r="J19" s="0">
-        <v>1.454332480197202</v>
+        <v>1.4543324801972055</v>
       </c>
       <c r="K19" s="0" t="b">
         <v>0</v>
@@ -1053,22 +1053,22 @@
         <v>25.5</v>
       </c>
       <c r="E20" s="0">
-        <v>21.496023629275225</v>
+        <v>21.496023629275136</v>
       </c>
       <c r="F20" s="0">
-        <v>-4.0039763707247751</v>
+        <v>-4.0039763707248639</v>
       </c>
       <c r="G20" s="0">
-        <v>4.0039763707247751</v>
+        <v>4.0039763707248639</v>
       </c>
       <c r="H20" s="0">
-        <v>20.996023629275225</v>
+        <v>20.996023629275136</v>
       </c>
       <c r="I20" s="0">
-        <v>-4.5039763707247751</v>
+        <v>-4.5039763707248639</v>
       </c>
       <c r="J20" s="0">
-        <v>4.5039763707247751</v>
+        <v>4.5039763707248639</v>
       </c>
       <c r="K20" s="0" t="b">
         <v>0</v>
@@ -1091,22 +1091,22 @@
         <v>22.5</v>
       </c>
       <c r="E21" s="0">
-        <v>23.568502663981224</v>
+        <v>23.568502663981246</v>
       </c>
       <c r="F21" s="0">
-        <v>1.0685026639812243</v>
+        <v>1.0685026639812456</v>
       </c>
       <c r="G21" s="0">
-        <v>1.0685026639812243</v>
+        <v>1.0685026639812456</v>
       </c>
       <c r="H21" s="0">
-        <v>23.068502663981224</v>
+        <v>23.068502663981246</v>
       </c>
       <c r="I21" s="0">
-        <v>0.56850266398122429</v>
+        <v>0.5685026639812456</v>
       </c>
       <c r="J21" s="0">
-        <v>0.56850266398122429</v>
+        <v>0.5685026639812456</v>
       </c>
       <c r="K21" s="0" t="b">
         <v>1</v>
@@ -1129,22 +1129,22 @@
         <v>21.5</v>
       </c>
       <c r="E22" s="0">
-        <v>20.390724184103309</v>
+        <v>20.390724184103235</v>
       </c>
       <c r="F22" s="0">
-        <v>-1.1092758158966909</v>
+        <v>-1.1092758158967655</v>
       </c>
       <c r="G22" s="0">
-        <v>1.1092758158966909</v>
+        <v>1.1092758158967655</v>
       </c>
       <c r="H22" s="0">
-        <v>19.890724184103309</v>
+        <v>19.890724184103235</v>
       </c>
       <c r="I22" s="0">
-        <v>-1.6092758158966909</v>
+        <v>-1.6092758158967655</v>
       </c>
       <c r="J22" s="0">
-        <v>1.6092758158966909</v>
+        <v>1.6092758158967655</v>
       </c>
       <c r="K22" s="0" t="b">
         <v>0</v>
@@ -1167,22 +1167,22 @@
         <v>20</v>
       </c>
       <c r="E23" s="0">
-        <v>21.287683950758986</v>
+        <v>21.287683950758982</v>
       </c>
       <c r="F23" s="0">
-        <v>1.2876839507589857</v>
+        <v>1.2876839507589821</v>
       </c>
       <c r="G23" s="0">
-        <v>1.2876839507589857</v>
+        <v>1.2876839507589821</v>
       </c>
       <c r="H23" s="0">
-        <v>20.787683950758986</v>
+        <v>20.787683950758982</v>
       </c>
       <c r="I23" s="0">
-        <v>0.78768395075898567</v>
+        <v>0.78768395075898212</v>
       </c>
       <c r="J23" s="0">
-        <v>0.78768395075898567</v>
+        <v>0.78768395075898212</v>
       </c>
       <c r="K23" s="0" t="b">
         <v>1</v>
@@ -1205,22 +1205,22 @@
         <v>19.5</v>
       </c>
       <c r="E24" s="0">
-        <v>21.042056395918586</v>
+        <v>21.042056395918579</v>
       </c>
       <c r="F24" s="0">
-        <v>1.5420563959185856</v>
+        <v>1.5420563959185785</v>
       </c>
       <c r="G24" s="0">
-        <v>1.5420563959185856</v>
+        <v>1.5420563959185785</v>
       </c>
       <c r="H24" s="0">
-        <v>20.542056395918586</v>
+        <v>20.542056395918579</v>
       </c>
       <c r="I24" s="0">
-        <v>1.0420563959185856</v>
+        <v>1.0420563959185785</v>
       </c>
       <c r="J24" s="0">
-        <v>1.0420563959185856</v>
+        <v>1.0420563959185785</v>
       </c>
       <c r="K24" s="0" t="b">
         <v>1</v>
@@ -1243,22 +1243,22 @@
         <v>18.5</v>
       </c>
       <c r="E25" s="0">
-        <v>20.835090168187961</v>
+        <v>20.835090168188007</v>
       </c>
       <c r="F25" s="0">
-        <v>2.3350901681879606</v>
+        <v>2.3350901681880067</v>
       </c>
       <c r="G25" s="0">
-        <v>2.3350901681879606</v>
+        <v>2.3350901681880067</v>
       </c>
       <c r="H25" s="0">
-        <v>20.335090168187961</v>
+        <v>20.335090168188007</v>
       </c>
       <c r="I25" s="0">
-        <v>1.8350901681879606</v>
+        <v>1.8350901681880067</v>
       </c>
       <c r="J25" s="0">
-        <v>1.8350901681879606</v>
+        <v>1.8350901681880067</v>
       </c>
       <c r="K25" s="0" t="b">
         <v>1</v>
@@ -1281,22 +1281,22 @@
         <v>17.5</v>
       </c>
       <c r="E26" s="0">
-        <v>20.863933052565162</v>
+        <v>20.863933052565219</v>
       </c>
       <c r="F26" s="0">
-        <v>3.3639330525651623</v>
+        <v>3.3639330525652191</v>
       </c>
       <c r="G26" s="0">
-        <v>3.3639330525651623</v>
+        <v>3.3639330525652191</v>
       </c>
       <c r="H26" s="0">
-        <v>20.363933052565162</v>
+        <v>20.363933052565219</v>
       </c>
       <c r="I26" s="0">
-        <v>2.8639330525651623</v>
+        <v>2.8639330525652191</v>
       </c>
       <c r="J26" s="0">
-        <v>2.8639330525651623</v>
+        <v>2.8639330525652191</v>
       </c>
       <c r="K26" s="0" t="b">
         <v>1</v>
@@ -1319,22 +1319,22 @@
         <v>21.25</v>
       </c>
       <c r="E27" s="0">
-        <v>21.115411716359887</v>
+        <v>21.115411716360001</v>
       </c>
       <c r="F27" s="0">
-        <v>-0.1345882836401131</v>
+        <v>-0.13458828363999942</v>
       </c>
       <c r="G27" s="0">
-        <v>0.1345882836401131</v>
+        <v>0.13458828363999942</v>
       </c>
       <c r="H27" s="0">
-        <v>20.615411716359887</v>
+        <v>20.615411716360001</v>
       </c>
       <c r="I27" s="0">
-        <v>-0.63458828364011311</v>
+        <v>-0.63458828363999942</v>
       </c>
       <c r="J27" s="0">
-        <v>0.63458828364011311</v>
+        <v>0.63458828363999942</v>
       </c>
       <c r="K27" s="0" t="b">
         <v>0</v>
@@ -1357,22 +1357,22 @@
         <v>19.25</v>
       </c>
       <c r="E28" s="0">
-        <v>20.100410455154179</v>
+        <v>20.100410455154197</v>
       </c>
       <c r="F28" s="0">
-        <v>0.85041045515417935</v>
+        <v>0.85041045515419711</v>
       </c>
       <c r="G28" s="0">
-        <v>0.85041045515417935</v>
+        <v>0.85041045515419711</v>
       </c>
       <c r="H28" s="0">
-        <v>19.600410455154179</v>
+        <v>19.600410455154197</v>
       </c>
       <c r="I28" s="0">
-        <v>0.35041045515417935</v>
+        <v>0.35041045515419711</v>
       </c>
       <c r="J28" s="0">
-        <v>0.35041045515417935</v>
+        <v>0.35041045515419711</v>
       </c>
       <c r="K28" s="0" t="b">
         <v>1</v>
@@ -1395,22 +1395,22 @@
         <v>21.75</v>
       </c>
       <c r="E29" s="0">
-        <v>21.338451874065345</v>
+        <v>21.338451874065342</v>
       </c>
       <c r="F29" s="0">
-        <v>-0.41154812593465451</v>
+        <v>-0.41154812593465806</v>
       </c>
       <c r="G29" s="0">
-        <v>0.41154812593465451</v>
+        <v>0.41154812593465806</v>
       </c>
       <c r="H29" s="0">
-        <v>20.838451874065345</v>
+        <v>20.838451874065342</v>
       </c>
       <c r="I29" s="0">
-        <v>-0.91154812593465451</v>
+        <v>-0.91154812593465806</v>
       </c>
       <c r="J29" s="0">
-        <v>0.91154812593465451</v>
+        <v>0.91154812593465806</v>
       </c>
       <c r="K29" s="0" t="b">
         <v>0</v>
@@ -1433,22 +1433,22 @@
         <v>20.75</v>
       </c>
       <c r="E30" s="0">
-        <v>23.569401079731211</v>
+        <v>23.569401079731229</v>
       </c>
       <c r="F30" s="0">
-        <v>2.819401079731211</v>
+        <v>2.8194010797312288</v>
       </c>
       <c r="G30" s="0">
-        <v>2.819401079731211</v>
+        <v>2.8194010797312288</v>
       </c>
       <c r="H30" s="0">
-        <v>23.069401079731211</v>
+        <v>23.069401079731229</v>
       </c>
       <c r="I30" s="0">
-        <v>2.319401079731211</v>
+        <v>2.3194010797312288</v>
       </c>
       <c r="J30" s="0">
-        <v>2.319401079731211</v>
+        <v>2.3194010797312288</v>
       </c>
       <c r="K30" s="0" t="b">
         <v>1</v>
@@ -1509,22 +1509,22 @@
         <v>19.5</v>
       </c>
       <c r="E32" s="0">
-        <v>19.973727228638744</v>
+        <v>19.973727228638794</v>
       </c>
       <c r="F32" s="0">
-        <v>0.47372722863874373</v>
+        <v>0.47372722863879346</v>
       </c>
       <c r="G32" s="0">
-        <v>0.47372722863874373</v>
+        <v>0.47372722863879346</v>
       </c>
       <c r="H32" s="0">
-        <v>19.473727228638744</v>
+        <v>19.473727228638794</v>
       </c>
       <c r="I32" s="0">
-        <v>-0.026272771361256275</v>
+        <v>-0.026272771361206537</v>
       </c>
       <c r="J32" s="0">
-        <v>0.026272771361256275</v>
+        <v>0.026272771361206537</v>
       </c>
       <c r="K32" s="0" t="b">
         <v>0</v>
@@ -1547,22 +1547,22 @@
         <v>19.5</v>
       </c>
       <c r="E33" s="0">
-        <v>20.249226530501581</v>
+        <v>20.249226530501588</v>
       </c>
       <c r="F33" s="0">
-        <v>0.74922653050158061</v>
+        <v>0.74922653050158772</v>
       </c>
       <c r="G33" s="0">
-        <v>0.74922653050158061</v>
+        <v>0.74922653050158772</v>
       </c>
       <c r="H33" s="0">
-        <v>19.749226530501581</v>
+        <v>19.749226530501588</v>
       </c>
       <c r="I33" s="0">
-        <v>0.24922653050158061</v>
+        <v>0.24922653050158772</v>
       </c>
       <c r="J33" s="0">
-        <v>0.24922653050158061</v>
+        <v>0.24922653050158772</v>
       </c>
       <c r="K33" s="0" t="b">
         <v>1</v>
@@ -1585,22 +1585,22 @@
         <v>21</v>
       </c>
       <c r="E34" s="0">
-        <v>20.251386587531563</v>
+        <v>20.251386587531567</v>
       </c>
       <c r="F34" s="0">
-        <v>-0.74861341246843693</v>
+        <v>-0.74861341246843338</v>
       </c>
       <c r="G34" s="0">
-        <v>0.74861341246843693</v>
+        <v>0.74861341246843338</v>
       </c>
       <c r="H34" s="0">
-        <v>19.751386587531563</v>
+        <v>19.751386587531567</v>
       </c>
       <c r="I34" s="0">
-        <v>-1.2486134124684369</v>
+        <v>-1.2486134124684334</v>
       </c>
       <c r="J34" s="0">
-        <v>1.2486134124684369</v>
+        <v>1.2486134124684334</v>
       </c>
       <c r="K34" s="0" t="b">
         <v>0</v>
@@ -1623,22 +1623,22 @@
         <v>20.25</v>
       </c>
       <c r="E35" s="0">
-        <v>21.064799978961272</v>
+        <v>21.064799978961261</v>
       </c>
       <c r="F35" s="0">
-        <v>0.81479997896127188</v>
+        <v>0.81479997896126122</v>
       </c>
       <c r="G35" s="0">
-        <v>0.81479997896127188</v>
+        <v>0.81479997896126122</v>
       </c>
       <c r="H35" s="0">
-        <v>20.564799978961272</v>
+        <v>20.564799978961261</v>
       </c>
       <c r="I35" s="0">
-        <v>0.31479997896127188</v>
+        <v>0.31479997896126122</v>
       </c>
       <c r="J35" s="0">
-        <v>0.31479997896127188</v>
+        <v>0.31479997896126122</v>
       </c>
       <c r="K35" s="0" t="b">
         <v>1</v>
@@ -1661,22 +1661,22 @@
         <v>21.5</v>
       </c>
       <c r="E36" s="0">
-        <v>20.889224533465722</v>
+        <v>20.889224533465761</v>
       </c>
       <c r="F36" s="0">
-        <v>-0.61077546653427817</v>
+        <v>-0.61077546653423909</v>
       </c>
       <c r="G36" s="0">
-        <v>0.61077546653427817</v>
+        <v>0.61077546653423909</v>
       </c>
       <c r="H36" s="0">
-        <v>20.389224533465722</v>
+        <v>20.389224533465761</v>
       </c>
       <c r="I36" s="0">
-        <v>-1.1107754665342782</v>
+        <v>-1.1107754665342391</v>
       </c>
       <c r="J36" s="0">
-        <v>1.1107754665342782</v>
+        <v>1.1107754665342391</v>
       </c>
       <c r="K36" s="0" t="b">
         <v>0</v>
@@ -1699,22 +1699,22 @@
         <v>19.5</v>
       </c>
       <c r="E37" s="0">
-        <v>20.189773060306788</v>
+        <v>20.189773060306699</v>
       </c>
       <c r="F37" s="0">
-        <v>0.68977306030678776</v>
+        <v>0.68977306030669894</v>
       </c>
       <c r="G37" s="0">
-        <v>0.68977306030678776</v>
+        <v>0.68977306030669894</v>
       </c>
       <c r="H37" s="0">
-        <v>19.689773060306788</v>
+        <v>19.689773060306699</v>
       </c>
       <c r="I37" s="0">
-        <v>0.18977306030678776</v>
+        <v>0.18977306030669894</v>
       </c>
       <c r="J37" s="0">
-        <v>0.18977306030678776</v>
+        <v>0.18977306030669894</v>
       </c>
       <c r="K37" s="0" t="b">
         <v>1</v>
@@ -1737,22 +1737,22 @@
         <v>25</v>
       </c>
       <c r="E38" s="0">
-        <v>21.333895759852712</v>
+        <v>21.333895759852865</v>
       </c>
       <c r="F38" s="0">
-        <v>-3.6661042401472877</v>
+        <v>-3.6661042401471349</v>
       </c>
       <c r="G38" s="0">
-        <v>3.6661042401472877</v>
+        <v>3.6661042401471349</v>
       </c>
       <c r="H38" s="0">
-        <v>20.833895759852712</v>
+        <v>20.833895759852865</v>
       </c>
       <c r="I38" s="0">
-        <v>-4.1661042401472877</v>
+        <v>-4.1661042401471349</v>
       </c>
       <c r="J38" s="0">
-        <v>4.1661042401472877</v>
+        <v>4.1661042401471349</v>
       </c>
       <c r="K38" s="0" t="b">
         <v>0</v>
@@ -1775,22 +1775,22 @@
         <v>19</v>
       </c>
       <c r="E39" s="0">
-        <v>20.246813641921079</v>
+        <v>20.246813641920994</v>
       </c>
       <c r="F39" s="0">
-        <v>1.2468136419210794</v>
+        <v>1.2468136419209941</v>
       </c>
       <c r="G39" s="0">
-        <v>1.2468136419210794</v>
+        <v>1.2468136419209941</v>
       </c>
       <c r="H39" s="0">
-        <v>19.746813641921079</v>
+        <v>19.746813641920994</v>
       </c>
       <c r="I39" s="0">
-        <v>0.74681364192107935</v>
+        <v>0.74681364192099409</v>
       </c>
       <c r="J39" s="0">
-        <v>0.74681364192107935</v>
+        <v>0.74681364192099409</v>
       </c>
       <c r="K39" s="0" t="b">
         <v>1</v>
@@ -1813,22 +1813,22 @@
         <v>19</v>
       </c>
       <c r="E40" s="0">
-        <v>21.184646472409469</v>
+        <v>21.184646472409455</v>
       </c>
       <c r="F40" s="0">
-        <v>2.1846464724094688</v>
+        <v>2.1846464724094545</v>
       </c>
       <c r="G40" s="0">
-        <v>2.1846464724094688</v>
+        <v>2.1846464724094545</v>
       </c>
       <c r="H40" s="0">
-        <v>20.684646472409469</v>
+        <v>20.684646472409455</v>
       </c>
       <c r="I40" s="0">
-        <v>1.6846464724094688</v>
+        <v>1.6846464724094545</v>
       </c>
       <c r="J40" s="0">
-        <v>1.6846464724094688</v>
+        <v>1.6846464724094545</v>
       </c>
       <c r="K40" s="0" t="b">
         <v>1</v>
@@ -1851,22 +1851,22 @@
         <v>21</v>
       </c>
       <c r="E41" s="0">
-        <v>20.699116814111534</v>
+        <v>20.699116814111523</v>
       </c>
       <c r="F41" s="0">
-        <v>-0.30088318588846619</v>
+        <v>-0.30088318588847685</v>
       </c>
       <c r="G41" s="0">
-        <v>0.30088318588846619</v>
+        <v>0.30088318588847685</v>
       </c>
       <c r="H41" s="0">
-        <v>20.199116814111534</v>
+        <v>20.199116814111523</v>
       </c>
       <c r="I41" s="0">
-        <v>-0.80088318588846619</v>
+        <v>-0.80088318588847685</v>
       </c>
       <c r="J41" s="0">
-        <v>0.80088318588846619</v>
+        <v>0.80088318588847685</v>
       </c>
       <c r="K41" s="0" t="b">
         <v>0</v>
@@ -1889,22 +1889,22 @@
         <v>20.5</v>
       </c>
       <c r="E42" s="0">
-        <v>21.08240152931262</v>
+        <v>21.082401529312627</v>
       </c>
       <c r="F42" s="0">
-        <v>0.58240152931261946</v>
+        <v>0.58240152931262656</v>
       </c>
       <c r="G42" s="0">
-        <v>0.58240152931261946</v>
+        <v>0.58240152931262656</v>
       </c>
       <c r="H42" s="0">
-        <v>20.58240152931262</v>
+        <v>20.582401529312627</v>
       </c>
       <c r="I42" s="0">
-        <v>0.082401529312619459</v>
+        <v>0.082401529312626565</v>
       </c>
       <c r="J42" s="0">
-        <v>0.082401529312619459</v>
+        <v>0.082401529312626565</v>
       </c>
       <c r="K42" s="0" t="b">
         <v>1</v>
@@ -1965,22 +1965,22 @@
         <v>20</v>
       </c>
       <c r="E44" s="0">
-        <v>21.023316309353117</v>
+        <v>21.023316309353106</v>
       </c>
       <c r="F44" s="0">
-        <v>1.0233163093531168</v>
+        <v>1.0233163093531061</v>
       </c>
       <c r="G44" s="0">
-        <v>1.0233163093531168</v>
+        <v>1.0233163093531061</v>
       </c>
       <c r="H44" s="0">
-        <v>20.523316309353117</v>
+        <v>20.523316309353106</v>
       </c>
       <c r="I44" s="0">
-        <v>0.52331630935311679</v>
+        <v>0.52331630935310613</v>
       </c>
       <c r="J44" s="0">
-        <v>0.52331630935311679</v>
+        <v>0.52331630935310613</v>
       </c>
       <c r="K44" s="0" t="b">
         <v>1</v>
@@ -2003,22 +2003,22 @@
         <v>20</v>
       </c>
       <c r="E45" s="0">
-        <v>21.254712523793806</v>
+        <v>21.254712523793803</v>
       </c>
       <c r="F45" s="0">
-        <v>1.2547125237938062</v>
+        <v>1.2547125237938026</v>
       </c>
       <c r="G45" s="0">
-        <v>1.2547125237938062</v>
+        <v>1.2547125237938026</v>
       </c>
       <c r="H45" s="0">
-        <v>20.754712523793806</v>
+        <v>20.754712523793803</v>
       </c>
       <c r="I45" s="0">
-        <v>0.75471252379380616</v>
+        <v>0.7547125237938026</v>
       </c>
       <c r="J45" s="0">
-        <v>0.75471252379380616</v>
+        <v>0.7547125237938026</v>
       </c>
       <c r="K45" s="0" t="b">
         <v>1</v>
@@ -2041,22 +2041,22 @@
         <v>20</v>
       </c>
       <c r="E46" s="0">
-        <v>20.294071043694377</v>
+        <v>20.294071043694299</v>
       </c>
       <c r="F46" s="0">
-        <v>0.29407104369437676</v>
+        <v>0.2940710436942986</v>
       </c>
       <c r="G46" s="0">
-        <v>0.29407104369437676</v>
+        <v>0.2940710436942986</v>
       </c>
       <c r="H46" s="0">
-        <v>19.794071043694377</v>
+        <v>19.794071043694299</v>
       </c>
       <c r="I46" s="0">
-        <v>-0.20592895630562325</v>
+        <v>-0.20592895630570141</v>
       </c>
       <c r="J46" s="0">
-        <v>0.20592895630562325</v>
+        <v>0.20592895630570141</v>
       </c>
       <c r="K46" s="0" t="b">
         <v>0</v>
@@ -2079,22 +2079,22 @@
         <v>22</v>
       </c>
       <c r="E47" s="0">
-        <v>20.512678259809739</v>
+        <v>20.512678259809707</v>
       </c>
       <c r="F47" s="0">
-        <v>-1.4873217401902608</v>
+        <v>-1.4873217401902927</v>
       </c>
       <c r="G47" s="0">
-        <v>1.4873217401902608</v>
+        <v>1.4873217401902927</v>
       </c>
       <c r="H47" s="0">
-        <v>20.012678259809739</v>
+        <v>20.012678259809707</v>
       </c>
       <c r="I47" s="0">
-        <v>-1.9873217401902608</v>
+        <v>-1.9873217401902927</v>
       </c>
       <c r="J47" s="0">
-        <v>1.9873217401902608</v>
+        <v>1.9873217401902927</v>
       </c>
       <c r="K47" s="0" t="b">
         <v>0</v>
@@ -2117,22 +2117,22 @@
         <v>22</v>
       </c>
       <c r="E48" s="0">
-        <v>20.996711000581946</v>
+        <v>20.996711000581893</v>
       </c>
       <c r="F48" s="0">
-        <v>-1.0032889994180536</v>
+        <v>-1.0032889994181069</v>
       </c>
       <c r="G48" s="0">
-        <v>1.0032889994180536</v>
+        <v>1.0032889994181069</v>
       </c>
       <c r="H48" s="0">
-        <v>20.496711000581946</v>
+        <v>20.496711000581893</v>
       </c>
       <c r="I48" s="0">
-        <v>-1.5032889994180536</v>
+        <v>-1.5032889994181069</v>
       </c>
       <c r="J48" s="0">
-        <v>1.5032889994180536</v>
+        <v>1.5032889994181069</v>
       </c>
       <c r="K48" s="0" t="b">
         <v>0</v>
@@ -2155,22 +2155,22 @@
         <v>23</v>
       </c>
       <c r="E49" s="0">
-        <v>21.448804788470863</v>
+        <v>21.448804788470845</v>
       </c>
       <c r="F49" s="0">
-        <v>-1.5511952115291372</v>
+        <v>-1.551195211529155</v>
       </c>
       <c r="G49" s="0">
-        <v>1.5511952115291372</v>
+        <v>1.551195211529155</v>
       </c>
       <c r="H49" s="0">
-        <v>20.948804788470863</v>
+        <v>20.948804788470845</v>
       </c>
       <c r="I49" s="0">
-        <v>-2.0511952115291372</v>
+        <v>-2.051195211529155</v>
       </c>
       <c r="J49" s="0">
-        <v>2.0511952115291372</v>
+        <v>2.051195211529155</v>
       </c>
       <c r="K49" s="0" t="b">
         <v>0</v>
@@ -2231,22 +2231,22 @@
         <v>21.5</v>
       </c>
       <c r="E51" s="0">
-        <v>20.581229951261133</v>
+        <v>20.581229951261111</v>
       </c>
       <c r="F51" s="0">
-        <v>-0.91877004873886747</v>
+        <v>-0.91877004873888879</v>
       </c>
       <c r="G51" s="0">
-        <v>0.91877004873886747</v>
+        <v>0.91877004873888879</v>
       </c>
       <c r="H51" s="0">
-        <v>20.081229951261133</v>
+        <v>20.081229951261111</v>
       </c>
       <c r="I51" s="0">
-        <v>-1.4187700487388675</v>
+        <v>-1.4187700487388888</v>
       </c>
       <c r="J51" s="0">
-        <v>1.4187700487388675</v>
+        <v>1.4187700487388888</v>
       </c>
       <c r="K51" s="0" t="b">
         <v>0</v>
@@ -2269,22 +2269,22 @@
         <v>19.199999999999999</v>
       </c>
       <c r="E52" s="0">
-        <v>21.027047777816293</v>
+        <v>21.027047777816232</v>
       </c>
       <c r="F52" s="0">
-        <v>1.8270477778162935</v>
+        <v>1.8270477778162331</v>
       </c>
       <c r="G52" s="0">
-        <v>1.8270477778162935</v>
+        <v>1.8270477778162331</v>
       </c>
       <c r="H52" s="0">
-        <v>20.527047777816293</v>
+        <v>20.527047777816232</v>
       </c>
       <c r="I52" s="0">
-        <v>1.3270477778162935</v>
+        <v>1.3270477778162331</v>
       </c>
       <c r="J52" s="0">
-        <v>1.3270477778162935</v>
+        <v>1.3270477778162331</v>
       </c>
       <c r="K52" s="0" t="b">
         <v>1</v>
@@ -2307,22 +2307,22 @@
         <v>17.5</v>
       </c>
       <c r="E53" s="0">
-        <v>20.692040524487059</v>
+        <v>20.692040524487062</v>
       </c>
       <c r="F53" s="0">
-        <v>3.1920405244870587</v>
+        <v>3.1920405244870622</v>
       </c>
       <c r="G53" s="0">
-        <v>3.1920405244870587</v>
+        <v>3.1920405244870622</v>
       </c>
       <c r="H53" s="0">
-        <v>20.192040524487059</v>
+        <v>20.192040524487062</v>
       </c>
       <c r="I53" s="0">
-        <v>2.6920405244870587</v>
+        <v>2.6920405244870622</v>
       </c>
       <c r="J53" s="0">
-        <v>2.6920405244870587</v>
+        <v>2.6920405244870622</v>
       </c>
       <c r="K53" s="0" t="b">
         <v>1</v>
@@ -2383,22 +2383,22 @@
         <v>19</v>
       </c>
       <c r="E55" s="0">
-        <v>21.067175469084791</v>
+        <v>21.067175469084717</v>
       </c>
       <c r="F55" s="0">
-        <v>2.0671754690847912</v>
+        <v>2.0671754690847166</v>
       </c>
       <c r="G55" s="0">
-        <v>2.0671754690847912</v>
+        <v>2.0671754690847166</v>
       </c>
       <c r="H55" s="0">
-        <v>20.567175469084791</v>
+        <v>20.567175469084717</v>
       </c>
       <c r="I55" s="0">
-        <v>1.5671754690847912</v>
+        <v>1.5671754690847166</v>
       </c>
       <c r="J55" s="0">
-        <v>1.5671754690847912</v>
+        <v>1.5671754690847166</v>
       </c>
       <c r="K55" s="0" t="b">
         <v>1</v>
@@ -2416,13 +2416,13 @@
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="51.140625" customWidth="true"/>
-    <col min="2" max="2" width="9.5703125" customWidth="true"/>
-    <col min="3" max="3" width="10.42578125" customWidth="true"/>
-    <col min="4" max="4" width="9.42578125" customWidth="true"/>
-    <col min="5" max="5" width="15.140625" customWidth="true"/>
-    <col min="6" max="6" width="14" customWidth="true"/>
-    <col min="7" max="7" width="11.7109375" customWidth="true"/>
+    <col min="1" max="1" width="46.21875" customWidth="true"/>
+    <col min="2" max="2" width="8.88671875" customWidth="true"/>
+    <col min="3" max="3" width="9.77734375" customWidth="true"/>
+    <col min="4" max="4" width="8.6640625" customWidth="true"/>
+    <col min="5" max="5" width="14.109375" customWidth="true"/>
+    <col min="6" max="6" width="12.5546875" customWidth="true"/>
+    <col min="7" max="7" width="10.5546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/預測結果與評估指標_kfold_mask幾何.xlsx
+++ b/預測結果與評估指標_kfold_mask幾何.xlsx
@@ -20,166 +20,166 @@
     <t>檔名</t>
   </si>
   <si>
-    <t>001_jpg.rf.4c9b567ff4deaebc95dfe818620028ba.jpg</t>
-  </si>
-  <si>
-    <t>002_jpg.rf.e7a3fcb45d83e3a2dd6afbe241bd1d73.jpg</t>
-  </si>
-  <si>
-    <t>003_jpg.rf.1f6d62636a99328020108bb78ef3c835.jpg</t>
-  </si>
-  <si>
-    <t>004_jpg.rf.4013d1526ae79399b0311b45cce6dc49.jpg</t>
-  </si>
-  <si>
-    <t>005_jpg.rf.db41c76a1a0f67c029e07def41fa7e71.jpg</t>
-  </si>
-  <si>
-    <t>006_jpg.rf.d226f3637e96179b1db115d31f983def.jpg</t>
-  </si>
-  <si>
-    <t>007_jpg.rf.700d0bf10fa8fd648835e0074572e5d8.jpg</t>
-  </si>
-  <si>
-    <t>008_jpg.rf.5812b75fe38ce91b0ecc6190e59be8c3.jpg</t>
-  </si>
-  <si>
-    <t>009_jpg.rf.8bab93b7d56749aa98648bdd1ca7afdb.jpg</t>
-  </si>
-  <si>
-    <t>010_jpg.rf.548a6fc07e0dd15ce1fb1c2efc5af9fa.jpg</t>
-  </si>
-  <si>
-    <t>011_jpg.rf.31dfe6cf21e941713e13d48e451b5b34.jpg</t>
-  </si>
-  <si>
-    <t>012_jpg.rf.1c49f445f9a076103a044e4d7ec4cbba.jpg</t>
-  </si>
-  <si>
-    <t>013_jpg.rf.5aa0c8322ac4e403fc96ddf0b299a532.jpg</t>
-  </si>
-  <si>
-    <t>014_jpg.rf.3c9e80b37f0a897edf939f5b2a539ad8.jpg</t>
-  </si>
-  <si>
-    <t>015_jpg.rf.94b4a7961d4eac445d4907eb273a8c9c.jpg</t>
-  </si>
-  <si>
-    <t>016_jpg.rf.7ab63b1fd0e68335acee897bc3b0a865.jpg</t>
-  </si>
-  <si>
-    <t>017_jpg.rf.f41244d846f5acefd512d3fe33b1f7c7.jpg</t>
-  </si>
-  <si>
-    <t>018_jpg.rf.22c1355b4bd4dc78157bf7cb3b88bd48.jpg</t>
-  </si>
-  <si>
-    <t>019_jpg.rf.5b1215807086f746eeb6c3f30bedcbee.jpg</t>
-  </si>
-  <si>
-    <t>020_jpg.rf.6f3df25507befe53cc2fe1e6839d320a.jpg</t>
-  </si>
-  <si>
-    <t>021_jpg.rf.8b63d0945baeef56e60cbc002150e4bb.jpg</t>
-  </si>
-  <si>
-    <t>022_jpg.rf.116af67b6e3794e3f8ed2f5d51cca8a1.jpg</t>
-  </si>
-  <si>
-    <t>023_jpg.rf.c81eb814a1c67711193aa6d0ef2ba449.jpg</t>
-  </si>
-  <si>
-    <t>024_jpg.rf.32a9c8afc84e54eb0a5df0b4c0ce394c.jpg</t>
-  </si>
-  <si>
-    <t>025_jpg.rf.f06a8c53e7f4b681c9427183b37f5bc2.jpg</t>
-  </si>
-  <si>
-    <t>026_jpg.rf.997b35ef0b16674048632d1fe4f74d00.jpg</t>
-  </si>
-  <si>
-    <t>027_jpg.rf.bef5c4b7ae4115dbc519047689c1b85a.jpg</t>
-  </si>
-  <si>
-    <t>028_jpg.rf.9dc294ecb02a107d9bb666dcad46368b.jpg</t>
-  </si>
-  <si>
-    <t>029_jpg.rf.68aa50dedf23782d475ba73aeefa8402.jpg</t>
-  </si>
-  <si>
-    <t>030_jpg.rf.324003241288b34853323a8b697e5754.jpg</t>
-  </si>
-  <si>
-    <t>031_jpg.rf.81b158711b26da9baabc14f9d9de3b5a.jpg</t>
-  </si>
-  <si>
-    <t>032_jpg.rf.3d37a54c9ba12c154d2dfd85c178f1a5.jpg</t>
-  </si>
-  <si>
-    <t>034_jpg.rf.e3e831d8a4dff6095497e0b762a559db.jpg</t>
-  </si>
-  <si>
-    <t>036_jpg.rf.8c4d79098e6081cff2adacdd480d6f2f.jpg</t>
-  </si>
-  <si>
-    <t>037_jpg.rf.819921ec8736ee833b89865b2a32b82c.jpg</t>
-  </si>
-  <si>
-    <t>038_jpg.rf.1a136bcdeab9ab0647ca0144bcfec321.jpg</t>
-  </si>
-  <si>
-    <t>039_jpg.rf.8aa0b7f7f99062b04dfaa93d6a8b3eb8.jpg</t>
-  </si>
-  <si>
-    <t>040_jpg.rf.df5a982adce80e1535fd79f09915d73e.jpg</t>
-  </si>
-  <si>
-    <t>041_jpg.rf.8deb0897ced5e98b0632a5bd5c8aa066.jpg</t>
-  </si>
-  <si>
-    <t>042_jpg.rf.537450cea4fdf0981f62c887cde69683.jpg</t>
-  </si>
-  <si>
-    <t>043_jpg.rf.1cfa29c51078c1490e4f53e0dbe550d0.jpg</t>
-  </si>
-  <si>
-    <t>044_jpg.rf.51542370502344e22d3b7f6d7fc12612.jpg</t>
-  </si>
-  <si>
-    <t>045_jpg.rf.e46cb1980f7a6958622ed2ded4ffffac.jpg</t>
-  </si>
-  <si>
-    <t>046_jpg.rf.0ca1b25cce4f59cd52ca2becb31fd347.jpg</t>
-  </si>
-  <si>
-    <t>047_jpg.rf.3e39cddbb127fc0627c898159bd295c5.jpg</t>
-  </si>
-  <si>
-    <t>048_jpg.rf.d2a9efb5a7dd6aa7a3c68edf3e1964fa.jpg</t>
-  </si>
-  <si>
-    <t>049_jpg.rf.b141f7e16aacaaeb3d29fbdccdd4fe3e.jpg</t>
-  </si>
-  <si>
-    <t>050_jpg.rf.c8c57a2d704b2ddbe1e8b0d476f7c4d2.jpg</t>
-  </si>
-  <si>
-    <t>051_jpg.rf.ee071fb1b0f034836f5eb0deae7cb200.jpg</t>
-  </si>
-  <si>
-    <t>052_jpg.rf.05513e55c358a01918e86390d9e777b0.jpg</t>
-  </si>
-  <si>
-    <t>054_jpg.rf.7a41f58896616b25f092f23715df71aa.jpg</t>
-  </si>
-  <si>
-    <t>055_jpg.rf.5978dcb08ec19062a87cfe4b44173ecb.jpg</t>
-  </si>
-  <si>
-    <t>056_jpg.rf.4cbb6e7aac1cddedc033a5d10d3dfbe4.jpg</t>
-  </si>
-  <si>
-    <t>057_jpg.rf.9ccaefd02e6cc640a3cd843e59908319.jpg</t>
+    <t>001_jpg.rf.f66116916f1034ff42d3ca622244a7a1.jpg</t>
+  </si>
+  <si>
+    <t>002_jpg.rf.9963a010c88f0c1cc16485557aa5bbe6.jpg</t>
+  </si>
+  <si>
+    <t>003_jpg.rf.e51ad05d7f902b25c75f3306c011afb7.jpg</t>
+  </si>
+  <si>
+    <t>004_jpg.rf.91185a83cc0c80eb5944863f195e0be0.jpg</t>
+  </si>
+  <si>
+    <t>005_jpg.rf.d6bfd25b1c387295bb0a4f9324b63b01.jpg</t>
+  </si>
+  <si>
+    <t>006_jpg.rf.8f9677e435d9bab806aec41abe9c509c.jpg</t>
+  </si>
+  <si>
+    <t>007_jpg.rf.28f6235ca85bfe67778bf72f55c5c953.jpg</t>
+  </si>
+  <si>
+    <t>008_jpg.rf.6e25bbbe74b05332cd98a16ebc2d06c0.jpg</t>
+  </si>
+  <si>
+    <t>009_jpg.rf.5810c0777bc3544fa8a8c4a2eec91372.jpg</t>
+  </si>
+  <si>
+    <t>010_jpg.rf.9cbc38a1e354038183129ed3ce5be3bd.jpg</t>
+  </si>
+  <si>
+    <t>011_jpg.rf.93e0abfd1c8ba679d6229582d68e3ebd.jpg</t>
+  </si>
+  <si>
+    <t>012_jpg.rf.e1e691535b634f6242b0126913c1555e.jpg</t>
+  </si>
+  <si>
+    <t>013_jpg.rf.74670a19a61e8d2ab4d6df93a721d0bf.jpg</t>
+  </si>
+  <si>
+    <t>014_jpg.rf.054fe3761f03a25fffe36bdaa7ab23e2.jpg</t>
+  </si>
+  <si>
+    <t>015_jpg.rf.695fde2697827038b691a9db68c2ea6d.jpg</t>
+  </si>
+  <si>
+    <t>016_jpg.rf.75bb53bb5f2a011d156abea4e002179b.jpg</t>
+  </si>
+  <si>
+    <t>017_jpg.rf.ad10c8b2d6a91298ac0054c6c5a26048.jpg</t>
+  </si>
+  <si>
+    <t>018_jpg.rf.91c3434693356f69dcfb4ff1391ae50a.jpg</t>
+  </si>
+  <si>
+    <t>019_jpg.rf.02669a2475da43f4dd5937f69b679539.jpg</t>
+  </si>
+  <si>
+    <t>020_jpg.rf.8aea54730f3eaefab1a23f121a8cdde5.jpg</t>
+  </si>
+  <si>
+    <t>021_jpg.rf.0e141b251ddd95981fa303ac34074643.jpg</t>
+  </si>
+  <si>
+    <t>022_jpg.rf.d81f9540b892ea7ac37449e2e58cd185.jpg</t>
+  </si>
+  <si>
+    <t>023_jpg.rf.a75c697708b75f0450bb502534659862.jpg</t>
+  </si>
+  <si>
+    <t>024_jpg.rf.b906eee89bff6be48d0b1f393563afe5.jpg</t>
+  </si>
+  <si>
+    <t>025_jpg.rf.53dce8c7583912dd1ab113e906cf36fb.jpg</t>
+  </si>
+  <si>
+    <t>026_jpg.rf.cfdf5a6895e2bd03cb6976a4b5cf835b.jpg</t>
+  </si>
+  <si>
+    <t>027_jpg.rf.ed6e0a09aff052ee7eb729d67c4ef8f1.jpg</t>
+  </si>
+  <si>
+    <t>028_jpg.rf.f3a5fa4f1100ce1f1b2fe62a286f4243.jpg</t>
+  </si>
+  <si>
+    <t>029_jpg.rf.7a37fc1012f6f1b9f3383cea6ef2e45d.jpg</t>
+  </si>
+  <si>
+    <t>030_jpg.rf.cbb0a79529edc5568178cf06bafeb089.jpg</t>
+  </si>
+  <si>
+    <t>031_jpg.rf.1ed000144fa3b11934892b9671c1e781.jpg</t>
+  </si>
+  <si>
+    <t>032_jpg.rf.877e0e9d11cc4ff0a204e9cd3caaafd6.jpg</t>
+  </si>
+  <si>
+    <t>034_jpg.rf.d7426278556ad57f73079b35d25ef281.jpg</t>
+  </si>
+  <si>
+    <t>036_jpg.rf.b3e624f1dc8935a1db79e67e87ddfadc.jpg</t>
+  </si>
+  <si>
+    <t>037_jpg.rf.a64a1a57aaa5a4d4b54a3780a8ce0073.jpg</t>
+  </si>
+  <si>
+    <t>038_jpg.rf.c4be0456da6e8262ed040a60b1cc3541.jpg</t>
+  </si>
+  <si>
+    <t>039_jpg.rf.9e9a050d1df53938e102f241a800ad16.jpg</t>
+  </si>
+  <si>
+    <t>040_jpg.rf.3deb2c457e4b0ef9a2dc1b8a45667489.jpg</t>
+  </si>
+  <si>
+    <t>041_jpg.rf.4bbbfea36253186251bba070ece9e7c7.jpg</t>
+  </si>
+  <si>
+    <t>042_jpg.rf.b5d22e7fba96fff8e1bc826bf0ec0937.jpg</t>
+  </si>
+  <si>
+    <t>043_jpg.rf.0335132c4f94a47f07539e86712ae9e6.jpg</t>
+  </si>
+  <si>
+    <t>044_jpg.rf.b6e79f35ae21127d7114b91bee408d7d.jpg</t>
+  </si>
+  <si>
+    <t>045_jpg.rf.f7b24cdaf9c17654e7cf9e869b4757cd.jpg</t>
+  </si>
+  <si>
+    <t>046_jpg.rf.76f88b64402215cc443ed5cde0e097f2.jpg</t>
+  </si>
+  <si>
+    <t>047_jpg.rf.6a632fd4b65280f5d73a840a623469ea.jpg</t>
+  </si>
+  <si>
+    <t>048_jpg.rf.bf3293ace23a9a7192c3fd3f36901326.jpg</t>
+  </si>
+  <si>
+    <t>049_jpg.rf.7897e5c4b008ac17dda52677eb16b205.jpg</t>
+  </si>
+  <si>
+    <t>050_jpg.rf.4958636e3e2fe16c23221882cbfdb04d.jpg</t>
+  </si>
+  <si>
+    <t>051_jpg.rf.118bab4a6988aee4201a5fea725f651f.jpg</t>
+  </si>
+  <si>
+    <t>052_jpg.rf.e73b115cdceaf7c86dad1611452102c0.jpg</t>
+  </si>
+  <si>
+    <t>054_jpg.rf.1120f4cec7153f33539442a19696cbc3.jpg</t>
+  </si>
+  <si>
+    <t>055_jpg.rf.9403ef7ae724ecc778852c7968e2eb87.jpg</t>
+  </si>
+  <si>
+    <t>056_jpg.rf.7fa989e1d469f5c2b2619b20bb44876f.jpg</t>
+  </si>
+  <si>
+    <t>057_jpg.rf.6317f9fbb5ade3115ac57c42351159ae.jpg</t>
   </si>
   <si>
     <t>Train_or_Test</t>
@@ -303,18 +303,18 @@
   <dimension ref="A1:L55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="44.6640625" customWidth="true"/>
-    <col min="2" max="2" width="12.33203125" customWidth="true"/>
-    <col min="3" max="3" width="11.88671875" customWidth="true"/>
-    <col min="4" max="4" width="13.109375" customWidth="true"/>
-    <col min="5" max="5" width="13.109375" customWidth="true"/>
-    <col min="6" max="6" width="13.21875" customWidth="true"/>
-    <col min="7" max="7" width="13.109375" customWidth="true"/>
-    <col min="8" max="8" width="15.109375" customWidth="true"/>
-    <col min="9" max="9" width="18.44140625" customWidth="true"/>
-    <col min="10" max="10" width="19.109375" customWidth="true"/>
-    <col min="11" max="11" width="9" customWidth="true"/>
-    <col min="12" max="12" width="5" customWidth="true"/>
+    <col min="1" max="1" width="46.85546875" customWidth="true"/>
+    <col min="2" max="2" width="13.140625" customWidth="true"/>
+    <col min="3" max="3" width="13.42578125" customWidth="true"/>
+    <col min="4" max="4" width="14.7109375" customWidth="true"/>
+    <col min="5" max="5" width="14.7109375" customWidth="true"/>
+    <col min="6" max="6" width="14.42578125" customWidth="true"/>
+    <col min="7" max="7" width="14.7109375" customWidth="true"/>
+    <col min="8" max="8" width="17" customWidth="true"/>
+    <col min="9" max="9" width="20.5703125" customWidth="true"/>
+    <col min="10" max="10" width="21.5703125" customWidth="true"/>
+    <col min="11" max="11" width="10.28515625" customWidth="true"/>
+    <col min="12" max="12" width="5.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -369,22 +369,22 @@
         <v>23</v>
       </c>
       <c r="E2" s="0">
-        <v>21.999107328227829</v>
+        <v>19.256509021241985</v>
       </c>
       <c r="F2" s="0">
-        <v>-1.0008926717721707</v>
+        <v>-3.7434909787580146</v>
       </c>
       <c r="G2" s="0">
-        <v>1.0008926717721707</v>
+        <v>3.7434909787580146</v>
       </c>
       <c r="H2" s="0">
-        <v>21.499107328227829</v>
+        <v>18.756509021241985</v>
       </c>
       <c r="I2" s="0">
-        <v>-1.5008926717721707</v>
+        <v>-4.2434909787580146</v>
       </c>
       <c r="J2" s="0">
-        <v>1.5008926717721707</v>
+        <v>4.2434909787580146</v>
       </c>
       <c r="K2" s="0" t="b">
         <v>0</v>
@@ -401,28 +401,28 @@
         <v>56</v>
       </c>
       <c r="C3" s="0">
-        <v>202.4933</v>
+        <v>202.364</v>
       </c>
       <c r="D3" s="0">
         <v>21</v>
       </c>
       <c r="E3" s="0">
-        <v>19.776981551893531</v>
+        <v>19.791564548921183</v>
       </c>
       <c r="F3" s="0">
-        <v>-1.223018448106469</v>
+        <v>-1.2084354510788167</v>
       </c>
       <c r="G3" s="0">
-        <v>1.223018448106469</v>
+        <v>1.2084354510788167</v>
       </c>
       <c r="H3" s="0">
-        <v>19.276981551893531</v>
+        <v>19.291564548921183</v>
       </c>
       <c r="I3" s="0">
-        <v>-1.723018448106469</v>
+        <v>-1.7084354510788167</v>
       </c>
       <c r="J3" s="0">
-        <v>1.723018448106469</v>
+        <v>1.7084354510788167</v>
       </c>
       <c r="K3" s="0" t="b">
         <v>0</v>
@@ -439,28 +439,28 @@
         <v>56</v>
       </c>
       <c r="C4" s="0">
-        <v>246.57509999999999</v>
+        <v>246.57499999999999</v>
       </c>
       <c r="D4" s="0">
         <v>23.5</v>
       </c>
       <c r="E4" s="0">
-        <v>21.363793534425252</v>
+        <v>22.834174027314667</v>
       </c>
       <c r="F4" s="0">
-        <v>-2.1362064655747481</v>
+        <v>-0.66582597268533306</v>
       </c>
       <c r="G4" s="0">
-        <v>2.1362064655747481</v>
+        <v>0.66582597268533306</v>
       </c>
       <c r="H4" s="0">
-        <v>20.863793534425252</v>
+        <v>22.334174027314667</v>
       </c>
       <c r="I4" s="0">
-        <v>-2.6362064655747481</v>
+        <v>-1.1658259726853331</v>
       </c>
       <c r="J4" s="0">
-        <v>2.6362064655747481</v>
+        <v>1.1658259726853331</v>
       </c>
       <c r="K4" s="0" t="b">
         <v>0</v>
@@ -477,28 +477,28 @@
         <v>56</v>
       </c>
       <c r="C5" s="0">
-        <v>196.19069999999999</v>
+        <v>196.19049999999999</v>
       </c>
       <c r="D5" s="0">
         <v>21</v>
       </c>
       <c r="E5" s="0">
-        <v>20.186188863331534</v>
+        <v>20.876133095140798</v>
       </c>
       <c r="F5" s="0">
-        <v>-0.81381113666846616</v>
+        <v>-0.12386690485920226</v>
       </c>
       <c r="G5" s="0">
-        <v>0.81381113666846616</v>
+        <v>0.12386690485920226</v>
       </c>
       <c r="H5" s="0">
-        <v>19.686188863331534</v>
+        <v>20.376133095140798</v>
       </c>
       <c r="I5" s="0">
-        <v>-1.3138111366684662</v>
+        <v>-0.62386690485920227</v>
       </c>
       <c r="J5" s="0">
-        <v>1.3138111366684662</v>
+        <v>0.62386690485920227</v>
       </c>
       <c r="K5" s="0" t="b">
         <v>0</v>
@@ -521,22 +521,22 @@
         <v>21.5</v>
       </c>
       <c r="E6" s="0">
-        <v>20.931050102647845</v>
+        <v>20.253685437691527</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.56894989735215518</v>
+        <v>-1.2463145623084735</v>
       </c>
       <c r="G6" s="0">
-        <v>0.56894989735215518</v>
+        <v>1.2463145623084735</v>
       </c>
       <c r="H6" s="0">
-        <v>20.431050102647845</v>
+        <v>19.753685437691527</v>
       </c>
       <c r="I6" s="0">
-        <v>-1.0689498973521552</v>
+        <v>-1.7463145623084735</v>
       </c>
       <c r="J6" s="0">
-        <v>1.0689498973521552</v>
+        <v>1.7463145623084735</v>
       </c>
       <c r="K6" s="0" t="b">
         <v>0</v>
@@ -553,28 +553,28 @@
         <v>56</v>
       </c>
       <c r="C7" s="0">
-        <v>248.35339999999999</v>
+        <v>248.34049999999999</v>
       </c>
       <c r="D7" s="0">
         <v>22</v>
       </c>
       <c r="E7" s="0">
-        <v>23.081272631069048</v>
+        <v>22.883750936856757</v>
       </c>
       <c r="F7" s="0">
-        <v>1.0812726310690479</v>
+        <v>0.88375093685675665</v>
       </c>
       <c r="G7" s="0">
-        <v>1.0812726310690479</v>
+        <v>0.88375093685675665</v>
       </c>
       <c r="H7" s="0">
-        <v>22.581272631069048</v>
+        <v>22.383750936856757</v>
       </c>
       <c r="I7" s="0">
-        <v>0.58127263106904792</v>
+        <v>0.38375093685675665</v>
       </c>
       <c r="J7" s="0">
-        <v>0.58127263106904792</v>
+        <v>0.38375093685675665</v>
       </c>
       <c r="K7" s="0" t="b">
         <v>1</v>
@@ -591,28 +591,28 @@
         <v>56</v>
       </c>
       <c r="C8" s="0">
-        <v>252.0284</v>
+        <v>254.0164</v>
       </c>
       <c r="D8" s="0">
         <v>25</v>
       </c>
       <c r="E8" s="0">
-        <v>21.940962053723673</v>
+        <v>21.620917228525357</v>
       </c>
       <c r="F8" s="0">
-        <v>-3.0590379462763266</v>
+        <v>-3.3790827714746428</v>
       </c>
       <c r="G8" s="0">
-        <v>3.0590379462763266</v>
+        <v>3.3790827714746428</v>
       </c>
       <c r="H8" s="0">
-        <v>21.440962053723673</v>
+        <v>21.120917228525357</v>
       </c>
       <c r="I8" s="0">
-        <v>-3.5590379462763266</v>
+        <v>-3.8790827714746428</v>
       </c>
       <c r="J8" s="0">
-        <v>3.5590379462763266</v>
+        <v>3.8790827714746428</v>
       </c>
       <c r="K8" s="0" t="b">
         <v>0</v>
@@ -635,22 +635,22 @@
         <v>20.5</v>
       </c>
       <c r="E9" s="0">
-        <v>22.99914808312565</v>
+        <v>23.566772455726461</v>
       </c>
       <c r="F9" s="0">
-        <v>2.4991480831256503</v>
+        <v>3.0667724557264613</v>
       </c>
       <c r="G9" s="0">
-        <v>2.4991480831256503</v>
+        <v>3.0667724557264613</v>
       </c>
       <c r="H9" s="0">
-        <v>22.49914808312565</v>
+        <v>23.066772455726461</v>
       </c>
       <c r="I9" s="0">
-        <v>1.9991480831256503</v>
+        <v>2.5667724557264613</v>
       </c>
       <c r="J9" s="0">
-        <v>1.9991480831256503</v>
+        <v>2.5667724557264613</v>
       </c>
       <c r="K9" s="0" t="b">
         <v>1</v>
@@ -667,28 +667,28 @@
         <v>56</v>
       </c>
       <c r="C10" s="0">
-        <v>108.35720000000001</v>
+        <v>108.35639999999999</v>
       </c>
       <c r="D10" s="0">
         <v>21</v>
       </c>
       <c r="E10" s="0">
-        <v>19.938530598075321</v>
+        <v>20.371173236816599</v>
       </c>
       <c r="F10" s="0">
-        <v>-1.0614694019246791</v>
+        <v>-0.62882676318340103</v>
       </c>
       <c r="G10" s="0">
-        <v>1.0614694019246791</v>
+        <v>0.62882676318340103</v>
       </c>
       <c r="H10" s="0">
-        <v>19.438530598075321</v>
+        <v>19.871173236816599</v>
       </c>
       <c r="I10" s="0">
-        <v>-1.5614694019246791</v>
+        <v>-1.128826763183401</v>
       </c>
       <c r="J10" s="0">
-        <v>1.5614694019246791</v>
+        <v>1.128826763183401</v>
       </c>
       <c r="K10" s="0" t="b">
         <v>0</v>
@@ -711,22 +711,22 @@
         <v>18</v>
       </c>
       <c r="E11" s="0">
-        <v>21.139223361952549</v>
+        <v>21.856834144450971</v>
       </c>
       <c r="F11" s="0">
-        <v>3.1392233619525491</v>
+        <v>3.8568341444509713</v>
       </c>
       <c r="G11" s="0">
-        <v>3.1392233619525491</v>
+        <v>3.8568341444509713</v>
       </c>
       <c r="H11" s="0">
-        <v>20.639223361952549</v>
+        <v>21.356834144450971</v>
       </c>
       <c r="I11" s="0">
-        <v>2.6392233619525491</v>
+        <v>3.3568341444509713</v>
       </c>
       <c r="J11" s="0">
-        <v>2.6392233619525491</v>
+        <v>3.3568341444509713</v>
       </c>
       <c r="K11" s="0" t="b">
         <v>1</v>
@@ -743,28 +743,28 @@
         <v>56</v>
       </c>
       <c r="C12" s="0">
-        <v>246.73050000000001</v>
+        <v>246.73159999999999</v>
       </c>
       <c r="D12" s="0">
         <v>25</v>
       </c>
       <c r="E12" s="0">
-        <v>21.340781093975799</v>
+        <v>22.096610047511053</v>
       </c>
       <c r="F12" s="0">
-        <v>-3.6592189060242006</v>
+        <v>-2.9033899524889471</v>
       </c>
       <c r="G12" s="0">
-        <v>3.6592189060242006</v>
+        <v>2.9033899524889471</v>
       </c>
       <c r="H12" s="0">
-        <v>20.840781093975799</v>
+        <v>21.596610047511053</v>
       </c>
       <c r="I12" s="0">
-        <v>-4.1592189060242006</v>
+        <v>-3.4033899524889471</v>
       </c>
       <c r="J12" s="0">
-        <v>4.1592189060242006</v>
+        <v>3.4033899524889471</v>
       </c>
       <c r="K12" s="0" t="b">
         <v>0</v>
@@ -781,28 +781,28 @@
         <v>56</v>
       </c>
       <c r="C13" s="0">
-        <v>217.12360000000001</v>
+        <v>217.1414</v>
       </c>
       <c r="D13" s="0">
         <v>22.5</v>
       </c>
       <c r="E13" s="0">
-        <v>20.978049923231478</v>
+        <v>20.526794291470562</v>
       </c>
       <c r="F13" s="0">
-        <v>-1.5219500767685226</v>
+        <v>-1.9732057085294379</v>
       </c>
       <c r="G13" s="0">
-        <v>1.5219500767685226</v>
+        <v>1.9732057085294379</v>
       </c>
       <c r="H13" s="0">
-        <v>20.478049923231478</v>
+        <v>20.026794291470562</v>
       </c>
       <c r="I13" s="0">
-        <v>-2.0219500767685226</v>
+        <v>-2.4732057085294379</v>
       </c>
       <c r="J13" s="0">
-        <v>2.0219500767685226</v>
+        <v>2.4732057085294379</v>
       </c>
       <c r="K13" s="0" t="b">
         <v>0</v>
@@ -819,28 +819,28 @@
         <v>56</v>
       </c>
       <c r="C14" s="0">
-        <v>228.24799999999999</v>
+        <v>228.28899999999999</v>
       </c>
       <c r="D14" s="0">
         <v>20.5</v>
       </c>
       <c r="E14" s="0">
-        <v>21.092127046570496</v>
+        <v>21.148813206690633</v>
       </c>
       <c r="F14" s="0">
-        <v>0.59212704657049642</v>
+        <v>0.64881320669063314</v>
       </c>
       <c r="G14" s="0">
-        <v>0.59212704657049642</v>
+        <v>0.64881320669063314</v>
       </c>
       <c r="H14" s="0">
-        <v>20.592127046570496</v>
+        <v>20.648813206690633</v>
       </c>
       <c r="I14" s="0">
-        <v>0.092127046570496418</v>
+        <v>0.14881320669063314</v>
       </c>
       <c r="J14" s="0">
-        <v>0.092127046570496418</v>
+        <v>0.14881320669063314</v>
       </c>
       <c r="K14" s="0" t="b">
         <v>1</v>
@@ -863,22 +863,22 @@
         <v>19.5</v>
       </c>
       <c r="E15" s="0">
-        <v>20.197647486641834</v>
+        <v>20.884502364735358</v>
       </c>
       <c r="F15" s="0">
-        <v>0.69764748664183429</v>
+        <v>1.3845023647353578</v>
       </c>
       <c r="G15" s="0">
-        <v>0.69764748664183429</v>
+        <v>1.3845023647353578</v>
       </c>
       <c r="H15" s="0">
-        <v>19.697647486641834</v>
+        <v>20.384502364735358</v>
       </c>
       <c r="I15" s="0">
-        <v>0.19764748664183429</v>
+        <v>0.88450236473535782</v>
       </c>
       <c r="J15" s="0">
-        <v>0.19764748664183429</v>
+        <v>0.88450236473535782</v>
       </c>
       <c r="K15" s="0" t="b">
         <v>1</v>
@@ -895,28 +895,28 @@
         <v>56</v>
       </c>
       <c r="C16" s="0">
-        <v>208.5238</v>
+        <v>208.52420000000001</v>
       </c>
       <c r="D16" s="0">
         <v>19.5</v>
       </c>
       <c r="E16" s="0">
-        <v>19.980930475594946</v>
+        <v>19.983398347107151</v>
       </c>
       <c r="F16" s="0">
-        <v>0.48093047559494551</v>
+        <v>0.48339834710715124</v>
       </c>
       <c r="G16" s="0">
-        <v>0.48093047559494551</v>
+        <v>0.48339834710715124</v>
       </c>
       <c r="H16" s="0">
-        <v>19.480930475594946</v>
+        <v>19.483398347107151</v>
       </c>
       <c r="I16" s="0">
-        <v>-0.019069524405054494</v>
+        <v>-0.016601652892848762</v>
       </c>
       <c r="J16" s="0">
-        <v>0.019069524405054494</v>
+        <v>0.016601652892848762</v>
       </c>
       <c r="K16" s="0" t="b">
         <v>0</v>
@@ -939,22 +939,22 @@
         <v>18.5</v>
       </c>
       <c r="E17" s="0">
-        <v>18.02480005119472</v>
+        <v>18.263979023324616</v>
       </c>
       <c r="F17" s="0">
-        <v>-0.4751999488052796</v>
+        <v>-0.23602097667538402</v>
       </c>
       <c r="G17" s="0">
-        <v>0.4751999488052796</v>
+        <v>0.23602097667538402</v>
       </c>
       <c r="H17" s="0">
-        <v>17.52480005119472</v>
+        <v>17.763979023324616</v>
       </c>
       <c r="I17" s="0">
-        <v>-0.9751999488052796</v>
+        <v>-0.73602097667538402</v>
       </c>
       <c r="J17" s="0">
-        <v>0.9751999488052796</v>
+        <v>0.73602097667538402</v>
       </c>
       <c r="K17" s="0" t="b">
         <v>0</v>
@@ -971,28 +971,28 @@
         <v>56</v>
       </c>
       <c r="C18" s="0">
-        <v>122.82769999999999</v>
+        <v>122.8275</v>
       </c>
       <c r="D18" s="0">
         <v>23.75</v>
       </c>
       <c r="E18" s="0">
-        <v>20.01748381978075</v>
+        <v>21.982286956214647</v>
       </c>
       <c r="F18" s="0">
-        <v>-3.7325161802192497</v>
+        <v>-1.7677130437853528</v>
       </c>
       <c r="G18" s="0">
-        <v>3.7325161802192497</v>
+        <v>1.7677130437853528</v>
       </c>
       <c r="H18" s="0">
-        <v>19.51748381978075</v>
+        <v>21.482286956214647</v>
       </c>
       <c r="I18" s="0">
-        <v>-4.2325161802192497</v>
+        <v>-2.2677130437853528</v>
       </c>
       <c r="J18" s="0">
-        <v>4.2325161802192497</v>
+        <v>2.2677130437853528</v>
       </c>
       <c r="K18" s="0" t="b">
         <v>0</v>
@@ -1009,28 +1009,28 @@
         <v>56</v>
       </c>
       <c r="C19" s="0">
-        <v>225.06450000000001</v>
+        <v>225.01329999999999</v>
       </c>
       <c r="D19" s="0">
         <v>22.25</v>
       </c>
       <c r="E19" s="0">
-        <v>21.295667519802794</v>
+        <v>20.930617251448268</v>
       </c>
       <c r="F19" s="0">
-        <v>-0.95433248019720551</v>
+        <v>-1.3193827485517318</v>
       </c>
       <c r="G19" s="0">
-        <v>0.95433248019720551</v>
+        <v>1.3193827485517318</v>
       </c>
       <c r="H19" s="0">
-        <v>20.795667519802794</v>
+        <v>20.430617251448268</v>
       </c>
       <c r="I19" s="0">
-        <v>-1.4543324801972055</v>
+        <v>-1.8193827485517318</v>
       </c>
       <c r="J19" s="0">
-        <v>1.4543324801972055</v>
+        <v>1.8193827485517318</v>
       </c>
       <c r="K19" s="0" t="b">
         <v>0</v>
@@ -1047,28 +1047,28 @@
         <v>56</v>
       </c>
       <c r="C20" s="0">
-        <v>257.20510000000002</v>
+        <v>257.21010000000001</v>
       </c>
       <c r="D20" s="0">
         <v>25.5</v>
       </c>
       <c r="E20" s="0">
-        <v>21.496023629275136</v>
+        <v>22.647153745857921</v>
       </c>
       <c r="F20" s="0">
-        <v>-4.0039763707248639</v>
+        <v>-2.8528462541420794</v>
       </c>
       <c r="G20" s="0">
-        <v>4.0039763707248639</v>
+        <v>2.8528462541420794</v>
       </c>
       <c r="H20" s="0">
-        <v>20.996023629275136</v>
+        <v>22.147153745857921</v>
       </c>
       <c r="I20" s="0">
-        <v>-4.5039763707248639</v>
+        <v>-3.3528462541420794</v>
       </c>
       <c r="J20" s="0">
-        <v>4.5039763707248639</v>
+        <v>3.3528462541420794</v>
       </c>
       <c r="K20" s="0" t="b">
         <v>0</v>
@@ -1085,28 +1085,28 @@
         <v>56</v>
       </c>
       <c r="C21" s="0">
-        <v>267.51420000000002</v>
+        <v>267.51400000000001</v>
       </c>
       <c r="D21" s="0">
         <v>22.5</v>
       </c>
       <c r="E21" s="0">
-        <v>23.568502663981246</v>
+        <v>23.592808572515491</v>
       </c>
       <c r="F21" s="0">
-        <v>1.0685026639812456</v>
+        <v>1.0928085725154908</v>
       </c>
       <c r="G21" s="0">
-        <v>1.0685026639812456</v>
+        <v>1.0928085725154908</v>
       </c>
       <c r="H21" s="0">
-        <v>23.068502663981246</v>
+        <v>23.092808572515491</v>
       </c>
       <c r="I21" s="0">
-        <v>0.5685026639812456</v>
+        <v>0.5928085725154908</v>
       </c>
       <c r="J21" s="0">
-        <v>0.5685026639812456</v>
+        <v>0.5928085725154908</v>
       </c>
       <c r="K21" s="0" t="b">
         <v>1</v>
@@ -1123,28 +1123,28 @@
         <v>56</v>
       </c>
       <c r="C22" s="0">
-        <v>206.54310000000001</v>
+        <v>206.51310000000001</v>
       </c>
       <c r="D22" s="0">
         <v>21.5</v>
       </c>
       <c r="E22" s="0">
-        <v>20.390724184103235</v>
+        <v>20.995000481751386</v>
       </c>
       <c r="F22" s="0">
-        <v>-1.1092758158967655</v>
+        <v>-0.50499951824861356</v>
       </c>
       <c r="G22" s="0">
-        <v>1.1092758158967655</v>
+        <v>0.50499951824861356</v>
       </c>
       <c r="H22" s="0">
-        <v>19.890724184103235</v>
+        <v>20.495000481751386</v>
       </c>
       <c r="I22" s="0">
-        <v>-1.6092758158967655</v>
+        <v>-1.0049995182486136</v>
       </c>
       <c r="J22" s="0">
-        <v>1.6092758158967655</v>
+        <v>1.0049995182486136</v>
       </c>
       <c r="K22" s="0" t="b">
         <v>0</v>
@@ -1161,28 +1161,28 @@
         <v>56</v>
       </c>
       <c r="C23" s="0">
-        <v>224.2312</v>
+        <v>224.2311</v>
       </c>
       <c r="D23" s="0">
         <v>20</v>
       </c>
       <c r="E23" s="0">
-        <v>21.287683950758982</v>
+        <v>20.856923169731644</v>
       </c>
       <c r="F23" s="0">
-        <v>1.2876839507589821</v>
+        <v>0.85692316973164395</v>
       </c>
       <c r="G23" s="0">
-        <v>1.2876839507589821</v>
+        <v>0.85692316973164395</v>
       </c>
       <c r="H23" s="0">
-        <v>20.787683950758982</v>
+        <v>20.356923169731644</v>
       </c>
       <c r="I23" s="0">
-        <v>0.78768395075898212</v>
+        <v>0.35692316973164395</v>
       </c>
       <c r="J23" s="0">
-        <v>0.78768395075898212</v>
+        <v>0.35692316973164395</v>
       </c>
       <c r="K23" s="0" t="b">
         <v>1</v>
@@ -1199,31 +1199,31 @@
         <v>56</v>
       </c>
       <c r="C24" s="0">
-        <v>198.60169999999999</v>
+        <v>198.6028</v>
       </c>
       <c r="D24" s="0">
         <v>19.5</v>
       </c>
       <c r="E24" s="0">
-        <v>21.042056395918579</v>
+        <v>19.844135128022451</v>
       </c>
       <c r="F24" s="0">
-        <v>1.5420563959185785</v>
+        <v>0.34413512802245094</v>
       </c>
       <c r="G24" s="0">
-        <v>1.5420563959185785</v>
+        <v>0.34413512802245094</v>
       </c>
       <c r="H24" s="0">
-        <v>20.542056395918579</v>
+        <v>19.344135128022451</v>
       </c>
       <c r="I24" s="0">
-        <v>1.0420563959185785</v>
+        <v>-0.15586487197754906</v>
       </c>
       <c r="J24" s="0">
-        <v>1.0420563959185785</v>
+        <v>0.15586487197754906</v>
       </c>
       <c r="K24" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="0">
         <v>1</v>
@@ -1237,28 +1237,28 @@
         <v>56</v>
       </c>
       <c r="C25" s="0">
-        <v>195.74289999999999</v>
+        <v>195.7431</v>
       </c>
       <c r="D25" s="0">
         <v>18.5</v>
       </c>
       <c r="E25" s="0">
-        <v>20.835090168188007</v>
+        <v>19.982662312777379</v>
       </c>
       <c r="F25" s="0">
-        <v>2.3350901681880067</v>
+        <v>1.4826623127773786</v>
       </c>
       <c r="G25" s="0">
-        <v>2.3350901681880067</v>
+        <v>1.4826623127773786</v>
       </c>
       <c r="H25" s="0">
-        <v>20.335090168188007</v>
+        <v>19.482662312777379</v>
       </c>
       <c r="I25" s="0">
-        <v>1.8350901681880067</v>
+        <v>0.98266231277737859</v>
       </c>
       <c r="J25" s="0">
-        <v>1.8350901681880067</v>
+        <v>0.98266231277737859</v>
       </c>
       <c r="K25" s="0" t="b">
         <v>1</v>
@@ -1275,28 +1275,28 @@
         <v>56</v>
       </c>
       <c r="C26" s="0">
-        <v>201.5384</v>
+        <v>201.52019999999999</v>
       </c>
       <c r="D26" s="0">
         <v>17.5</v>
       </c>
       <c r="E26" s="0">
-        <v>20.863933052565219</v>
+        <v>20.011519810330988</v>
       </c>
       <c r="F26" s="0">
-        <v>3.3639330525652191</v>
+        <v>2.5115198103309879</v>
       </c>
       <c r="G26" s="0">
-        <v>3.3639330525652191</v>
+        <v>2.5115198103309879</v>
       </c>
       <c r="H26" s="0">
-        <v>20.363933052565219</v>
+        <v>19.511519810330988</v>
       </c>
       <c r="I26" s="0">
-        <v>2.8639330525652191</v>
+        <v>2.0115198103309879</v>
       </c>
       <c r="J26" s="0">
-        <v>2.8639330525652191</v>
+        <v>2.0115198103309879</v>
       </c>
       <c r="K26" s="0" t="b">
         <v>1</v>
@@ -1313,28 +1313,28 @@
         <v>56</v>
       </c>
       <c r="C27" s="0">
-        <v>230.2414</v>
+        <v>230.24180000000001</v>
       </c>
       <c r="D27" s="0">
         <v>21.25</v>
       </c>
       <c r="E27" s="0">
-        <v>21.115411716360001</v>
+        <v>21.264505967557486</v>
       </c>
       <c r="F27" s="0">
-        <v>-0.13458828363999942</v>
+        <v>0.014505967557486343</v>
       </c>
       <c r="G27" s="0">
-        <v>0.13458828363999942</v>
+        <v>0.014505967557486343</v>
       </c>
       <c r="H27" s="0">
-        <v>20.615411716360001</v>
+        <v>20.764505967557486</v>
       </c>
       <c r="I27" s="0">
-        <v>-0.63458828363999942</v>
+        <v>-0.48549403244251366</v>
       </c>
       <c r="J27" s="0">
-        <v>0.63458828363999942</v>
+        <v>0.48549403244251366</v>
       </c>
       <c r="K27" s="0" t="b">
         <v>0</v>
@@ -1351,28 +1351,28 @@
         <v>56</v>
       </c>
       <c r="C28" s="0">
-        <v>210.9821</v>
+        <v>210.9819</v>
       </c>
       <c r="D28" s="0">
         <v>19.25</v>
       </c>
       <c r="E28" s="0">
-        <v>20.100410455154197</v>
+        <v>20.099519928983529</v>
       </c>
       <c r="F28" s="0">
-        <v>0.85041045515419711</v>
+        <v>0.84951992898352913</v>
       </c>
       <c r="G28" s="0">
-        <v>0.85041045515419711</v>
+        <v>0.84951992898352913</v>
       </c>
       <c r="H28" s="0">
-        <v>19.600410455154197</v>
+        <v>19.599519928983529</v>
       </c>
       <c r="I28" s="0">
-        <v>0.35041045515419711</v>
+        <v>0.34951992898352913</v>
       </c>
       <c r="J28" s="0">
-        <v>0.35041045515419711</v>
+        <v>0.34951992898352913</v>
       </c>
       <c r="K28" s="0" t="b">
         <v>1</v>
@@ -1395,22 +1395,22 @@
         <v>21.75</v>
       </c>
       <c r="E29" s="0">
-        <v>21.338451874065342</v>
+        <v>21.375762401209496</v>
       </c>
       <c r="F29" s="0">
-        <v>-0.41154812593465806</v>
+        <v>-0.37423759879050422</v>
       </c>
       <c r="G29" s="0">
-        <v>0.41154812593465806</v>
+        <v>0.37423759879050422</v>
       </c>
       <c r="H29" s="0">
-        <v>20.838451874065342</v>
+        <v>20.875762401209496</v>
       </c>
       <c r="I29" s="0">
-        <v>-0.91154812593465806</v>
+        <v>-0.87423759879050422</v>
       </c>
       <c r="J29" s="0">
-        <v>0.91154812593465806</v>
+        <v>0.87423759879050422</v>
       </c>
       <c r="K29" s="0" t="b">
         <v>0</v>
@@ -1427,28 +1427,28 @@
         <v>56</v>
       </c>
       <c r="C30" s="0">
-        <v>267.35820000000001</v>
+        <v>267.358</v>
       </c>
       <c r="D30" s="0">
         <v>20.75</v>
       </c>
       <c r="E30" s="0">
-        <v>23.569401079731229</v>
+        <v>23.590141187034799</v>
       </c>
       <c r="F30" s="0">
-        <v>2.8194010797312288</v>
+        <v>2.8401411870347992</v>
       </c>
       <c r="G30" s="0">
-        <v>2.8194010797312288</v>
+        <v>2.8401411870347992</v>
       </c>
       <c r="H30" s="0">
-        <v>23.069401079731229</v>
+        <v>23.090141187034799</v>
       </c>
       <c r="I30" s="0">
-        <v>2.3194010797312288</v>
+        <v>2.3401411870347992</v>
       </c>
       <c r="J30" s="0">
-        <v>2.3194010797312288</v>
+        <v>2.3401411870347992</v>
       </c>
       <c r="K30" s="0" t="b">
         <v>1</v>
@@ -1465,28 +1465,28 @@
         <v>56</v>
       </c>
       <c r="C31" s="0">
-        <v>231.851</v>
+        <v>231.82570000000001</v>
       </c>
       <c r="D31" s="0">
         <v>21.5</v>
       </c>
       <c r="E31" s="0">
-        <v>21.745317939877012</v>
+        <v>21.660476259905586</v>
       </c>
       <c r="F31" s="0">
-        <v>0.24531793987701178</v>
+        <v>0.16047625990558601</v>
       </c>
       <c r="G31" s="0">
-        <v>0.24531793987701178</v>
+        <v>0.16047625990558601</v>
       </c>
       <c r="H31" s="0">
-        <v>21.245317939877012</v>
+        <v>21.160476259905586</v>
       </c>
       <c r="I31" s="0">
-        <v>-0.25468206012298822</v>
+        <v>-0.339523740094414</v>
       </c>
       <c r="J31" s="0">
-        <v>0.25468206012298822</v>
+        <v>0.339523740094414</v>
       </c>
       <c r="K31" s="0" t="b">
         <v>0</v>
@@ -1503,31 +1503,31 @@
         <v>56</v>
       </c>
       <c r="C32" s="0">
-        <v>115.20050000000001</v>
+        <v>115.2003</v>
       </c>
       <c r="D32" s="0">
         <v>19.5</v>
       </c>
       <c r="E32" s="0">
-        <v>19.973727228638794</v>
+        <v>21.242264850205764</v>
       </c>
       <c r="F32" s="0">
-        <v>0.47372722863879346</v>
+        <v>1.7422648502057641</v>
       </c>
       <c r="G32" s="0">
-        <v>0.47372722863879346</v>
+        <v>1.7422648502057641</v>
       </c>
       <c r="H32" s="0">
-        <v>19.473727228638794</v>
+        <v>20.742264850205764</v>
       </c>
       <c r="I32" s="0">
-        <v>-0.026272771361206537</v>
+        <v>1.242264850205764</v>
       </c>
       <c r="J32" s="0">
-        <v>0.026272771361206537</v>
+        <v>1.242264850205764</v>
       </c>
       <c r="K32" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="0">
         <v>4</v>
@@ -1547,22 +1547,22 @@
         <v>19.5</v>
       </c>
       <c r="E33" s="0">
-        <v>20.249226530501588</v>
+        <v>21.341796549116605</v>
       </c>
       <c r="F33" s="0">
-        <v>0.74922653050158772</v>
+        <v>1.8417965491166051</v>
       </c>
       <c r="G33" s="0">
-        <v>0.74922653050158772</v>
+        <v>1.8417965491166051</v>
       </c>
       <c r="H33" s="0">
-        <v>19.749226530501588</v>
+        <v>20.841796549116605</v>
       </c>
       <c r="I33" s="0">
-        <v>0.24922653050158772</v>
+        <v>1.3417965491166051</v>
       </c>
       <c r="J33" s="0">
-        <v>0.24922653050158772</v>
+        <v>1.3417965491166051</v>
       </c>
       <c r="K33" s="0" t="b">
         <v>1</v>
@@ -1579,28 +1579,28 @@
         <v>56</v>
       </c>
       <c r="C34" s="0">
-        <v>114.13679999999999</v>
+        <v>114.13630000000001</v>
       </c>
       <c r="D34" s="0">
         <v>21</v>
       </c>
       <c r="E34" s="0">
-        <v>20.251386587531567</v>
+        <v>21.375751794862214</v>
       </c>
       <c r="F34" s="0">
-        <v>-0.74861341246843338</v>
+        <v>0.37575179486221444</v>
       </c>
       <c r="G34" s="0">
-        <v>0.74861341246843338</v>
+        <v>0.37575179486221444</v>
       </c>
       <c r="H34" s="0">
-        <v>19.751386587531567</v>
+        <v>20.875751794862214</v>
       </c>
       <c r="I34" s="0">
-        <v>-1.2486134124684334</v>
+        <v>-0.12424820513778556</v>
       </c>
       <c r="J34" s="0">
-        <v>1.2486134124684334</v>
+        <v>0.12424820513778556</v>
       </c>
       <c r="K34" s="0" t="b">
         <v>0</v>
@@ -1617,31 +1617,31 @@
         <v>56</v>
       </c>
       <c r="C35" s="0">
-        <v>200.9769</v>
+        <v>200.97659999999999</v>
       </c>
       <c r="D35" s="0">
         <v>20.25</v>
       </c>
       <c r="E35" s="0">
-        <v>21.064799978961261</v>
+        <v>19.79932258512078</v>
       </c>
       <c r="F35" s="0">
-        <v>0.81479997896126122</v>
+        <v>-0.45067741487921964</v>
       </c>
       <c r="G35" s="0">
-        <v>0.81479997896126122</v>
+        <v>0.45067741487921964</v>
       </c>
       <c r="H35" s="0">
-        <v>20.564799978961261</v>
+        <v>19.29932258512078</v>
       </c>
       <c r="I35" s="0">
-        <v>0.31479997896126122</v>
+        <v>-0.95067741487921964</v>
       </c>
       <c r="J35" s="0">
-        <v>0.31479997896126122</v>
+        <v>0.95067741487921964</v>
       </c>
       <c r="K35" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="0">
         <v>1</v>
@@ -1655,28 +1655,28 @@
         <v>56</v>
       </c>
       <c r="C36" s="0">
-        <v>210.40799999999999</v>
+        <v>210.4085</v>
       </c>
       <c r="D36" s="0">
         <v>21.5</v>
       </c>
       <c r="E36" s="0">
-        <v>20.889224533465761</v>
+        <v>20.011672598326889</v>
       </c>
       <c r="F36" s="0">
-        <v>-0.61077546653423909</v>
+        <v>-1.4883274016731107</v>
       </c>
       <c r="G36" s="0">
-        <v>0.61077546653423909</v>
+        <v>1.4883274016731107</v>
       </c>
       <c r="H36" s="0">
-        <v>20.389224533465761</v>
+        <v>19.511672598326889</v>
       </c>
       <c r="I36" s="0">
-        <v>-1.1107754665342391</v>
+        <v>-1.9883274016731107</v>
       </c>
       <c r="J36" s="0">
-        <v>1.1107754665342391</v>
+        <v>1.9883274016731107</v>
       </c>
       <c r="K36" s="0" t="b">
         <v>0</v>
@@ -1693,28 +1693,28 @@
         <v>56</v>
       </c>
       <c r="C37" s="0">
-        <v>196.4297</v>
+        <v>196.4307</v>
       </c>
       <c r="D37" s="0">
         <v>19.5</v>
       </c>
       <c r="E37" s="0">
-        <v>20.189773060306699</v>
+        <v>20.878800480447247</v>
       </c>
       <c r="F37" s="0">
-        <v>0.68977306030669894</v>
+        <v>1.3788004804472465</v>
       </c>
       <c r="G37" s="0">
-        <v>0.68977306030669894</v>
+        <v>1.3788004804472465</v>
       </c>
       <c r="H37" s="0">
-        <v>19.689773060306699</v>
+        <v>20.378800480447247</v>
       </c>
       <c r="I37" s="0">
-        <v>0.18977306030669894</v>
+        <v>0.87880048044724646</v>
       </c>
       <c r="J37" s="0">
-        <v>0.18977306030669894</v>
+        <v>0.87880048044724646</v>
       </c>
       <c r="K37" s="0" t="b">
         <v>1</v>
@@ -1731,28 +1731,28 @@
         <v>56</v>
       </c>
       <c r="C38" s="0">
-        <v>246.28299999999999</v>
+        <v>246.28210000000001</v>
       </c>
       <c r="D38" s="0">
         <v>25</v>
       </c>
       <c r="E38" s="0">
-        <v>21.333895759852865</v>
+        <v>22.080282317222363</v>
       </c>
       <c r="F38" s="0">
-        <v>-3.6661042401471349</v>
+        <v>-2.9197176827776374</v>
       </c>
       <c r="G38" s="0">
-        <v>3.6661042401471349</v>
+        <v>2.9197176827776374</v>
       </c>
       <c r="H38" s="0">
-        <v>20.833895759852865</v>
+        <v>21.580282317222363</v>
       </c>
       <c r="I38" s="0">
-        <v>-4.1661042401471349</v>
+        <v>-3.4197176827776374</v>
       </c>
       <c r="J38" s="0">
-        <v>4.1661042401471349</v>
+        <v>3.4197176827776374</v>
       </c>
       <c r="K38" s="0" t="b">
         <v>0</v>
@@ -1769,28 +1769,28 @@
         <v>56</v>
       </c>
       <c r="C39" s="0">
-        <v>199.8417</v>
+        <v>199.84190000000001</v>
       </c>
       <c r="D39" s="0">
         <v>19</v>
       </c>
       <c r="E39" s="0">
-        <v>20.246813641920994</v>
+        <v>20.917200468595318</v>
       </c>
       <c r="F39" s="0">
-        <v>1.2468136419209941</v>
+        <v>1.9172004685953184</v>
       </c>
       <c r="G39" s="0">
-        <v>1.2468136419209941</v>
+        <v>1.9172004685953184</v>
       </c>
       <c r="H39" s="0">
-        <v>19.746813641920994</v>
+        <v>20.417200468595318</v>
       </c>
       <c r="I39" s="0">
-        <v>0.74681364192099409</v>
+        <v>1.4172004685953184</v>
       </c>
       <c r="J39" s="0">
-        <v>0.74681364192099409</v>
+        <v>1.4172004685953184</v>
       </c>
       <c r="K39" s="0" t="b">
         <v>1</v>
@@ -1807,28 +1807,28 @@
         <v>56</v>
       </c>
       <c r="C40" s="0">
-        <v>232.77719999999999</v>
+        <v>232.77090000000001</v>
       </c>
       <c r="D40" s="0">
         <v>19</v>
       </c>
       <c r="E40" s="0">
-        <v>21.184646472409455</v>
+        <v>22.173375625360215</v>
       </c>
       <c r="F40" s="0">
-        <v>2.1846464724094545</v>
+        <v>3.1733756253602152</v>
       </c>
       <c r="G40" s="0">
-        <v>2.1846464724094545</v>
+        <v>3.1733756253602152</v>
       </c>
       <c r="H40" s="0">
-        <v>20.684646472409455</v>
+        <v>21.673375625360215</v>
       </c>
       <c r="I40" s="0">
-        <v>1.6846464724094545</v>
+        <v>2.6733756253602152</v>
       </c>
       <c r="J40" s="0">
-        <v>1.6846464724094545</v>
+        <v>2.6733756253602152</v>
       </c>
       <c r="K40" s="0" t="b">
         <v>1</v>
@@ -1845,31 +1845,31 @@
         <v>56</v>
       </c>
       <c r="C41" s="0">
-        <v>162.56059999999999</v>
+        <v>162.53960000000001</v>
       </c>
       <c r="D41" s="0">
         <v>21</v>
       </c>
       <c r="E41" s="0">
-        <v>20.699116814111523</v>
+        <v>22.611817581912881</v>
       </c>
       <c r="F41" s="0">
-        <v>-0.30088318588847685</v>
+        <v>1.6118175819128808</v>
       </c>
       <c r="G41" s="0">
-        <v>0.30088318588847685</v>
+        <v>1.6118175819128808</v>
       </c>
       <c r="H41" s="0">
-        <v>20.199116814111523</v>
+        <v>22.111817581912881</v>
       </c>
       <c r="I41" s="0">
-        <v>-0.80088318588847685</v>
+        <v>1.1118175819128808</v>
       </c>
       <c r="J41" s="0">
-        <v>0.80088318588847685</v>
+        <v>1.1118175819128808</v>
       </c>
       <c r="K41" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="0">
         <v>1</v>
@@ -1883,28 +1883,28 @@
         <v>56</v>
       </c>
       <c r="C42" s="0">
-        <v>225.04929999999999</v>
+        <v>225.0488</v>
       </c>
       <c r="D42" s="0">
         <v>20.5</v>
       </c>
       <c r="E42" s="0">
-        <v>21.082401529312627</v>
+        <v>21.411828605020677</v>
       </c>
       <c r="F42" s="0">
-        <v>0.58240152931262656</v>
+        <v>0.91182860502067698</v>
       </c>
       <c r="G42" s="0">
-        <v>0.58240152931262656</v>
+        <v>0.91182860502067698</v>
       </c>
       <c r="H42" s="0">
-        <v>20.582401529312627</v>
+        <v>20.911828605020677</v>
       </c>
       <c r="I42" s="0">
-        <v>0.082401529312626565</v>
+        <v>0.41182860502067698</v>
       </c>
       <c r="J42" s="0">
-        <v>0.082401529312626565</v>
+        <v>0.41182860502067698</v>
       </c>
       <c r="K42" s="0" t="b">
         <v>1</v>
@@ -1921,28 +1921,28 @@
         <v>56</v>
       </c>
       <c r="C43" s="0">
-        <v>264.49709999999999</v>
+        <v>264.40339999999998</v>
       </c>
       <c r="D43" s="0">
         <v>19.25</v>
       </c>
       <c r="E43" s="0">
-        <v>21.671216003090478</v>
+        <v>23.340906313035056</v>
       </c>
       <c r="F43" s="0">
-        <v>2.4212160030904784</v>
+        <v>4.090906313035056</v>
       </c>
       <c r="G43" s="0">
-        <v>2.4212160030904784</v>
+        <v>4.090906313035056</v>
       </c>
       <c r="H43" s="0">
-        <v>21.171216003090478</v>
+        <v>22.840906313035056</v>
       </c>
       <c r="I43" s="0">
-        <v>1.9212160030904784</v>
+        <v>3.590906313035056</v>
       </c>
       <c r="J43" s="0">
-        <v>1.9212160030904784</v>
+        <v>3.590906313035056</v>
       </c>
       <c r="K43" s="0" t="b">
         <v>1</v>
@@ -1959,31 +1959,31 @@
         <v>56</v>
       </c>
       <c r="C44" s="0">
-        <v>196.6438</v>
+        <v>196.63919999999999</v>
       </c>
       <c r="D44" s="0">
         <v>20</v>
       </c>
       <c r="E44" s="0">
-        <v>21.023316309353106</v>
+        <v>19.902010008028352</v>
       </c>
       <c r="F44" s="0">
-        <v>1.0233163093531061</v>
+        <v>-0.097989991971648038</v>
       </c>
       <c r="G44" s="0">
-        <v>1.0233163093531061</v>
+        <v>0.097989991971648038</v>
       </c>
       <c r="H44" s="0">
-        <v>20.523316309353106</v>
+        <v>19.402010008028352</v>
       </c>
       <c r="I44" s="0">
-        <v>0.52331630935310613</v>
+        <v>-0.59798999197164804</v>
       </c>
       <c r="J44" s="0">
-        <v>0.52331630935310613</v>
+        <v>0.59798999197164804</v>
       </c>
       <c r="K44" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="0">
         <v>1</v>
@@ -1997,28 +1997,28 @@
         <v>56</v>
       </c>
       <c r="C45" s="0">
-        <v>220.79060000000001</v>
+        <v>220.78960000000001</v>
       </c>
       <c r="D45" s="0">
         <v>20</v>
       </c>
       <c r="E45" s="0">
-        <v>21.254712523793803</v>
+        <v>20.551675246026814</v>
       </c>
       <c r="F45" s="0">
-        <v>1.2547125237938026</v>
+        <v>0.55167524602681439</v>
       </c>
       <c r="G45" s="0">
-        <v>1.2547125237938026</v>
+        <v>0.55167524602681439</v>
       </c>
       <c r="H45" s="0">
-        <v>20.754712523793803</v>
+        <v>20.051675246026814</v>
       </c>
       <c r="I45" s="0">
-        <v>0.7547125237938026</v>
+        <v>0.051675246026814392</v>
       </c>
       <c r="J45" s="0">
-        <v>0.7547125237938026</v>
+        <v>0.051675246026814392</v>
       </c>
       <c r="K45" s="0" t="b">
         <v>1</v>
@@ -2035,31 +2035,31 @@
         <v>56</v>
       </c>
       <c r="C46" s="0">
-        <v>202.2679</v>
+        <v>202.2698</v>
       </c>
       <c r="D46" s="0">
         <v>20</v>
       </c>
       <c r="E46" s="0">
-        <v>20.294071043694299</v>
+        <v>20.94511016469604</v>
       </c>
       <c r="F46" s="0">
-        <v>0.2940710436942986</v>
+        <v>0.94511016469603959</v>
       </c>
       <c r="G46" s="0">
-        <v>0.2940710436942986</v>
+        <v>0.94511016469603959</v>
       </c>
       <c r="H46" s="0">
-        <v>19.794071043694299</v>
+        <v>20.44511016469604</v>
       </c>
       <c r="I46" s="0">
-        <v>-0.20592895630570141</v>
+        <v>0.44511016469603959</v>
       </c>
       <c r="J46" s="0">
-        <v>0.20592895630570141</v>
+        <v>0.44511016469603959</v>
       </c>
       <c r="K46" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="0">
         <v>3</v>
@@ -2073,28 +2073,28 @@
         <v>56</v>
       </c>
       <c r="C47" s="0">
-        <v>122.1951</v>
+        <v>122.1789</v>
       </c>
       <c r="D47" s="0">
         <v>22</v>
       </c>
       <c r="E47" s="0">
-        <v>20.512678259809707</v>
+        <v>20.304440065155259</v>
       </c>
       <c r="F47" s="0">
-        <v>-1.4873217401902927</v>
+        <v>-1.6955599348447414</v>
       </c>
       <c r="G47" s="0">
-        <v>1.4873217401902927</v>
+        <v>1.6955599348447414</v>
       </c>
       <c r="H47" s="0">
-        <v>20.012678259809707</v>
+        <v>19.804440065155259</v>
       </c>
       <c r="I47" s="0">
-        <v>-1.9873217401902927</v>
+        <v>-2.1955599348447414</v>
       </c>
       <c r="J47" s="0">
-        <v>1.9873217401902927</v>
+        <v>2.1955599348447414</v>
       </c>
       <c r="K47" s="0" t="b">
         <v>0</v>
@@ -2111,28 +2111,28 @@
         <v>56</v>
       </c>
       <c r="C48" s="0">
-        <v>112.8064</v>
+        <v>113.0775</v>
       </c>
       <c r="D48" s="0">
         <v>22</v>
       </c>
       <c r="E48" s="0">
-        <v>20.996711000581893</v>
+        <v>21.019275625847794</v>
       </c>
       <c r="F48" s="0">
-        <v>-1.0032889994181069</v>
+        <v>-0.98072437415220648</v>
       </c>
       <c r="G48" s="0">
-        <v>1.0032889994181069</v>
+        <v>0.98072437415220648</v>
       </c>
       <c r="H48" s="0">
-        <v>20.496711000581893</v>
+        <v>20.519275625847794</v>
       </c>
       <c r="I48" s="0">
-        <v>-1.5032889994181069</v>
+        <v>-1.4807243741522065</v>
       </c>
       <c r="J48" s="0">
-        <v>1.5032889994181069</v>
+        <v>1.4807243741522065</v>
       </c>
       <c r="K48" s="0" t="b">
         <v>0</v>
@@ -2149,28 +2149,28 @@
         <v>56</v>
       </c>
       <c r="C49" s="0">
-        <v>117.8344</v>
+        <v>117.8364</v>
       </c>
       <c r="D49" s="0">
         <v>23</v>
       </c>
       <c r="E49" s="0">
-        <v>21.448804788470845</v>
+        <v>21.249627801210845</v>
       </c>
       <c r="F49" s="0">
-        <v>-1.551195211529155</v>
+        <v>-1.7503721987891545</v>
       </c>
       <c r="G49" s="0">
-        <v>1.551195211529155</v>
+        <v>1.7503721987891545</v>
       </c>
       <c r="H49" s="0">
-        <v>20.948804788470845</v>
+        <v>20.749627801210845</v>
       </c>
       <c r="I49" s="0">
-        <v>-2.051195211529155</v>
+        <v>-2.2503721987891545</v>
       </c>
       <c r="J49" s="0">
-        <v>2.051195211529155</v>
+        <v>2.2503721987891545</v>
       </c>
       <c r="K49" s="0" t="b">
         <v>0</v>
@@ -2187,28 +2187,28 @@
         <v>56</v>
       </c>
       <c r="C50" s="0">
-        <v>112.1668</v>
+        <v>112.167</v>
       </c>
       <c r="D50" s="0">
         <v>21.75</v>
       </c>
       <c r="E50" s="0">
-        <v>20.71820805822491</v>
+        <v>20.64835391424014</v>
       </c>
       <c r="F50" s="0">
-        <v>-1.03179194177509</v>
+        <v>-1.1016460857598602</v>
       </c>
       <c r="G50" s="0">
-        <v>1.03179194177509</v>
+        <v>1.1016460857598602</v>
       </c>
       <c r="H50" s="0">
-        <v>20.21820805822491</v>
+        <v>20.14835391424014</v>
       </c>
       <c r="I50" s="0">
-        <v>-1.53179194177509</v>
+        <v>-1.6016460857598602</v>
       </c>
       <c r="J50" s="0">
-        <v>1.53179194177509</v>
+        <v>1.6016460857598602</v>
       </c>
       <c r="K50" s="0" t="b">
         <v>0</v>
@@ -2225,28 +2225,28 @@
         <v>56</v>
       </c>
       <c r="C51" s="0">
-        <v>114.0197</v>
+        <v>113.8848</v>
       </c>
       <c r="D51" s="0">
         <v>21.5</v>
       </c>
       <c r="E51" s="0">
-        <v>20.581229951261111</v>
+        <v>20.269931981227696</v>
       </c>
       <c r="F51" s="0">
-        <v>-0.91877004873888879</v>
+        <v>-1.2300680187723039</v>
       </c>
       <c r="G51" s="0">
-        <v>0.91877004873888879</v>
+        <v>1.2300680187723039</v>
       </c>
       <c r="H51" s="0">
-        <v>20.081229951261111</v>
+        <v>19.769931981227696</v>
       </c>
       <c r="I51" s="0">
-        <v>-1.4187700487388888</v>
+        <v>-1.7300680187723039</v>
       </c>
       <c r="J51" s="0">
-        <v>1.4187700487388888</v>
+        <v>1.7300680187723039</v>
       </c>
       <c r="K51" s="0" t="b">
         <v>0</v>
@@ -2263,28 +2263,28 @@
         <v>56</v>
       </c>
       <c r="C52" s="0">
-        <v>105.68340000000001</v>
+        <v>105.6833</v>
       </c>
       <c r="D52" s="0">
         <v>19.199999999999999</v>
       </c>
       <c r="E52" s="0">
-        <v>21.027047777816232</v>
+        <v>19.849946271205688</v>
       </c>
       <c r="F52" s="0">
-        <v>1.8270477778162331</v>
+        <v>0.64994627120568893</v>
       </c>
       <c r="G52" s="0">
-        <v>1.8270477778162331</v>
+        <v>0.64994627120568893</v>
       </c>
       <c r="H52" s="0">
-        <v>20.527047777816232</v>
+        <v>19.349946271205688</v>
       </c>
       <c r="I52" s="0">
-        <v>1.3270477778162331</v>
+        <v>0.14994627120568893</v>
       </c>
       <c r="J52" s="0">
-        <v>1.3270477778162331</v>
+        <v>0.14994627120568893</v>
       </c>
       <c r="K52" s="0" t="b">
         <v>1</v>
@@ -2301,28 +2301,28 @@
         <v>56</v>
       </c>
       <c r="C53" s="0">
-        <v>96.877700000000004</v>
+        <v>96.877300000000005</v>
       </c>
       <c r="D53" s="0">
         <v>17.5</v>
       </c>
       <c r="E53" s="0">
-        <v>20.692040524487062</v>
+        <v>20.214294519320244</v>
       </c>
       <c r="F53" s="0">
-        <v>3.1920405244870622</v>
+        <v>2.7142945193202444</v>
       </c>
       <c r="G53" s="0">
-        <v>3.1920405244870622</v>
+        <v>2.7142945193202444</v>
       </c>
       <c r="H53" s="0">
-        <v>20.192040524487062</v>
+        <v>19.714294519320244</v>
       </c>
       <c r="I53" s="0">
-        <v>2.6920405244870622</v>
+        <v>2.2142945193202444</v>
       </c>
       <c r="J53" s="0">
-        <v>2.6920405244870622</v>
+        <v>2.2142945193202444</v>
       </c>
       <c r="K53" s="0" t="b">
         <v>1</v>
@@ -2345,22 +2345,22 @@
         <v>18.399999999999999</v>
       </c>
       <c r="E54" s="0">
-        <v>20.679155891559333</v>
+        <v>20.221079478415319</v>
       </c>
       <c r="F54" s="0">
-        <v>2.2791558915593342</v>
+        <v>1.8210794784153208</v>
       </c>
       <c r="G54" s="0">
-        <v>2.2791558915593342</v>
+        <v>1.8210794784153208</v>
       </c>
       <c r="H54" s="0">
-        <v>20.179155891559333</v>
+        <v>19.721079478415319</v>
       </c>
       <c r="I54" s="0">
-        <v>1.7791558915593342</v>
+        <v>1.3210794784153208</v>
       </c>
       <c r="J54" s="0">
-        <v>1.7791558915593342</v>
+        <v>1.3210794784153208</v>
       </c>
       <c r="K54" s="0" t="b">
         <v>1</v>
@@ -2377,31 +2377,31 @@
         <v>56</v>
       </c>
       <c r="C55" s="0">
-        <v>94.863200000000006</v>
+        <v>94.863299999999995</v>
       </c>
       <c r="D55" s="0">
         <v>19</v>
       </c>
       <c r="E55" s="0">
-        <v>21.067175469084717</v>
+        <v>18.070520682674793</v>
       </c>
       <c r="F55" s="0">
-        <v>2.0671754690847166</v>
+        <v>-0.92947931732520672</v>
       </c>
       <c r="G55" s="0">
-        <v>2.0671754690847166</v>
+        <v>0.92947931732520672</v>
       </c>
       <c r="H55" s="0">
-        <v>20.567175469084717</v>
+        <v>17.570520682674793</v>
       </c>
       <c r="I55" s="0">
-        <v>1.5671754690847166</v>
+        <v>-1.4294793173252067</v>
       </c>
       <c r="J55" s="0">
-        <v>1.5671754690847166</v>
+        <v>1.4294793173252067</v>
       </c>
       <c r="K55" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="0">
         <v>5</v>
@@ -2416,13 +2416,13 @@
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="46.21875" customWidth="true"/>
-    <col min="2" max="2" width="8.88671875" customWidth="true"/>
-    <col min="3" max="3" width="9.77734375" customWidth="true"/>
-    <col min="4" max="4" width="8.6640625" customWidth="true"/>
-    <col min="5" max="5" width="14.109375" customWidth="true"/>
-    <col min="6" max="6" width="12.5546875" customWidth="true"/>
-    <col min="7" max="7" width="10.5546875" customWidth="true"/>
+    <col min="1" max="1" width="51.140625" customWidth="true"/>
+    <col min="2" max="2" width="9.5703125" customWidth="true"/>
+    <col min="3" max="3" width="10.42578125" customWidth="true"/>
+    <col min="4" max="4" width="9.42578125" customWidth="true"/>
+    <col min="5" max="5" width="15.140625" customWidth="true"/>
+    <col min="6" max="6" width="14" customWidth="true"/>
+    <col min="7" max="7" width="11.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2453,16 +2453,16 @@
         <v>68</v>
       </c>
       <c r="B2" s="0">
-        <v>1.484</v>
+        <v>1.482</v>
       </c>
       <c r="C2" s="0">
-        <v>1.8380000000000001</v>
+        <v>1.833</v>
       </c>
       <c r="D2" s="0">
-        <v>0.10199999999999999</v>
+        <v>0.108</v>
       </c>
       <c r="E2" s="0">
-        <v>0.099000000000000005</v>
+        <v>0.104</v>
       </c>
       <c r="F2" s="0"/>
       <c r="G2" s="0"/>
@@ -2472,22 +2472,22 @@
         <v>69</v>
       </c>
       <c r="B3" s="0">
-        <v>0.036999999999999998</v>
+        <v>0.069000000000000006</v>
       </c>
       <c r="C3" s="0">
+        <v>0.087999999999999995</v>
+      </c>
+      <c r="D3" s="0">
         <v>0.064000000000000001</v>
       </c>
-      <c r="D3" s="0">
-        <v>0.047</v>
-      </c>
       <c r="E3" s="0">
-        <v>0.051999999999999998</v>
+        <v>0.079000000000000001</v>
       </c>
       <c r="F3" s="0">
-        <v>1.5</v>
+        <v>2.8999999999999999</v>
       </c>
       <c r="G3" s="0">
-        <v>1.8</v>
+        <v>2.3999999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2506,18 +2506,18 @@
         <v>71</v>
       </c>
       <c r="B5" s="0">
-        <v>1.484</v>
+        <v>1.4830000000000001</v>
       </c>
       <c r="C5" s="0"/>
       <c r="D5" s="0"/>
       <c r="E5" s="0">
-        <v>-0.40100000000000002</v>
+        <v>-0.39600000000000002</v>
       </c>
       <c r="F5" s="0">
-        <v>40.399999999999999</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="G5" s="0">
-        <v>44.600000000000001</v>
+        <v>44.799999999999997</v>
       </c>
     </row>
     <row r="6">
@@ -2525,10 +2525,10 @@
         <v>72</v>
       </c>
       <c r="B6" s="0">
-        <v>1.51</v>
+        <v>1.5089999999999999</v>
       </c>
       <c r="C6" s="0">
-        <v>1.853</v>
+        <v>1.8520000000000001</v>
       </c>
       <c r="D6" s="0">
         <v>0.051999999999999998</v>

--- a/預測結果與評估指標_kfold_mask幾何.xlsx
+++ b/預測結果與評估指標_kfold_mask幾何.xlsx
@@ -22,205 +22,205 @@
     <t>檔名</t>
   </si>
   <si>
-    <t>001_d1_jpg.rf.55ca288714ec60e15df18c82ae76bc67.jpg</t>
-  </si>
-  <si>
-    <t>002_d0_jpg.rf.b8790bc4063f3067d227a4e526ae4d5a.jpg</t>
-  </si>
-  <si>
-    <t>003_d1_jpg.rf.3973562f637d9898e830f77b6c80ee47.jpg</t>
-  </si>
-  <si>
-    <t>004_d3_jpg.rf.436425ea8d3cfea07d5ef2c70caae4b5.jpg</t>
-  </si>
-  <si>
-    <t>005_d1_jpg.rf.1d35baa3c5801a31e87ca0a899761d4b.jpg</t>
-  </si>
-  <si>
-    <t>006_d1_jpg.rf.fb89dd26c09868f7f2e2c25b37391b5f.jpg</t>
-  </si>
-  <si>
-    <t>007_d1_jpg.rf.2110ece5cbfd523ce6fcb59e5d6ad175.jpg</t>
-  </si>
-  <si>
-    <t>008_d1_jpg.rf.1cb684b004a4e0ce882049570d799742.jpg</t>
-  </si>
-  <si>
-    <t>009_d1_jpg.rf.d07b2087243858aeb80be1e1ba7bb714.jpg</t>
-  </si>
-  <si>
-    <t>010_d1_jpg.rf.12ed75eb6a538870bf7c1892befd47be.jpg</t>
-  </si>
-  <si>
-    <t>011_d0_jpg.rf.24a3e73fb488d0e0a7ca2d4611dd2557.jpg</t>
-  </si>
-  <si>
-    <t>012_d1_jpg.rf.6c455947b4199ab5255c85a091b58a31.jpg</t>
-  </si>
-  <si>
-    <t>013_d1_jpg.rf.34ce0b922f6a8d44280cc06be70b40ad.jpg</t>
-  </si>
-  <si>
-    <t>014_d2_jpg.rf.dde521f03ce3dfcd7df92ba1e3713e58.jpg</t>
-  </si>
-  <si>
-    <t>015_d2_jpg.rf.70e2f6dc9893c6e58cabccd7c011d5b9.jpg</t>
-  </si>
-  <si>
-    <t>016_d2_jpg.rf.65b8db683dc4f8cc8aaac8393cb41f39.jpg</t>
-  </si>
-  <si>
-    <t>017_d0_jpg.rf.708a61dec88abfd33e593ec334f78b1d.jpg</t>
-  </si>
-  <si>
-    <t>018_d1_jpg.rf.5bf79ee3a41faec6e55dc417b91586fc.jpg</t>
-  </si>
-  <si>
-    <t>019_d1_jpg.rf.3db79a352ad46867b221abf127fe08f8.jpg</t>
-  </si>
-  <si>
-    <t>020_d0_jpg.rf.3e4b934f23cd8b513cc009cdb9d82b17.jpg</t>
-  </si>
-  <si>
-    <t>021_d1_jpg.rf.9ae2277fadfdc6d0ff28f1441fdefe6c.jpg</t>
-  </si>
-  <si>
-    <t>022_d1_jpg.rf.65006c8cf3a5a9b18f602e9ac24a4d85.jpg</t>
-  </si>
-  <si>
-    <t>023_d1_jpg.rf.a0f1e12c783fc45b2c71606440cd9cdf.jpg</t>
-  </si>
-  <si>
-    <t>024_d2_jpg.rf.e037af81f2e84ee3621c491021bbedca.jpg</t>
-  </si>
-  <si>
-    <t>026_d1_jpg.rf.72f8bbf079abb3c27d2d96190ecb7b7c.jpg</t>
-  </si>
-  <si>
-    <t>027_d0_jpg.rf.069f8c640691d4f7444bb89af4656ea7.jpg</t>
-  </si>
-  <si>
-    <t>028_d1_jpg.rf.f57ec19622124ac1188f2ba3ec1abeaf.jpg</t>
-  </si>
-  <si>
-    <t>029_d1_jpg.rf.bb10ad14fba1241f3e45fd6287010555.jpg</t>
-  </si>
-  <si>
-    <t>030_d1_jpg.rf.5ebd911c8c14b6d894d03468ab54db54.jpg</t>
-  </si>
-  <si>
-    <t>031_d1_jpg.rf.027a2168cae2921b8f520ac35b5091c7.jpg</t>
-  </si>
-  <si>
-    <t>032_d0_jpg.rf.24d3028acaa9d78ef4b6a5190aa6dd17.jpg</t>
-  </si>
-  <si>
-    <t>034_d1_jpg.rf.75b8f74e83d0a432cafb48b71b900e7f.jpg</t>
-  </si>
-  <si>
-    <t>036_d0_jpg.rf.5f87f7a84eec81ff2996ded4e3ab17c5.jpg</t>
-  </si>
-  <si>
-    <t>037_d0_jpg.rf.7ca9e76521533829c44da4a608e38227.jpg</t>
-  </si>
-  <si>
-    <t>038_d1_jpg.rf.105efb541fd013d353eeea0415e0ad08.jpg</t>
-  </si>
-  <si>
-    <t>039_d1_jpg.rf.9325f3f6007c15ce956824ba4ed19434.jpg</t>
-  </si>
-  <si>
-    <t>040_d0_jpg.rf.bfd5d4db30aed99753ef178ebd96f211.jpg</t>
-  </si>
-  <si>
-    <t>041_d1_jpg.rf.6d42d568e5349b1bc1401afb1a032541.jpg</t>
-  </si>
-  <si>
-    <t>042_d2_jpg.rf.d4047f8c04a5c6faf623949469d955f6.jpg</t>
-  </si>
-  <si>
-    <t>043_d1_jpg.rf.4f546939d5c894ee236287322e2a2e78.jpg</t>
-  </si>
-  <si>
-    <t>044_d2_jpg.rf.0b53fdb22fc286dd9e8a4b21f2d31d85.jpg</t>
-  </si>
-  <si>
-    <t>045_d3_jpg.rf.b35aec29b73f7b5084e0cc6459be15f9.jpg</t>
-  </si>
-  <si>
-    <t>046_d1_jpg.rf.f55bcf163d5589c797bef5d8b412f9c1.jpg</t>
-  </si>
-  <si>
-    <t>047_d0_jpg.rf.9b7b50de4731edce3e8002cfad34afd5.jpg</t>
-  </si>
-  <si>
-    <t>048_d0_jpg.rf.9207ac2109faa2bec8a4d9eb813c70d6.jpg</t>
-  </si>
-  <si>
-    <t>049_d0_jpg.rf.6310b61e8ff6675b1a465351852f5a51.jpg</t>
-  </si>
-  <si>
-    <t>050_d1_jpg.rf.84fdb6257046bd80c5e84db13b1750bf.jpg</t>
-  </si>
-  <si>
-    <t>051_d0_jpg.rf.cafc462d1790b6c6ca401c3e8b037955.jpg</t>
-  </si>
-  <si>
-    <t>052_d1_jpg.rf.7418283c5166896604237ccbcf8dc037.jpg</t>
-  </si>
-  <si>
-    <t>054_d3_jpg.rf.2821b14c46e7909ff2bdbba385d59b6f.jpg</t>
-  </si>
-  <si>
-    <t>055_d2_jpg.rf.7d9db9b7ce9613b3c0bfdf073bd012b3.jpg</t>
-  </si>
-  <si>
-    <t>056_d1_jpg.rf.379c6c5dbc15404b789258691866c2b0.jpg</t>
-  </si>
-  <si>
-    <t>057_d2_jpg.rf.e31cea9a4d92a78adb15f39ce5d86ba8.jpg</t>
-  </si>
-  <si>
-    <t>058_d0_jpg.rf.ae804795ef69cfb93e94e1fdf33195a7.jpg</t>
-  </si>
-  <si>
-    <t>059_d1_jpg.rf.7518cf6b72f813a6057c1bb9e8b0ea4f.jpg</t>
-  </si>
-  <si>
-    <t>060_jpg.rf.26630a77bf453ed3cdc227f0f3fcf9d0.jpg</t>
-  </si>
-  <si>
-    <t>061_d1_jpg.rf.d829f21952ac35c555d13a51f5a580a2.jpg</t>
-  </si>
-  <si>
-    <t>062_d0_jpg.rf.ded7d8972acae712489fcab7f698f5ae.jpg</t>
-  </si>
-  <si>
-    <t>063_d1_jpg.rf.da08e84fee24b5569efa2a750d1bff2f.jpg</t>
-  </si>
-  <si>
-    <t>064_d2_jpg.rf.c8e62f1580424dee4c21d34d668a4e64.jpg</t>
-  </si>
-  <si>
-    <t>065_d0_jpg.rf.959e6c5e9deaf114048e57d62b769ac0.jpg</t>
-  </si>
-  <si>
-    <t>066_d1_jpg.rf.c23dcc0077b0cdf367a6f29daa31affc.jpg</t>
-  </si>
-  <si>
-    <t>067_d0_jpg.rf.ac90bce7f88c1b868e5f95777451272a.jpg</t>
-  </si>
-  <si>
-    <t>068_d1_jpg.rf.4c942bc2ee8c89e7542268bf3b006b03.jpg</t>
-  </si>
-  <si>
-    <t>069_d0_jpg.rf.52b762e91c73d1d37d7ff85ef3bab696.jpg</t>
-  </si>
-  <si>
-    <t>070_d1_jpg.rf.1c5eda7e45ce43492d0c6f1cdfbd0d5c.jpg</t>
-  </si>
-  <si>
-    <t>071_d2_jpg.rf.56b09cdbf1c783b3b1e6f5b2bc96d8b4.jpg</t>
+    <t>001_d1_jpg.rf.55c174a77b98ec1352828ebfa5b9ab51.jpg</t>
+  </si>
+  <si>
+    <t>002_d0_jpg.rf.239b012acf3a5d81cc23f63768811eab.jpg</t>
+  </si>
+  <si>
+    <t>003_d1_jpg.rf.38cc6ea2963bec79f589d69fb3c38567.jpg</t>
+  </si>
+  <si>
+    <t>004_d3_jpg.rf.0908e2acaf0d93383f9ba4d0804e8011.jpg</t>
+  </si>
+  <si>
+    <t>005_d1_jpg.rf.93c30592402d913f3267450c16f2d887.jpg</t>
+  </si>
+  <si>
+    <t>006_d1_jpg.rf.3c7d07d05aae59d1f393853f31eb78a9.jpg</t>
+  </si>
+  <si>
+    <t>007_d1_jpg.rf.dd647087a302f451c265723a4c79a4f4.jpg</t>
+  </si>
+  <si>
+    <t>008_d1_jpg.rf.fbef341d23507d0e4aca06499a411bb3.jpg</t>
+  </si>
+  <si>
+    <t>009_d1_jpg.rf.a4e9643443ee2e940ab17d8bc2f79ed4.jpg</t>
+  </si>
+  <si>
+    <t>010_d1_jpg.rf.9c2ea6a8287eca71401d1cb4a5b4c75c.jpg</t>
+  </si>
+  <si>
+    <t>011_d0_jpg.rf.8592f84486d3e21026a0de8bd8475f37.jpg</t>
+  </si>
+  <si>
+    <t>012_d1_jpg.rf.8f5edc0c4d896e0ac72c42fad4b4ae7e.jpg</t>
+  </si>
+  <si>
+    <t>013_d1_jpg.rf.b7990f89d66aa887a430c51d7385ddcd.jpg</t>
+  </si>
+  <si>
+    <t>014_d2_jpg.rf.a14a36104d29927ab54f862a9837d584.jpg</t>
+  </si>
+  <si>
+    <t>015_d2_jpg.rf.dae752b5463a5088dc2770f784a243e6.jpg</t>
+  </si>
+  <si>
+    <t>016_d2_jpg.rf.d69ea271fc8ead7e00a19c4bff62665c.jpg</t>
+  </si>
+  <si>
+    <t>017_d0_jpg.rf.e371f94baddb2eaf7462ec73ce042fb3.jpg</t>
+  </si>
+  <si>
+    <t>018_d1_jpg.rf.4cb760e4db18ad5514645a6d9ee54a47.jpg</t>
+  </si>
+  <si>
+    <t>019_d1_jpg.rf.b5bbd4289ae38c62eccbabb5ba23cee6.jpg</t>
+  </si>
+  <si>
+    <t>020_d0_jpg.rf.ac00bbc8dce23d8bb488146d95350cfe.jpg</t>
+  </si>
+  <si>
+    <t>021_d1_jpg.rf.ce2222b68f762d4951ed21a7e32abfa1.jpg</t>
+  </si>
+  <si>
+    <t>022_d1_jpg.rf.f1be5fe64a13290e324eac2bae09a30c.jpg</t>
+  </si>
+  <si>
+    <t>023_d1_jpg.rf.19149aa200ed2ab6d2f9f95936683869.jpg</t>
+  </si>
+  <si>
+    <t>024_d2_jpg.rf.dfde607ee1a1abd88070f4a4e9c873a7.jpg</t>
+  </si>
+  <si>
+    <t>026_d1_jpg.rf.cbebc4e773617f19901fea82d27a7481.jpg</t>
+  </si>
+  <si>
+    <t>027_d0_jpg.rf.172e9a9162be8b33b29886a7a7c2044f.jpg</t>
+  </si>
+  <si>
+    <t>028_d1_jpg.rf.c32bbe4c003dc55f0e7db7b213e120d5.jpg</t>
+  </si>
+  <si>
+    <t>029_d1_jpg.rf.60d86604165d1ad5ec3e55f3d4a92ed0.jpg</t>
+  </si>
+  <si>
+    <t>030_d1_jpg.rf.642032a0ccf11c21478fc98e431d62c2.jpg</t>
+  </si>
+  <si>
+    <t>031_d1_jpg.rf.0a64e6a881d6244f0916844a19eec968.jpg</t>
+  </si>
+  <si>
+    <t>032_d0_jpg.rf.9285b7976f1da306fcfec57b8ac03392.jpg</t>
+  </si>
+  <si>
+    <t>034_d1_jpg.rf.c71a61069d50d94065010b64a9ffd1a5.jpg</t>
+  </si>
+  <si>
+    <t>036_d0_jpg.rf.cd77e3ba407312ef40811e53f8234dfc.jpg</t>
+  </si>
+  <si>
+    <t>037_d0_jpg.rf.26d3c419d8aa463d4ccb6f397ffd8a0d.jpg</t>
+  </si>
+  <si>
+    <t>038_d1_jpg.rf.b3c9c20efafeb14a18e816c6ca8d7855.jpg</t>
+  </si>
+  <si>
+    <t>039_d1_jpg.rf.d49148703ce141d56d8246b6549a4760.jpg</t>
+  </si>
+  <si>
+    <t>040_d0_jpg.rf.8f2cbb2d727d030158755add43241d12.jpg</t>
+  </si>
+  <si>
+    <t>041_d1_jpg.rf.cb07a3b2089be3295cec77cb809df396.jpg</t>
+  </si>
+  <si>
+    <t>042_d2_jpg.rf.b762e168ff32523cefa4b66b23ff4fa2.jpg</t>
+  </si>
+  <si>
+    <t>043_d1_jpg.rf.ff8a6dfd8d13cd19c47af53d9384c375.jpg</t>
+  </si>
+  <si>
+    <t>044_d2_jpg.rf.da81051630fbd29d52f53bff91f9d894.jpg</t>
+  </si>
+  <si>
+    <t>045_d3_jpg.rf.e7b47a708da0d4954eb6d698fb50fbc2.jpg</t>
+  </si>
+  <si>
+    <t>046_d1_jpg.rf.ec359b9c3be4b77858006f1894a4fe89.jpg</t>
+  </si>
+  <si>
+    <t>047_d0_jpg.rf.7cdd34b48873ec944be1cf54e2bbe7de.jpg</t>
+  </si>
+  <si>
+    <t>048_d0_jpg.rf.b9d97351b8bbb80a941065b51ab298c2.jpg</t>
+  </si>
+  <si>
+    <t>049_d0_jpg.rf.a92e6c133f098bc8b880cd0c95917303.jpg</t>
+  </si>
+  <si>
+    <t>050_d1_jpg.rf.84fe073fb9b1dc338920f1a858bf5e87.jpg</t>
+  </si>
+  <si>
+    <t>051_d0_jpg.rf.37687ccc93b1c959bc854c565f03d537.jpg</t>
+  </si>
+  <si>
+    <t>052_d1_jpg.rf.3b6940e484968d5a668f3c1f9ae214aa.jpg</t>
+  </si>
+  <si>
+    <t>054_d3_jpg.rf.873773ad3ada175d0933d8f47c5af6c8.jpg</t>
+  </si>
+  <si>
+    <t>055_d2_jpg.rf.165029284ddb2793ad8deac65e1c3f91.jpg</t>
+  </si>
+  <si>
+    <t>056_d1_jpg.rf.9429abcc45818b6e31b5dd0c7d043dfd.jpg</t>
+  </si>
+  <si>
+    <t>057_d2_jpg.rf.cdb9bd6640c5fb65eee49172b52cbf93.jpg</t>
+  </si>
+  <si>
+    <t>058_d0_jpg.rf.ab8df462eb38a7cfd65cff39b2992cdb.jpg</t>
+  </si>
+  <si>
+    <t>059_d1_jpg.rf.3f42e0602c43c121b117dcecca57b59d.jpg</t>
+  </si>
+  <si>
+    <t>060_jpg.rf.4a64dc5e1c74ac81bc312481b7e581e5.jpg</t>
+  </si>
+  <si>
+    <t>061_d1_jpg.rf.db8df0c1f429b3e2e71267f1fbffc989.jpg</t>
+  </si>
+  <si>
+    <t>062_d0_jpg.rf.420ca201dfb51cbc2be18110aeb5765e.jpg</t>
+  </si>
+  <si>
+    <t>063_d1_jpg.rf.3d9a28c55c36d0806810a87e5ea9470f.jpg</t>
+  </si>
+  <si>
+    <t>064_d2_jpg.rf.7b174bc08e6f9220d59234147d56740a.jpg</t>
+  </si>
+  <si>
+    <t>065_d0_jpg.rf.ee2a42597e7bd3f73156286c58ff062a.jpg</t>
+  </si>
+  <si>
+    <t>066_d1_jpg.rf.cca8412d959b332e5836a79cb1f63bb9.jpg</t>
+  </si>
+  <si>
+    <t>067_d0_jpg.rf.5e98d5946a7670ae9374f063be3378c8.jpg</t>
+  </si>
+  <si>
+    <t>068_d1_jpg.rf.dccd7a7a1610957846e542d412bd78a8.jpg</t>
+  </si>
+  <si>
+    <t>069_d0_jpg.rf.e7743bd9b6bf261cd082bb4e0ea61007.jpg</t>
+  </si>
+  <si>
+    <t>070_d1_jpg.rf.dc10b95de92898fa67c004505cf51be2.jpg</t>
+  </si>
+  <si>
+    <t>071_d2_jpg.rf.0959cd07ae695e4405ee3ab991b172da.jpg</t>
   </si>
   <si>
     <t>Train_or_Test</t>
@@ -416,13 +416,13 @@
   <dimension ref="A1:N68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.28515625" customWidth="true"/>
+    <col min="1" max="1" width="50" customWidth="true"/>
     <col min="2" max="2" width="13.140625" customWidth="true"/>
     <col min="3" max="3" width="13.42578125" customWidth="true"/>
     <col min="4" max="4" width="14.7109375" customWidth="true"/>
     <col min="5" max="5" width="14.7109375" customWidth="true"/>
-    <col min="6" max="6" width="15.42578125" customWidth="true"/>
-    <col min="7" max="7" width="14.7109375" customWidth="true"/>
+    <col min="6" max="6" width="15.5703125" customWidth="true"/>
+    <col min="7" max="7" width="15.5703125" customWidth="true"/>
     <col min="8" max="8" width="17" customWidth="true"/>
     <col min="9" max="9" width="20.5703125" customWidth="true"/>
     <col min="10" max="10" width="21.5703125" customWidth="true"/>
@@ -484,28 +484,28 @@
         <v>69</v>
       </c>
       <c r="C2" s="0">
-        <v>492.23230000000001</v>
+        <v>403.60700000000003</v>
       </c>
       <c r="D2" s="0">
         <v>23</v>
       </c>
       <c r="E2" s="0">
-        <v>19.890481975429893</v>
+        <v>20.98498961846407</v>
       </c>
       <c r="F2" s="0">
-        <v>-3.1095180245701073</v>
+        <v>-2.0150103815359302</v>
       </c>
       <c r="G2" s="0">
-        <v>3.1095180245701073</v>
+        <v>2.0150103815359302</v>
       </c>
       <c r="H2" s="0">
-        <v>19.390481975429893</v>
+        <v>20.48498961846407</v>
       </c>
       <c r="I2" s="0">
-        <v>-3.6095180245701073</v>
+        <v>-2.5150103815359302</v>
       </c>
       <c r="J2" s="0">
-        <v>3.6095180245701073</v>
+        <v>2.5150103815359302</v>
       </c>
       <c r="K2" s="0" t="b">
         <v>0</v>
@@ -528,28 +528,28 @@
         <v>69</v>
       </c>
       <c r="C3" s="0">
-        <v>718.98620000000005</v>
+        <v>605.62289999999996</v>
       </c>
       <c r="D3" s="0">
         <v>21</v>
       </c>
       <c r="E3" s="0">
-        <v>20.996824496097592</v>
+        <v>21.092996503984867</v>
       </c>
       <c r="F3" s="0">
-        <v>-0.0031755039024083942</v>
+        <v>0.092996503984867473</v>
       </c>
       <c r="G3" s="0">
-        <v>0.0031755039024083942</v>
+        <v>0.092996503984867473</v>
       </c>
       <c r="H3" s="0">
-        <v>20.496824496097592</v>
+        <v>20.592996503984867</v>
       </c>
       <c r="I3" s="0">
-        <v>-0.50317550390240839</v>
+        <v>-0.40700349601513253</v>
       </c>
       <c r="J3" s="0">
-        <v>0.50317550390240839</v>
+        <v>0.40700349601513253</v>
       </c>
       <c r="K3" s="0" t="b">
         <v>0</v>
@@ -572,28 +572,28 @@
         <v>69</v>
       </c>
       <c r="C4" s="0">
-        <v>915.48400000000004</v>
+        <v>773.59109999999998</v>
       </c>
       <c r="D4" s="0">
         <v>23.5</v>
       </c>
       <c r="E4" s="0">
-        <v>24.519624400221911</v>
+        <v>24.148057825206287</v>
       </c>
       <c r="F4" s="0">
-        <v>1.019624400221911</v>
+        <v>0.64805782520628696</v>
       </c>
       <c r="G4" s="0">
-        <v>1.019624400221911</v>
+        <v>0.64805782520628696</v>
       </c>
       <c r="H4" s="0">
-        <v>24.019624400221911</v>
+        <v>23.648057825206287</v>
       </c>
       <c r="I4" s="0">
-        <v>0.51962440022191103</v>
+        <v>0.14805782520628696</v>
       </c>
       <c r="J4" s="0">
-        <v>0.51962440022191103</v>
+        <v>0.14805782520628696</v>
       </c>
       <c r="K4" s="0" t="b">
         <v>1</v>
@@ -616,28 +616,28 @@
         <v>69</v>
       </c>
       <c r="C5" s="0">
-        <v>700.44370000000004</v>
+        <v>579.42529999999999</v>
       </c>
       <c r="D5" s="0">
         <v>21</v>
       </c>
       <c r="E5" s="0">
-        <v>20.702736582308138</v>
+        <v>21.010949789759543</v>
       </c>
       <c r="F5" s="0">
-        <v>-0.29726341769186249</v>
+        <v>0.010949789759543194</v>
       </c>
       <c r="G5" s="0">
-        <v>0.29726341769186249</v>
+        <v>0.010949789759543194</v>
       </c>
       <c r="H5" s="0">
-        <v>20.202736582308138</v>
+        <v>20.510949789759543</v>
       </c>
       <c r="I5" s="0">
-        <v>-0.79726341769186249</v>
+        <v>-0.48905021024045681</v>
       </c>
       <c r="J5" s="0">
-        <v>0.79726341769186249</v>
+        <v>0.48905021024045681</v>
       </c>
       <c r="K5" s="0" t="b">
         <v>0</v>
@@ -660,28 +660,28 @@
         <v>69</v>
       </c>
       <c r="C6" s="0">
-        <v>784.41660000000002</v>
+        <v>632.08730000000003</v>
       </c>
       <c r="D6" s="0">
         <v>21.5</v>
       </c>
       <c r="E6" s="0">
-        <v>21.349186198906164</v>
+        <v>21.255370603035321</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.15081380109383602</v>
+        <v>-0.24462939696467956</v>
       </c>
       <c r="G6" s="0">
-        <v>0.15081380109383602</v>
+        <v>0.24462939696467956</v>
       </c>
       <c r="H6" s="0">
-        <v>20.849186198906164</v>
+        <v>20.755370603035321</v>
       </c>
       <c r="I6" s="0">
-        <v>-0.65081380109383602</v>
+        <v>-0.74462939696467956</v>
       </c>
       <c r="J6" s="0">
-        <v>0.65081380109383602</v>
+        <v>0.74462939696467956</v>
       </c>
       <c r="K6" s="0" t="b">
         <v>0</v>
@@ -704,28 +704,28 @@
         <v>69</v>
       </c>
       <c r="C7" s="0">
-        <v>845.90949999999998</v>
+        <v>720.98979999999995</v>
       </c>
       <c r="D7" s="0">
         <v>22</v>
       </c>
       <c r="E7" s="0">
-        <v>21.409417843837225</v>
+        <v>21.03196546052645</v>
       </c>
       <c r="F7" s="0">
-        <v>-0.59058215616277465</v>
+        <v>-0.96803453947354967</v>
       </c>
       <c r="G7" s="0">
-        <v>0.59058215616277465</v>
+        <v>0.96803453947354967</v>
       </c>
       <c r="H7" s="0">
-        <v>20.909417843837225</v>
+        <v>20.53196546052645</v>
       </c>
       <c r="I7" s="0">
-        <v>-1.0905821561627747</v>
+        <v>-1.4680345394735497</v>
       </c>
       <c r="J7" s="0">
-        <v>1.0905821561627747</v>
+        <v>1.4680345394735497</v>
       </c>
       <c r="K7" s="0" t="b">
         <v>0</v>
@@ -748,28 +748,28 @@
         <v>69</v>
       </c>
       <c r="C8" s="0">
-        <v>921.03729999999996</v>
+        <v>758.05489999999998</v>
       </c>
       <c r="D8" s="0">
         <v>25</v>
       </c>
       <c r="E8" s="0">
-        <v>24.914636186131396</v>
+        <v>24.043822955457799</v>
       </c>
       <c r="F8" s="0">
-        <v>-0.0853638138686037</v>
+        <v>-0.95617704454220132</v>
       </c>
       <c r="G8" s="0">
-        <v>0.0853638138686037</v>
+        <v>0.95617704454220132</v>
       </c>
       <c r="H8" s="0">
-        <v>24.414636186131396</v>
+        <v>23.543822955457799</v>
       </c>
       <c r="I8" s="0">
-        <v>-0.5853638138686037</v>
+        <v>-1.4561770445422013</v>
       </c>
       <c r="J8" s="0">
-        <v>0.5853638138686037</v>
+        <v>1.4561770445422013</v>
       </c>
       <c r="K8" s="0" t="b">
         <v>0</v>
@@ -792,28 +792,28 @@
         <v>69</v>
       </c>
       <c r="C9" s="0">
-        <v>462.82240000000002</v>
+        <v>400.07780000000002</v>
       </c>
       <c r="D9" s="0">
         <v>20.5</v>
       </c>
       <c r="E9" s="0">
-        <v>19.979202518331054</v>
+        <v>20.07924866119598</v>
       </c>
       <c r="F9" s="0">
-        <v>-0.52079748166894646</v>
+        <v>-0.42075133880402049</v>
       </c>
       <c r="G9" s="0">
-        <v>0.52079748166894646</v>
+        <v>0.42075133880402049</v>
       </c>
       <c r="H9" s="0">
-        <v>19.479202518331054</v>
+        <v>19.57924866119598</v>
       </c>
       <c r="I9" s="0">
-        <v>-1.0207974816689465</v>
+        <v>-0.92075133880402049</v>
       </c>
       <c r="J9" s="0">
-        <v>1.0207974816689465</v>
+        <v>0.92075133880402049</v>
       </c>
       <c r="K9" s="0" t="b">
         <v>0</v>
@@ -836,28 +836,28 @@
         <v>69</v>
       </c>
       <c r="C10" s="0">
-        <v>1559.8009</v>
+        <v>1283.9973</v>
       </c>
       <c r="D10" s="0">
         <v>21</v>
       </c>
       <c r="E10" s="0">
-        <v>20.709467101092244</v>
+        <v>20.627113766277876</v>
       </c>
       <c r="F10" s="0">
-        <v>-0.29053289890775602</v>
+        <v>-0.37288623372212371</v>
       </c>
       <c r="G10" s="0">
-        <v>0.29053289890775602</v>
+        <v>0.37288623372212371</v>
       </c>
       <c r="H10" s="0">
-        <v>20.209467101092244</v>
+        <v>20.127113766277876</v>
       </c>
       <c r="I10" s="0">
-        <v>-0.79053289890775602</v>
+        <v>-0.87288623372212371</v>
       </c>
       <c r="J10" s="0">
-        <v>0.79053289890775602</v>
+        <v>0.87288623372212371</v>
       </c>
       <c r="K10" s="0" t="b">
         <v>0</v>
@@ -880,28 +880,28 @@
         <v>69</v>
       </c>
       <c r="C11" s="0">
-        <v>382.24470000000002</v>
+        <v>317.95030000000003</v>
       </c>
       <c r="D11" s="0">
         <v>18</v>
       </c>
       <c r="E11" s="0">
-        <v>19.593661709947174</v>
+        <v>20.972418057343077</v>
       </c>
       <c r="F11" s="0">
-        <v>1.5936617099471739</v>
+        <v>2.9724180573430772</v>
       </c>
       <c r="G11" s="0">
-        <v>1.5936617099471739</v>
+        <v>2.9724180573430772</v>
       </c>
       <c r="H11" s="0">
-        <v>19.093661709947174</v>
+        <v>20.472418057343077</v>
       </c>
       <c r="I11" s="0">
-        <v>1.0936617099471739</v>
+        <v>2.4724180573430772</v>
       </c>
       <c r="J11" s="0">
-        <v>1.0936617099471739</v>
+        <v>2.4724180573430772</v>
       </c>
       <c r="K11" s="0" t="b">
         <v>1</v>
@@ -924,28 +924,28 @@
         <v>69</v>
       </c>
       <c r="C12" s="0">
-        <v>869.45579999999995</v>
+        <v>750.11170000000004</v>
       </c>
       <c r="D12" s="0">
         <v>25</v>
       </c>
       <c r="E12" s="0">
-        <v>20.952593319683157</v>
+        <v>23.872563626712871</v>
       </c>
       <c r="F12" s="0">
-        <v>-4.0474066803168434</v>
+        <v>-1.1274363732871286</v>
       </c>
       <c r="G12" s="0">
-        <v>4.0474066803168434</v>
+        <v>1.1274363732871286</v>
       </c>
       <c r="H12" s="0">
-        <v>20.452593319683157</v>
+        <v>23.372563626712871</v>
       </c>
       <c r="I12" s="0">
-        <v>-4.5474066803168434</v>
+        <v>-1.6274363732871286</v>
       </c>
       <c r="J12" s="0">
-        <v>4.5474066803168434</v>
+        <v>1.6274363732871286</v>
       </c>
       <c r="K12" s="0" t="b">
         <v>0</v>
@@ -968,28 +968,28 @@
         <v>69</v>
       </c>
       <c r="C13" s="0">
-        <v>799.36030000000005</v>
+        <v>675.26099999999997</v>
       </c>
       <c r="D13" s="0">
         <v>22.5</v>
       </c>
       <c r="E13" s="0">
-        <v>20.952593319683157</v>
+        <v>21.672327173166902</v>
       </c>
       <c r="F13" s="0">
-        <v>-1.5474066803168434</v>
+        <v>-0.82767282683309773</v>
       </c>
       <c r="G13" s="0">
-        <v>1.5474066803168434</v>
+        <v>0.82767282683309773</v>
       </c>
       <c r="H13" s="0">
-        <v>20.452593319683157</v>
+        <v>21.172327173166902</v>
       </c>
       <c r="I13" s="0">
-        <v>-2.0474066803168434</v>
+        <v>-1.3276728268330977</v>
       </c>
       <c r="J13" s="0">
-        <v>2.0474066803168434</v>
+        <v>1.3276728268330977</v>
       </c>
       <c r="K13" s="0" t="b">
         <v>0</v>
@@ -1012,28 +1012,28 @@
         <v>69</v>
       </c>
       <c r="C14" s="0">
-        <v>816.15729999999996</v>
+        <v>674.45989999999995</v>
       </c>
       <c r="D14" s="0">
         <v>20.5</v>
       </c>
       <c r="E14" s="0">
-        <v>21.220210185921431</v>
+        <v>21.337548916327187</v>
       </c>
       <c r="F14" s="0">
-        <v>0.72021018592143093</v>
+        <v>0.83754891632718653</v>
       </c>
       <c r="G14" s="0">
-        <v>0.72021018592143093</v>
+        <v>0.83754891632718653</v>
       </c>
       <c r="H14" s="0">
-        <v>20.720210185921431</v>
+        <v>20.837548916327187</v>
       </c>
       <c r="I14" s="0">
-        <v>0.22021018592143094</v>
+        <v>0.33754891632718653</v>
       </c>
       <c r="J14" s="0">
-        <v>0.22021018592143094</v>
+        <v>0.33754891632718653</v>
       </c>
       <c r="K14" s="0" t="b">
         <v>1</v>
@@ -1056,28 +1056,28 @@
         <v>69</v>
       </c>
       <c r="C15" s="0">
-        <v>710.17160000000001</v>
+        <v>583.64300000000003</v>
       </c>
       <c r="D15" s="0">
         <v>19.5</v>
       </c>
       <c r="E15" s="0">
-        <v>20.952593319683157</v>
+        <v>20.066072873466098</v>
       </c>
       <c r="F15" s="0">
-        <v>1.4525933196831566</v>
+        <v>0.5660728734660978</v>
       </c>
       <c r="G15" s="0">
-        <v>1.4525933196831566</v>
+        <v>0.5660728734660978</v>
       </c>
       <c r="H15" s="0">
-        <v>20.452593319683157</v>
+        <v>19.566072873466098</v>
       </c>
       <c r="I15" s="0">
-        <v>0.95259331968315664</v>
+        <v>0.066072873466097804</v>
       </c>
       <c r="J15" s="0">
-        <v>0.95259331968315664</v>
+        <v>0.066072873466097804</v>
       </c>
       <c r="K15" s="0" t="b">
         <v>1</v>
@@ -1100,28 +1100,28 @@
         <v>69</v>
       </c>
       <c r="C16" s="0">
-        <v>741.25810000000001</v>
+        <v>617.06880000000001</v>
       </c>
       <c r="D16" s="0">
         <v>19.5</v>
       </c>
       <c r="E16" s="0">
-        <v>21.114205082167672</v>
+        <v>21.162821885280515</v>
       </c>
       <c r="F16" s="0">
-        <v>1.6142050821676719</v>
+        <v>1.6628218852805148</v>
       </c>
       <c r="G16" s="0">
-        <v>1.6142050821676719</v>
+        <v>1.6628218852805148</v>
       </c>
       <c r="H16" s="0">
-        <v>20.614205082167672</v>
+        <v>20.662821885280515</v>
       </c>
       <c r="I16" s="0">
-        <v>1.1142050821676719</v>
+        <v>1.1628218852805148</v>
       </c>
       <c r="J16" s="0">
-        <v>1.1142050821676719</v>
+        <v>1.1628218852805148</v>
       </c>
       <c r="K16" s="0" t="b">
         <v>1</v>
@@ -1144,28 +1144,28 @@
         <v>69</v>
       </c>
       <c r="C17" s="0">
-        <v>1356.1457</v>
+        <v>1130.2846</v>
       </c>
       <c r="D17" s="0">
         <v>18.5</v>
       </c>
       <c r="E17" s="0">
-        <v>18.365567669400512</v>
+        <v>18.406758654163408</v>
       </c>
       <c r="F17" s="0">
-        <v>-0.13443233059948767</v>
+        <v>-0.09324134583659216</v>
       </c>
       <c r="G17" s="0">
-        <v>0.13443233059948767</v>
+        <v>0.09324134583659216</v>
       </c>
       <c r="H17" s="0">
-        <v>17.865567669400512</v>
+        <v>17.906758654163408</v>
       </c>
       <c r="I17" s="0">
-        <v>-0.63443233059948767</v>
+        <v>-0.59324134583659216</v>
       </c>
       <c r="J17" s="0">
-        <v>0.63443233059948767</v>
+        <v>0.59324134583659216</v>
       </c>
       <c r="K17" s="0" t="b">
         <v>0</v>
@@ -1188,28 +1188,28 @@
         <v>69</v>
       </c>
       <c r="C18" s="0">
-        <v>1782.7297000000001</v>
+        <v>1452.2846</v>
       </c>
       <c r="D18" s="0">
         <v>23.75</v>
       </c>
       <c r="E18" s="0">
-        <v>20.952593319683157</v>
+        <v>22.173720357696652</v>
       </c>
       <c r="F18" s="0">
-        <v>-2.7974066803168434</v>
+        <v>-1.5762796423033478</v>
       </c>
       <c r="G18" s="0">
-        <v>2.7974066803168434</v>
+        <v>1.5762796423033478</v>
       </c>
       <c r="H18" s="0">
-        <v>20.452593319683157</v>
+        <v>21.673720357696652</v>
       </c>
       <c r="I18" s="0">
-        <v>-3.2974066803168434</v>
+        <v>-2.0762796423033478</v>
       </c>
       <c r="J18" s="0">
-        <v>3.2974066803168434</v>
+        <v>2.0762796423033478</v>
       </c>
       <c r="K18" s="0" t="b">
         <v>0</v>
@@ -1232,28 +1232,28 @@
         <v>69</v>
       </c>
       <c r="C19" s="0">
-        <v>812.73040000000003</v>
+        <v>668.60829999999999</v>
       </c>
       <c r="D19" s="0">
         <v>22.25</v>
       </c>
       <c r="E19" s="0">
-        <v>20.84599063255709</v>
+        <v>20.866965531298369</v>
       </c>
       <c r="F19" s="0">
-        <v>-1.4040093674429102</v>
+        <v>-1.3830344687016307</v>
       </c>
       <c r="G19" s="0">
-        <v>1.4040093674429102</v>
+        <v>1.3830344687016307</v>
       </c>
       <c r="H19" s="0">
-        <v>20.34599063255709</v>
+        <v>20.366965531298369</v>
       </c>
       <c r="I19" s="0">
-        <v>-1.9040093674429102</v>
+        <v>-1.8830344687016307</v>
       </c>
       <c r="J19" s="0">
-        <v>1.9040093674429102</v>
+        <v>1.8830344687016307</v>
       </c>
       <c r="K19" s="0" t="b">
         <v>0</v>
@@ -1276,28 +1276,28 @@
         <v>69</v>
       </c>
       <c r="C20" s="0">
-        <v>910.79949999999997</v>
+        <v>750.32280000000003</v>
       </c>
       <c r="D20" s="0">
         <v>25.5</v>
       </c>
       <c r="E20" s="0">
-        <v>21.692877681580384</v>
+        <v>21.036328859161373</v>
       </c>
       <c r="F20" s="0">
-        <v>-3.8071223184196157</v>
+        <v>-4.4636711408386276</v>
       </c>
       <c r="G20" s="0">
-        <v>3.8071223184196157</v>
+        <v>4.4636711408386276</v>
       </c>
       <c r="H20" s="0">
-        <v>21.192877681580384</v>
+        <v>20.536328859161373</v>
       </c>
       <c r="I20" s="0">
-        <v>-4.3071223184196157</v>
+        <v>-4.9636711408386276</v>
       </c>
       <c r="J20" s="0">
-        <v>4.3071223184196157</v>
+        <v>4.9636711408386276</v>
       </c>
       <c r="K20" s="0" t="b">
         <v>0</v>
@@ -1320,28 +1320,28 @@
         <v>69</v>
       </c>
       <c r="C21" s="0">
-        <v>416.36110000000002</v>
+        <v>345.22919999999999</v>
       </c>
       <c r="D21" s="0">
         <v>22.5</v>
       </c>
       <c r="E21" s="0">
-        <v>20.952593319683157</v>
+        <v>19.827445989184444</v>
       </c>
       <c r="F21" s="0">
-        <v>-1.5474066803168434</v>
+        <v>-2.6725540108155563</v>
       </c>
       <c r="G21" s="0">
-        <v>1.5474066803168434</v>
+        <v>2.6725540108155563</v>
       </c>
       <c r="H21" s="0">
-        <v>20.452593319683157</v>
+        <v>19.327445989184444</v>
       </c>
       <c r="I21" s="0">
-        <v>-2.0474066803168434</v>
+        <v>-3.1725540108155563</v>
       </c>
       <c r="J21" s="0">
-        <v>2.0474066803168434</v>
+        <v>3.1725540108155563</v>
       </c>
       <c r="K21" s="0" t="b">
         <v>0</v>
@@ -1364,28 +1364,28 @@
         <v>69</v>
       </c>
       <c r="C22" s="0">
-        <v>753.03869999999995</v>
+        <v>622.22630000000004</v>
       </c>
       <c r="D22" s="0">
         <v>21.5</v>
       </c>
       <c r="E22" s="0">
-        <v>20.033412318845389</v>
+        <v>20.144372708484866</v>
       </c>
       <c r="F22" s="0">
-        <v>-1.4665876811546106</v>
+        <v>-1.3556272915151339</v>
       </c>
       <c r="G22" s="0">
-        <v>1.4665876811546106</v>
+        <v>1.3556272915151339</v>
       </c>
       <c r="H22" s="0">
-        <v>19.533412318845389</v>
+        <v>19.644372708484866</v>
       </c>
       <c r="I22" s="0">
-        <v>-1.9665876811546106</v>
+        <v>-1.855627291515134</v>
       </c>
       <c r="J22" s="0">
-        <v>1.9665876811546106</v>
+        <v>1.855627291515134</v>
       </c>
       <c r="K22" s="0" t="b">
         <v>0</v>
@@ -1408,28 +1408,28 @@
         <v>69</v>
       </c>
       <c r="C23" s="0">
-        <v>837.13900000000001</v>
+        <v>671.48209999999995</v>
       </c>
       <c r="D23" s="0">
         <v>20</v>
       </c>
       <c r="E23" s="0">
-        <v>21.872016433752879</v>
+        <v>21.247165178907721</v>
       </c>
       <c r="F23" s="0">
-        <v>1.8720164337528793</v>
+        <v>1.2471651789077214</v>
       </c>
       <c r="G23" s="0">
-        <v>1.8720164337528793</v>
+        <v>1.2471651789077214</v>
       </c>
       <c r="H23" s="0">
-        <v>21.372016433752879</v>
+        <v>20.747165178907721</v>
       </c>
       <c r="I23" s="0">
-        <v>1.3720164337528793</v>
+        <v>0.74716517890772138</v>
       </c>
       <c r="J23" s="0">
-        <v>1.3720164337528793</v>
+        <v>0.74716517890772138</v>
       </c>
       <c r="K23" s="0" t="b">
         <v>1</v>
@@ -1452,28 +1452,28 @@
         <v>69</v>
       </c>
       <c r="C24" s="0">
-        <v>708.72850000000005</v>
+        <v>582.96010000000001</v>
       </c>
       <c r="D24" s="0">
         <v>19.5</v>
       </c>
       <c r="E24" s="0">
-        <v>20.943968695902335</v>
+        <v>20.957433177360869</v>
       </c>
       <c r="F24" s="0">
-        <v>1.4439686959023348</v>
+        <v>1.4574331773608691</v>
       </c>
       <c r="G24" s="0">
-        <v>1.4439686959023348</v>
+        <v>1.4574331773608691</v>
       </c>
       <c r="H24" s="0">
-        <v>20.443968695902335</v>
+        <v>20.457433177360869</v>
       </c>
       <c r="I24" s="0">
-        <v>0.94396869590233479</v>
+        <v>0.95743317736086908</v>
       </c>
       <c r="J24" s="0">
-        <v>0.94396869590233479</v>
+        <v>0.95743317736086908</v>
       </c>
       <c r="K24" s="0" t="b">
         <v>1</v>
@@ -1496,28 +1496,28 @@
         <v>69</v>
       </c>
       <c r="C25" s="0">
-        <v>696.64210000000003</v>
+        <v>577.6952</v>
       </c>
       <c r="D25" s="0">
         <v>18.5</v>
       </c>
       <c r="E25" s="0">
-        <v>20.262683070750473</v>
+        <v>19.998765336244446</v>
       </c>
       <c r="F25" s="0">
-        <v>1.762683070750473</v>
+        <v>1.4987653362444462</v>
       </c>
       <c r="G25" s="0">
-        <v>1.762683070750473</v>
+        <v>1.4987653362444462</v>
       </c>
       <c r="H25" s="0">
-        <v>19.762683070750473</v>
+        <v>19.498765336244446</v>
       </c>
       <c r="I25" s="0">
-        <v>1.262683070750473</v>
+        <v>0.99876533624444619</v>
       </c>
       <c r="J25" s="0">
-        <v>1.262683070750473</v>
+        <v>0.99876533624444619</v>
       </c>
       <c r="K25" s="0" t="b">
         <v>1</v>
@@ -1540,31 +1540,31 @@
         <v>69</v>
       </c>
       <c r="C26" s="0">
-        <v>831.55809999999997</v>
+        <v>689.21019999999999</v>
       </c>
       <c r="D26" s="0">
         <v>21.25</v>
       </c>
       <c r="E26" s="0">
-        <v>20.952593319683157</v>
+        <v>22.29141410040539</v>
       </c>
       <c r="F26" s="0">
-        <v>-0.29740668031684336</v>
+        <v>1.0414141004053903</v>
       </c>
       <c r="G26" s="0">
-        <v>0.29740668031684336</v>
+        <v>1.0414141004053903</v>
       </c>
       <c r="H26" s="0">
-        <v>20.452593319683157</v>
+        <v>21.79141410040539</v>
       </c>
       <c r="I26" s="0">
-        <v>-0.79740668031684336</v>
+        <v>0.54141410040539029</v>
       </c>
       <c r="J26" s="0">
-        <v>0.79740668031684336</v>
+        <v>0.54141410040539029</v>
       </c>
       <c r="K26" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="0">
         <v>3</v>
@@ -1584,28 +1584,28 @@
         <v>69</v>
       </c>
       <c r="C27" s="0">
-        <v>758.57349999999997</v>
+        <v>641.4787</v>
       </c>
       <c r="D27" s="0">
         <v>19.25</v>
       </c>
       <c r="E27" s="0">
-        <v>20.084969658824715</v>
+        <v>20.476669092205185</v>
       </c>
       <c r="F27" s="0">
-        <v>0.83496965882471486</v>
+        <v>1.2266690922051851</v>
       </c>
       <c r="G27" s="0">
-        <v>0.83496965882471486</v>
+        <v>1.2266690922051851</v>
       </c>
       <c r="H27" s="0">
-        <v>19.584969658824715</v>
+        <v>19.976669092205185</v>
       </c>
       <c r="I27" s="0">
-        <v>0.33496965882471486</v>
+        <v>0.72666909220518505</v>
       </c>
       <c r="J27" s="0">
-        <v>0.33496965882471486</v>
+        <v>0.72666909220518505</v>
       </c>
       <c r="K27" s="0" t="b">
         <v>1</v>
@@ -1628,28 +1628,28 @@
         <v>69</v>
       </c>
       <c r="C28" s="0">
-        <v>850.76089999999999</v>
+        <v>684.71199999999999</v>
       </c>
       <c r="D28" s="0">
         <v>21.75</v>
       </c>
       <c r="E28" s="0">
-        <v>21.432312022728894</v>
+        <v>21.026572635827932</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.31768797727110609</v>
+        <v>-0.72342736417206766</v>
       </c>
       <c r="G28" s="0">
-        <v>0.31768797727110609</v>
+        <v>0.72342736417206766</v>
       </c>
       <c r="H28" s="0">
-        <v>20.932312022728894</v>
+        <v>20.526572635827932</v>
       </c>
       <c r="I28" s="0">
-        <v>-0.81768797727110609</v>
+        <v>-1.2234273641720677</v>
       </c>
       <c r="J28" s="0">
-        <v>0.81768797727110609</v>
+        <v>1.2234273641720677</v>
       </c>
       <c r="K28" s="0" t="b">
         <v>0</v>
@@ -1672,28 +1672,28 @@
         <v>69</v>
       </c>
       <c r="C29" s="0">
-        <v>428.6198</v>
+        <v>353.73129999999998</v>
       </c>
       <c r="D29" s="0">
         <v>20.75</v>
       </c>
       <c r="E29" s="0">
-        <v>20.94998459515832</v>
+        <v>20.93991176863781</v>
       </c>
       <c r="F29" s="0">
-        <v>0.19998459515831968</v>
+        <v>0.18991176863780979</v>
       </c>
       <c r="G29" s="0">
-        <v>0.19998459515831968</v>
+        <v>0.18991176863780979</v>
       </c>
       <c r="H29" s="0">
-        <v>20.44998459515832</v>
+        <v>20.43991176863781</v>
       </c>
       <c r="I29" s="0">
-        <v>-0.30001540484168032</v>
+        <v>-0.31008823136219021</v>
       </c>
       <c r="J29" s="0">
-        <v>0.30001540484168032</v>
+        <v>0.31008823136219021</v>
       </c>
       <c r="K29" s="0" t="b">
         <v>0</v>
@@ -1716,28 +1716,28 @@
         <v>69</v>
       </c>
       <c r="C30" s="0">
-        <v>834.92809999999997</v>
+        <v>683.46259999999995</v>
       </c>
       <c r="D30" s="0">
         <v>21.5</v>
       </c>
       <c r="E30" s="0">
-        <v>21.626874311819677</v>
+        <v>21.571381470138199</v>
       </c>
       <c r="F30" s="0">
-        <v>0.12687431181967668</v>
+        <v>0.071381470138199177</v>
       </c>
       <c r="G30" s="0">
-        <v>0.12687431181967668</v>
+        <v>0.071381470138199177</v>
       </c>
       <c r="H30" s="0">
-        <v>21.126874311819677</v>
+        <v>21.071381470138199</v>
       </c>
       <c r="I30" s="0">
-        <v>-0.37312568818032332</v>
+        <v>-0.42861852986180082</v>
       </c>
       <c r="J30" s="0">
-        <v>0.37312568818032332</v>
+        <v>0.42861852986180082</v>
       </c>
       <c r="K30" s="0" t="b">
         <v>0</v>
@@ -1760,28 +1760,28 @@
         <v>69</v>
       </c>
       <c r="C31" s="0">
-        <v>1636.5373999999999</v>
+        <v>1356.9842000000001</v>
       </c>
       <c r="D31" s="0">
         <v>19.5</v>
       </c>
       <c r="E31" s="0">
-        <v>21.467732353821877</v>
+        <v>21.531804995208255</v>
       </c>
       <c r="F31" s="0">
-        <v>1.9677323538218765</v>
+        <v>2.0318049952082546</v>
       </c>
       <c r="G31" s="0">
-        <v>1.9677323538218765</v>
+        <v>2.0318049952082546</v>
       </c>
       <c r="H31" s="0">
-        <v>20.967732353821877</v>
+        <v>21.031804995208255</v>
       </c>
       <c r="I31" s="0">
-        <v>1.4677323538218765</v>
+        <v>1.5318049952082546</v>
       </c>
       <c r="J31" s="0">
-        <v>1.4677323538218765</v>
+        <v>1.5318049952082546</v>
       </c>
       <c r="K31" s="0" t="b">
         <v>1</v>
@@ -1804,28 +1804,28 @@
         <v>69</v>
       </c>
       <c r="C32" s="0">
-        <v>1616.8412000000001</v>
+        <v>1312.2254</v>
       </c>
       <c r="D32" s="0">
         <v>19.5</v>
       </c>
       <c r="E32" s="0">
-        <v>21.269874869670097</v>
+        <v>20.967725137838141</v>
       </c>
       <c r="F32" s="0">
-        <v>1.7698748696700974</v>
+        <v>1.4677251378381406</v>
       </c>
       <c r="G32" s="0">
-        <v>1.7698748696700974</v>
+        <v>1.4677251378381406</v>
       </c>
       <c r="H32" s="0">
-        <v>20.769874869670097</v>
+        <v>20.467725137838141</v>
       </c>
       <c r="I32" s="0">
-        <v>1.2698748696700974</v>
+        <v>0.96772513783814063</v>
       </c>
       <c r="J32" s="0">
-        <v>1.2698748696700974</v>
+        <v>0.96772513783814063</v>
       </c>
       <c r="K32" s="0" t="b">
         <v>1</v>
@@ -1848,28 +1848,28 @@
         <v>69</v>
       </c>
       <c r="C33" s="0">
-        <v>1630.0059000000001</v>
+        <v>1359.0623000000001</v>
       </c>
       <c r="D33" s="0">
         <v>21</v>
       </c>
       <c r="E33" s="0">
-        <v>20.621656608608412</v>
+        <v>20.90548818667094</v>
       </c>
       <c r="F33" s="0">
-        <v>-0.37834339139158857</v>
+        <v>-0.094511813329059891</v>
       </c>
       <c r="G33" s="0">
-        <v>0.37834339139158857</v>
+        <v>0.094511813329059891</v>
       </c>
       <c r="H33" s="0">
-        <v>20.121656608608412</v>
+        <v>20.40548818667094</v>
       </c>
       <c r="I33" s="0">
-        <v>-0.87834339139158857</v>
+        <v>-0.59451181332905989</v>
       </c>
       <c r="J33" s="0">
-        <v>0.87834339139158857</v>
+        <v>0.59451181332905989</v>
       </c>
       <c r="K33" s="0" t="b">
         <v>0</v>
@@ -1892,31 +1892,31 @@
         <v>69</v>
       </c>
       <c r="C34" s="0">
-        <v>728.40809999999999</v>
+        <v>611.02089999999998</v>
       </c>
       <c r="D34" s="0">
         <v>20.25</v>
       </c>
       <c r="E34" s="0">
-        <v>20.952593319683157</v>
+        <v>19.926322962763244</v>
       </c>
       <c r="F34" s="0">
-        <v>0.70259331968315664</v>
+        <v>-0.32367703723675589</v>
       </c>
       <c r="G34" s="0">
-        <v>0.70259331968315664</v>
+        <v>0.32367703723675589</v>
       </c>
       <c r="H34" s="0">
-        <v>20.452593319683157</v>
+        <v>19.426322962763244</v>
       </c>
       <c r="I34" s="0">
-        <v>0.20259331968315664</v>
+        <v>-0.82367703723675589</v>
       </c>
       <c r="J34" s="0">
-        <v>0.20259331968315664</v>
+        <v>0.82367703723675589</v>
       </c>
       <c r="K34" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="0">
         <v>3</v>
@@ -1936,28 +1936,28 @@
         <v>69</v>
       </c>
       <c r="C35" s="0">
-        <v>745.38679999999999</v>
+        <v>623.09130000000005</v>
       </c>
       <c r="D35" s="0">
         <v>21.5</v>
       </c>
       <c r="E35" s="0">
-        <v>19.968935446053447</v>
+        <v>20.160506478160269</v>
       </c>
       <c r="F35" s="0">
-        <v>-1.5310645539465533</v>
+        <v>-1.3394935218397315</v>
       </c>
       <c r="G35" s="0">
-        <v>1.5310645539465533</v>
+        <v>1.3394935218397315</v>
       </c>
       <c r="H35" s="0">
-        <v>19.468935446053447</v>
+        <v>19.660506478160269</v>
       </c>
       <c r="I35" s="0">
-        <v>-2.0310645539465533</v>
+        <v>-1.8394935218397315</v>
       </c>
       <c r="J35" s="0">
-        <v>2.0310645539465533</v>
+        <v>1.8394935218397315</v>
       </c>
       <c r="K35" s="0" t="b">
         <v>0</v>
@@ -1980,28 +1980,28 @@
         <v>69</v>
       </c>
       <c r="C36" s="0">
-        <v>756.16819999999996</v>
+        <v>590.04459999999995</v>
       </c>
       <c r="D36" s="0">
         <v>19.5</v>
       </c>
       <c r="E36" s="0">
-        <v>20.00175131271623</v>
+        <v>20.005659223890444</v>
       </c>
       <c r="F36" s="0">
-        <v>0.5017513127162303</v>
+        <v>0.5056592238904436</v>
       </c>
       <c r="G36" s="0">
-        <v>0.5017513127162303</v>
+        <v>0.5056592238904436</v>
       </c>
       <c r="H36" s="0">
-        <v>19.50175131271623</v>
+        <v>19.505659223890444</v>
       </c>
       <c r="I36" s="0">
-        <v>0.0017513127162303022</v>
+        <v>0.0056592238904435987</v>
       </c>
       <c r="J36" s="0">
-        <v>0.0017513127162303022</v>
+        <v>0.0056592238904435987</v>
       </c>
       <c r="K36" s="0" t="b">
         <v>1</v>
@@ -2024,28 +2024,28 @@
         <v>69</v>
       </c>
       <c r="C37" s="0">
-        <v>911.95219999999995</v>
+        <v>724.99620000000004</v>
       </c>
       <c r="D37" s="0">
         <v>25</v>
       </c>
       <c r="E37" s="0">
-        <v>24.426625489247453</v>
+        <v>23.035895932057049</v>
       </c>
       <c r="F37" s="0">
-        <v>-0.5733745107525472</v>
+        <v>-1.9641040679429516</v>
       </c>
       <c r="G37" s="0">
-        <v>0.5733745107525472</v>
+        <v>1.9641040679429516</v>
       </c>
       <c r="H37" s="0">
-        <v>23.926625489247453</v>
+        <v>22.535895932057049</v>
       </c>
       <c r="I37" s="0">
-        <v>-1.0733745107525472</v>
+        <v>-2.4641040679429516</v>
       </c>
       <c r="J37" s="0">
-        <v>1.0733745107525472</v>
+        <v>2.4641040679429516</v>
       </c>
       <c r="K37" s="0" t="b">
         <v>0</v>
@@ -2068,28 +2068,28 @@
         <v>69</v>
       </c>
       <c r="C38" s="0">
-        <v>723.88289999999995</v>
+        <v>600.44100000000003</v>
       </c>
       <c r="D38" s="0">
         <v>19</v>
       </c>
       <c r="E38" s="0">
-        <v>20.813434707609066</v>
+        <v>21.014064337538343</v>
       </c>
       <c r="F38" s="0">
-        <v>1.8134347076090656</v>
+        <v>2.0140643375383434</v>
       </c>
       <c r="G38" s="0">
-        <v>1.8134347076090656</v>
+        <v>2.0140643375383434</v>
       </c>
       <c r="H38" s="0">
-        <v>20.313434707609066</v>
+        <v>20.514064337538343</v>
       </c>
       <c r="I38" s="0">
-        <v>1.3134347076090656</v>
+        <v>1.5140643375383434</v>
       </c>
       <c r="J38" s="0">
-        <v>1.3134347076090656</v>
+        <v>1.5140643375383434</v>
       </c>
       <c r="K38" s="0" t="b">
         <v>1</v>
@@ -2112,28 +2112,28 @@
         <v>69</v>
       </c>
       <c r="C39" s="0">
-        <v>839.00130000000001</v>
+        <v>692.81489999999997</v>
       </c>
       <c r="D39" s="0">
         <v>19</v>
       </c>
       <c r="E39" s="0">
-        <v>20.952593319683157</v>
+        <v>22.447322862856218</v>
       </c>
       <c r="F39" s="0">
-        <v>1.9525933196831566</v>
+        <v>3.4473228628562183</v>
       </c>
       <c r="G39" s="0">
-        <v>1.9525933196831566</v>
+        <v>3.4473228628562183</v>
       </c>
       <c r="H39" s="0">
-        <v>20.452593319683157</v>
+        <v>21.947322862856218</v>
       </c>
       <c r="I39" s="0">
-        <v>1.4525933196831566</v>
+        <v>2.9473228628562183</v>
       </c>
       <c r="J39" s="0">
-        <v>1.4525933196831566</v>
+        <v>2.9473228628562183</v>
       </c>
       <c r="K39" s="0" t="b">
         <v>1</v>
@@ -2156,28 +2156,28 @@
         <v>69</v>
       </c>
       <c r="C40" s="0">
-        <v>1436.3468</v>
+        <v>1193.8898999999999</v>
       </c>
       <c r="D40" s="0">
         <v>21</v>
       </c>
       <c r="E40" s="0">
-        <v>19.799254863605253</v>
+        <v>19.780018032000889</v>
       </c>
       <c r="F40" s="0">
-        <v>-1.2007451363947475</v>
+        <v>-1.2199819679991109</v>
       </c>
       <c r="G40" s="0">
-        <v>1.2007451363947475</v>
+        <v>1.2199819679991109</v>
       </c>
       <c r="H40" s="0">
-        <v>19.299254863605253</v>
+        <v>19.280018032000889</v>
       </c>
       <c r="I40" s="0">
-        <v>-1.7007451363947475</v>
+        <v>-1.7199819679991109</v>
       </c>
       <c r="J40" s="0">
-        <v>1.7007451363947475</v>
+        <v>1.7199819679991109</v>
       </c>
       <c r="K40" s="0" t="b">
         <v>0</v>
@@ -2200,28 +2200,28 @@
         <v>69</v>
       </c>
       <c r="C41" s="0">
-        <v>821.44240000000002</v>
+        <v>666.36320000000001</v>
       </c>
       <c r="D41" s="0">
         <v>20.5</v>
       </c>
       <c r="E41" s="0">
-        <v>21.553387080881478</v>
+        <v>21.467409019029652</v>
       </c>
       <c r="F41" s="0">
-        <v>1.0533870808814783</v>
+        <v>0.96740901902965248</v>
       </c>
       <c r="G41" s="0">
-        <v>1.0533870808814783</v>
+        <v>0.96740901902965248</v>
       </c>
       <c r="H41" s="0">
-        <v>21.053387080881478</v>
+        <v>20.967409019029652</v>
       </c>
       <c r="I41" s="0">
-        <v>0.55338708088147826</v>
+        <v>0.46740901902965248</v>
       </c>
       <c r="J41" s="0">
-        <v>0.55338708088147826</v>
+        <v>0.46740901902965248</v>
       </c>
       <c r="K41" s="0" t="b">
         <v>1</v>
@@ -2244,28 +2244,28 @@
         <v>69</v>
       </c>
       <c r="C42" s="0">
-        <v>417.36169999999999</v>
+        <v>340.92939999999999</v>
       </c>
       <c r="D42" s="0">
         <v>19.25</v>
       </c>
       <c r="E42" s="0">
-        <v>20.61461522823555</v>
+        <v>20.503776424720034</v>
       </c>
       <c r="F42" s="0">
-        <v>1.3646152282355501</v>
+        <v>1.2537764247200336</v>
       </c>
       <c r="G42" s="0">
-        <v>1.3646152282355501</v>
+        <v>1.2537764247200336</v>
       </c>
       <c r="H42" s="0">
-        <v>20.11461522823555</v>
+        <v>20.003776424720034</v>
       </c>
       <c r="I42" s="0">
-        <v>0.86461522823555015</v>
+        <v>0.75377642472003359</v>
       </c>
       <c r="J42" s="0">
-        <v>0.86461522823555015</v>
+        <v>0.75377642472003359</v>
       </c>
       <c r="K42" s="0" t="b">
         <v>1</v>
@@ -2288,28 +2288,28 @@
         <v>69</v>
       </c>
       <c r="C43" s="0">
-        <v>721.39269999999999</v>
+        <v>582.97400000000005</v>
       </c>
       <c r="D43" s="0">
         <v>20</v>
       </c>
       <c r="E43" s="0">
-        <v>20.80153979876177</v>
+        <v>21.011475562361106</v>
       </c>
       <c r="F43" s="0">
-        <v>0.80153979876176962</v>
+        <v>1.011475562361106</v>
       </c>
       <c r="G43" s="0">
-        <v>0.80153979876176962</v>
+        <v>1.011475562361106</v>
       </c>
       <c r="H43" s="0">
-        <v>20.30153979876177</v>
+        <v>20.511475562361106</v>
       </c>
       <c r="I43" s="0">
-        <v>0.30153979876176962</v>
+        <v>0.51147556236110603</v>
       </c>
       <c r="J43" s="0">
-        <v>0.30153979876176962</v>
+        <v>0.51147556236110603</v>
       </c>
       <c r="K43" s="0" t="b">
         <v>1</v>
@@ -2332,28 +2332,28 @@
         <v>69</v>
       </c>
       <c r="C44" s="0">
-        <v>788.81579999999997</v>
+        <v>657.05769999999996</v>
       </c>
       <c r="D44" s="0">
         <v>20</v>
       </c>
       <c r="E44" s="0">
-        <v>20.952593319683157</v>
+        <v>20.914181050969081</v>
       </c>
       <c r="F44" s="0">
-        <v>0.95259331968315664</v>
+        <v>0.91418105096908065</v>
       </c>
       <c r="G44" s="0">
-        <v>0.95259331968315664</v>
+        <v>0.91418105096908065</v>
       </c>
       <c r="H44" s="0">
-        <v>20.452593319683157</v>
+        <v>20.414181050969081</v>
       </c>
       <c r="I44" s="0">
-        <v>0.45259331968315664</v>
+        <v>0.41418105096908064</v>
       </c>
       <c r="J44" s="0">
-        <v>0.45259331968315664</v>
+        <v>0.41418105096908064</v>
       </c>
       <c r="K44" s="0" t="b">
         <v>1</v>
@@ -2376,28 +2376,28 @@
         <v>69</v>
       </c>
       <c r="C45" s="0">
-        <v>697.63379999999995</v>
+        <v>584.81910000000005</v>
       </c>
       <c r="D45" s="0">
         <v>20</v>
       </c>
       <c r="E45" s="0">
-        <v>20.250630153857145</v>
+        <v>20.000060372903125</v>
       </c>
       <c r="F45" s="0">
-        <v>0.25063015385714493</v>
+        <v>6.0372903124772392e-05</v>
       </c>
       <c r="G45" s="0">
-        <v>0.25063015385714493</v>
+        <v>6.0372903124772392e-05</v>
       </c>
       <c r="H45" s="0">
-        <v>19.750630153857145</v>
+        <v>19.500060372903125</v>
       </c>
       <c r="I45" s="0">
-        <v>-0.24936984614285507</v>
+        <v>-0.49993962709687523</v>
       </c>
       <c r="J45" s="0">
-        <v>0.24936984614285507</v>
+        <v>0.49993962709687523</v>
       </c>
       <c r="K45" s="0" t="b">
         <v>0</v>
@@ -2420,28 +2420,28 @@
         <v>69</v>
       </c>
       <c r="C46" s="0">
-        <v>1776.3958</v>
+        <v>1457.3396</v>
       </c>
       <c r="D46" s="0">
         <v>22</v>
       </c>
       <c r="E46" s="0">
-        <v>20.952593319683157</v>
+        <v>22.227827773727821</v>
       </c>
       <c r="F46" s="0">
-        <v>-1.0474066803168434</v>
+        <v>0.22782777372782093</v>
       </c>
       <c r="G46" s="0">
-        <v>1.0474066803168434</v>
+        <v>0.22782777372782093</v>
       </c>
       <c r="H46" s="0">
-        <v>20.452593319683157</v>
+        <v>21.727827773727821</v>
       </c>
       <c r="I46" s="0">
-        <v>-1.5474066803168434</v>
+        <v>-0.27217222627217907</v>
       </c>
       <c r="J46" s="0">
-        <v>1.5474066803168434</v>
+        <v>0.27217222627217907</v>
       </c>
       <c r="K46" s="0" t="b">
         <v>0</v>
@@ -2464,28 +2464,28 @@
         <v>69</v>
       </c>
       <c r="C47" s="0">
-        <v>1708.9593</v>
+        <v>1394.6958999999999</v>
       </c>
       <c r="D47" s="0">
         <v>22</v>
       </c>
       <c r="E47" s="0">
-        <v>20.952593319683157</v>
+        <v>21.560829214787056</v>
       </c>
       <c r="F47" s="0">
-        <v>-1.0474066803168434</v>
+        <v>-0.43917078521294428</v>
       </c>
       <c r="G47" s="0">
-        <v>1.0474066803168434</v>
+        <v>0.43917078521294428</v>
       </c>
       <c r="H47" s="0">
-        <v>20.452593319683157</v>
+        <v>21.060829214787056</v>
       </c>
       <c r="I47" s="0">
-        <v>-1.5474066803168434</v>
+        <v>-0.93917078521294428</v>
       </c>
       <c r="J47" s="0">
-        <v>1.5474066803168434</v>
+        <v>0.93917078521294428</v>
       </c>
       <c r="K47" s="0" t="b">
         <v>0</v>
@@ -2508,28 +2508,28 @@
         <v>69</v>
       </c>
       <c r="C48" s="0">
-        <v>1598.7165</v>
+        <v>1393.5521000000001</v>
       </c>
       <c r="D48" s="0">
         <v>23</v>
       </c>
       <c r="E48" s="0">
-        <v>20.224513868926604</v>
+        <v>21.473763729052905</v>
       </c>
       <c r="F48" s="0">
-        <v>-2.7754861310733965</v>
+        <v>-1.5262362709470949</v>
       </c>
       <c r="G48" s="0">
-        <v>2.7754861310733965</v>
+        <v>1.5262362709470949</v>
       </c>
       <c r="H48" s="0">
-        <v>19.724513868926604</v>
+        <v>20.973763729052905</v>
       </c>
       <c r="I48" s="0">
-        <v>-3.2754861310733965</v>
+        <v>-2.0262362709470949</v>
       </c>
       <c r="J48" s="0">
-        <v>3.2754861310733965</v>
+        <v>2.0262362709470949</v>
       </c>
       <c r="K48" s="0" t="b">
         <v>0</v>
@@ -2552,28 +2552,28 @@
         <v>69</v>
       </c>
       <c r="C49" s="0">
-        <v>1634.0162</v>
+        <v>1328.9452000000001</v>
       </c>
       <c r="D49" s="0">
         <v>21.75</v>
       </c>
       <c r="E49" s="0">
-        <v>20.675252244183458</v>
+        <v>20.477403014567297</v>
       </c>
       <c r="F49" s="0">
-        <v>-1.0747477558165421</v>
+        <v>-1.2725969854327026</v>
       </c>
       <c r="G49" s="0">
-        <v>1.0747477558165421</v>
+        <v>1.2725969854327026</v>
       </c>
       <c r="H49" s="0">
-        <v>20.175252244183458</v>
+        <v>19.977403014567297</v>
       </c>
       <c r="I49" s="0">
-        <v>-1.5747477558165421</v>
+        <v>-1.7725969854327026</v>
       </c>
       <c r="J49" s="0">
-        <v>1.5747477558165421</v>
+        <v>1.7725969854327026</v>
       </c>
       <c r="K49" s="0" t="b">
         <v>0</v>
@@ -2596,28 +2596,28 @@
         <v>69</v>
       </c>
       <c r="C50" s="0">
-        <v>1629.5543</v>
+        <v>1373.3529000000001</v>
       </c>
       <c r="D50" s="0">
         <v>21.5</v>
       </c>
       <c r="E50" s="0">
-        <v>21.046247024774818</v>
+        <v>21.129008959458787</v>
       </c>
       <c r="F50" s="0">
-        <v>-0.4537529752251821</v>
+        <v>-0.37099104054121312</v>
       </c>
       <c r="G50" s="0">
-        <v>0.4537529752251821</v>
+        <v>0.37099104054121312</v>
       </c>
       <c r="H50" s="0">
-        <v>20.546247024774818</v>
+        <v>20.629008959458787</v>
       </c>
       <c r="I50" s="0">
-        <v>-0.9537529752251821</v>
+        <v>-0.87099104054121313</v>
       </c>
       <c r="J50" s="0">
-        <v>0.9537529752251821</v>
+        <v>0.87099104054121313</v>
       </c>
       <c r="K50" s="0" t="b">
         <v>0</v>
@@ -2640,28 +2640,28 @@
         <v>69</v>
       </c>
       <c r="C51" s="0">
-        <v>1482.7846999999999</v>
+        <v>1232.3471999999999</v>
       </c>
       <c r="D51" s="0">
         <v>19.199999999999999</v>
       </c>
       <c r="E51" s="0">
-        <v>20.062203270590331</v>
+        <v>20.079370974948691</v>
       </c>
       <c r="F51" s="0">
-        <v>0.86220327059033153</v>
+        <v>0.87937097494869221</v>
       </c>
       <c r="G51" s="0">
-        <v>0.86220327059033153</v>
+        <v>0.87937097494869221</v>
       </c>
       <c r="H51" s="0">
-        <v>19.562203270590331</v>
+        <v>19.579370974948691</v>
       </c>
       <c r="I51" s="0">
-        <v>0.36220327059033153</v>
+        <v>0.37937097494869221</v>
       </c>
       <c r="J51" s="0">
-        <v>0.36220327059033153</v>
+        <v>0.37937097494869221</v>
       </c>
       <c r="K51" s="0" t="b">
         <v>1</v>
@@ -2684,28 +2684,28 @@
         <v>69</v>
       </c>
       <c r="C52" s="0">
-        <v>1423.4996000000001</v>
+        <v>1151.9466</v>
       </c>
       <c r="D52" s="0">
         <v>17.5</v>
       </c>
       <c r="E52" s="0">
-        <v>19.492338237131236</v>
+        <v>19.972524371484436</v>
       </c>
       <c r="F52" s="0">
-        <v>1.9923382371312357</v>
+        <v>2.4725243714844361</v>
       </c>
       <c r="G52" s="0">
-        <v>1.9923382371312357</v>
+        <v>2.4725243714844361</v>
       </c>
       <c r="H52" s="0">
-        <v>18.992338237131236</v>
+        <v>19.472524371484436</v>
       </c>
       <c r="I52" s="0">
-        <v>1.4923382371312357</v>
+        <v>1.9725243714844361</v>
       </c>
       <c r="J52" s="0">
-        <v>1.4923382371312357</v>
+        <v>1.9725243714844361</v>
       </c>
       <c r="K52" s="0" t="b">
         <v>1</v>
@@ -2728,28 +2728,28 @@
         <v>69</v>
       </c>
       <c r="C53" s="0">
-        <v>1416.4271000000001</v>
+        <v>1179.067</v>
       </c>
       <c r="D53" s="0">
         <v>18.399999999999999</v>
       </c>
       <c r="E53" s="0">
-        <v>19.040377519089628</v>
+        <v>19.070370210915961</v>
       </c>
       <c r="F53" s="0">
-        <v>0.64037751908962903</v>
+        <v>0.67037021091596216</v>
       </c>
       <c r="G53" s="0">
-        <v>0.64037751908962903</v>
+        <v>0.67037021091596216</v>
       </c>
       <c r="H53" s="0">
-        <v>18.540377519089628</v>
+        <v>18.570370210915961</v>
       </c>
       <c r="I53" s="0">
-        <v>0.14037751908962903</v>
+        <v>0.17037021091596216</v>
       </c>
       <c r="J53" s="0">
-        <v>0.14037751908962903</v>
+        <v>0.17037021091596216</v>
       </c>
       <c r="K53" s="0" t="b">
         <v>1</v>
@@ -2772,28 +2772,28 @@
         <v>69</v>
       </c>
       <c r="C54" s="0">
-        <v>1379.5600999999999</v>
+        <v>1127.4477999999999</v>
       </c>
       <c r="D54" s="0">
         <v>19</v>
       </c>
       <c r="E54" s="0">
-        <v>19.86131088735473</v>
+        <v>21.092511877833928</v>
       </c>
       <c r="F54" s="0">
-        <v>0.86131088735472972</v>
+        <v>2.0925118778339282</v>
       </c>
       <c r="G54" s="0">
-        <v>0.86131088735472972</v>
+        <v>2.0925118778339282</v>
       </c>
       <c r="H54" s="0">
-        <v>19.36131088735473</v>
+        <v>20.592511877833928</v>
       </c>
       <c r="I54" s="0">
-        <v>0.36131088735472972</v>
+        <v>1.5925118778339282</v>
       </c>
       <c r="J54" s="0">
-        <v>0.36131088735472972</v>
+        <v>1.5925118778339282</v>
       </c>
       <c r="K54" s="0" t="b">
         <v>1</v>
@@ -2816,28 +2816,28 @@
         <v>69</v>
       </c>
       <c r="C55" s="0">
-        <v>729.85500000000002</v>
+        <v>600.82780000000002</v>
       </c>
       <c r="D55" s="0">
         <v>19.5</v>
       </c>
       <c r="E55" s="0">
-        <v>20.842079057727389</v>
+        <v>21.014121681167985</v>
       </c>
       <c r="F55" s="0">
-        <v>1.3420790577273891</v>
+        <v>1.5141216811679854</v>
       </c>
       <c r="G55" s="0">
-        <v>1.3420790577273891</v>
+        <v>1.5141216811679854</v>
       </c>
       <c r="H55" s="0">
-        <v>20.342079057727389</v>
+        <v>20.514121681167985</v>
       </c>
       <c r="I55" s="0">
-        <v>0.84207905772738911</v>
+        <v>1.0141216811679854</v>
       </c>
       <c r="J55" s="0">
-        <v>0.84207905772738911</v>
+        <v>1.0141216811679854</v>
       </c>
       <c r="K55" s="0" t="b">
         <v>1</v>
@@ -2860,31 +2860,31 @@
         <v>69</v>
       </c>
       <c r="C56" s="0">
-        <v>834.5933</v>
+        <v>727.90769999999998</v>
       </c>
       <c r="D56" s="0">
         <v>20.5</v>
       </c>
       <c r="E56" s="0">
-        <v>20.952593319683157</v>
+        <v>23.616720111350517</v>
       </c>
       <c r="F56" s="0">
-        <v>0.45259331968315664</v>
+        <v>3.1167201113505172</v>
       </c>
       <c r="G56" s="0">
-        <v>0.45259331968315664</v>
+        <v>3.1167201113505172</v>
       </c>
       <c r="H56" s="0">
-        <v>20.452593319683157</v>
+        <v>23.116720111350517</v>
       </c>
       <c r="I56" s="0">
-        <v>-0.047406680316843364</v>
+        <v>2.6167201113505172</v>
       </c>
       <c r="J56" s="0">
-        <v>0.047406680316843364</v>
+        <v>2.6167201113505172</v>
       </c>
       <c r="K56" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="0">
         <v>3</v>
@@ -2904,28 +2904,28 @@
         <v>69</v>
       </c>
       <c r="C57" s="0">
-        <v>796.79129999999998</v>
+        <v>646.02480000000003</v>
       </c>
       <c r="D57" s="0">
         <v>21</v>
       </c>
       <c r="E57" s="0">
-        <v>20.493315418312719</v>
+        <v>20.43088960097548</v>
       </c>
       <c r="F57" s="0">
-        <v>-0.50668458168728137</v>
+        <v>-0.56911039902452032</v>
       </c>
       <c r="G57" s="0">
-        <v>0.50668458168728137</v>
+        <v>0.56911039902452032</v>
       </c>
       <c r="H57" s="0">
-        <v>19.993315418312719</v>
+        <v>19.93088960097548</v>
       </c>
       <c r="I57" s="0">
-        <v>-1.0066845816872814</v>
+        <v>-1.0691103990245203</v>
       </c>
       <c r="J57" s="0">
-        <v>1.0066845816872814</v>
+        <v>1.0691103990245203</v>
       </c>
       <c r="K57" s="0" t="b">
         <v>0</v>
@@ -2948,28 +2948,28 @@
         <v>69</v>
       </c>
       <c r="C58" s="0">
-        <v>1335.2448999999999</v>
+        <v>1120.8548000000001</v>
       </c>
       <c r="D58" s="0">
         <v>23.5</v>
       </c>
       <c r="E58" s="0">
-        <v>18.122186529833378</v>
+        <v>18.2728288694931</v>
       </c>
       <c r="F58" s="0">
-        <v>-5.3778134701666218</v>
+        <v>-5.2271711305068998</v>
       </c>
       <c r="G58" s="0">
-        <v>5.3778134701666218</v>
+        <v>5.2271711305068998</v>
       </c>
       <c r="H58" s="0">
-        <v>17.622186529833378</v>
+        <v>17.7728288694931</v>
       </c>
       <c r="I58" s="0">
-        <v>-5.8778134701666218</v>
+        <v>-5.7271711305068998</v>
       </c>
       <c r="J58" s="0">
-        <v>5.8778134701666218</v>
+        <v>5.7271711305068998</v>
       </c>
       <c r="K58" s="0" t="b">
         <v>0</v>
@@ -2992,28 +2992,28 @@
         <v>69</v>
       </c>
       <c r="C59" s="0">
-        <v>831.26670000000001</v>
+        <v>665.77250000000004</v>
       </c>
       <c r="D59" s="0">
         <v>20.5</v>
       </c>
       <c r="E59" s="0">
-        <v>21.607017223234109</v>
+        <v>21.463780422255688</v>
       </c>
       <c r="F59" s="0">
-        <v>1.1070172232341093</v>
+        <v>0.96378042225568805</v>
       </c>
       <c r="G59" s="0">
-        <v>1.1070172232341093</v>
+        <v>0.96378042225568805</v>
       </c>
       <c r="H59" s="0">
-        <v>21.107017223234109</v>
+        <v>20.963780422255688</v>
       </c>
       <c r="I59" s="0">
-        <v>0.60701722323410934</v>
+        <v>0.46378042225568805</v>
       </c>
       <c r="J59" s="0">
-        <v>0.60701722323410934</v>
+        <v>0.46378042225568805</v>
       </c>
       <c r="K59" s="0" t="b">
         <v>1</v>
@@ -3036,28 +3036,28 @@
         <v>69</v>
       </c>
       <c r="C60" s="0">
-        <v>783.88189999999997</v>
+        <v>695.50199999999995</v>
       </c>
       <c r="D60" s="0">
         <v>21.5</v>
       </c>
       <c r="E60" s="0">
-        <v>21.106591160636267</v>
+        <v>21.028176154091835</v>
       </c>
       <c r="F60" s="0">
-        <v>-0.39340883936373317</v>
+        <v>-0.4718238459081654</v>
       </c>
       <c r="G60" s="0">
-        <v>0.39340883936373317</v>
+        <v>0.4718238459081654</v>
       </c>
       <c r="H60" s="0">
-        <v>20.606591160636267</v>
+        <v>20.528176154091835</v>
       </c>
       <c r="I60" s="0">
-        <v>-0.89340883936373316</v>
+        <v>-0.9718238459081654</v>
       </c>
       <c r="J60" s="0">
-        <v>0.89340883936373316</v>
+        <v>0.9718238459081654</v>
       </c>
       <c r="K60" s="0" t="b">
         <v>0</v>
@@ -3080,31 +3080,31 @@
         <v>69</v>
       </c>
       <c r="C61" s="0">
-        <v>788.45299999999998</v>
+        <v>639.4633</v>
       </c>
       <c r="D61" s="0">
         <v>20</v>
       </c>
       <c r="E61" s="0">
-        <v>20.541211560684232</v>
+        <v>20.435450032599146</v>
       </c>
       <c r="F61" s="0">
-        <v>0.54121156068423204</v>
+        <v>0.43545003259914594</v>
       </c>
       <c r="G61" s="0">
-        <v>0.54121156068423204</v>
+        <v>0.43545003259914594</v>
       </c>
       <c r="H61" s="0">
-        <v>20.041211560684232</v>
+        <v>19.935450032599146</v>
       </c>
       <c r="I61" s="0">
-        <v>0.04121156068423204</v>
+        <v>-0.064549967400854058</v>
       </c>
       <c r="J61" s="0">
-        <v>0.04121156068423204</v>
+        <v>0.064549967400854058</v>
       </c>
       <c r="K61" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="0">
         <v>4</v>
@@ -3124,28 +3124,28 @@
         <v>69</v>
       </c>
       <c r="C62" s="0">
-        <v>835.44200000000001</v>
+        <v>699.43420000000003</v>
       </c>
       <c r="D62" s="0">
         <v>23</v>
       </c>
       <c r="E62" s="0">
-        <v>21.815734254813655</v>
+        <v>22.160118870267631</v>
       </c>
       <c r="F62" s="0">
-        <v>-1.1842657451863445</v>
+        <v>-0.83988112973236895</v>
       </c>
       <c r="G62" s="0">
-        <v>1.1842657451863445</v>
+        <v>0.83988112973236895</v>
       </c>
       <c r="H62" s="0">
-        <v>21.315734254813655</v>
+        <v>21.660118870267631</v>
       </c>
       <c r="I62" s="0">
-        <v>-1.6842657451863445</v>
+        <v>-1.339881129732369</v>
       </c>
       <c r="J62" s="0">
-        <v>1.6842657451863445</v>
+        <v>1.339881129732369</v>
       </c>
       <c r="K62" s="0" t="b">
         <v>0</v>
@@ -3168,31 +3168,31 @@
         <v>69</v>
       </c>
       <c r="C63" s="0">
-        <v>823.30409999999995</v>
+        <v>683.36609999999996</v>
       </c>
       <c r="D63" s="0">
         <v>21.5</v>
       </c>
       <c r="E63" s="0">
-        <v>20.952593319683157</v>
+        <v>22.033198673861211</v>
       </c>
       <c r="F63" s="0">
-        <v>-0.54740668031684336</v>
+        <v>0.53319867386121089</v>
       </c>
       <c r="G63" s="0">
-        <v>0.54740668031684336</v>
+        <v>0.53319867386121089</v>
       </c>
       <c r="H63" s="0">
-        <v>20.452593319683157</v>
+        <v>21.533198673861211</v>
       </c>
       <c r="I63" s="0">
-        <v>-1.0474066803168434</v>
+        <v>0.033198673861210892</v>
       </c>
       <c r="J63" s="0">
-        <v>1.0474066803168434</v>
+        <v>0.033198673861210892</v>
       </c>
       <c r="K63" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="0">
         <v>3</v>
@@ -3212,28 +3212,28 @@
         <v>69</v>
       </c>
       <c r="C64" s="0">
-        <v>514.31870000000004</v>
+        <v>421.81869999999998</v>
       </c>
       <c r="D64" s="0">
         <v>22.5</v>
       </c>
       <c r="E64" s="0">
-        <v>19.960664350319469</v>
+        <v>20.987669544358823</v>
       </c>
       <c r="F64" s="0">
-        <v>-2.5393356496805311</v>
+        <v>-1.5123304556411767</v>
       </c>
       <c r="G64" s="0">
-        <v>2.5393356496805311</v>
+        <v>1.5123304556411767</v>
       </c>
       <c r="H64" s="0">
-        <v>19.460664350319469</v>
+        <v>20.487669544358823</v>
       </c>
       <c r="I64" s="0">
-        <v>-3.0393356496805311</v>
+        <v>-2.0123304556411767</v>
       </c>
       <c r="J64" s="0">
-        <v>3.0393356496805311</v>
+        <v>2.0123304556411767</v>
       </c>
       <c r="K64" s="0" t="b">
         <v>0</v>
@@ -3256,28 +3256,28 @@
         <v>69</v>
       </c>
       <c r="C65" s="0">
-        <v>718.11779999999999</v>
+        <v>594.92830000000004</v>
       </c>
       <c r="D65" s="0">
         <v>19.25</v>
       </c>
       <c r="E65" s="0">
-        <v>20.992318441200375</v>
+        <v>21.028520638478124</v>
       </c>
       <c r="F65" s="0">
-        <v>1.7423184412003749</v>
+        <v>1.778520638478124</v>
       </c>
       <c r="G65" s="0">
-        <v>1.7423184412003749</v>
+        <v>1.778520638478124</v>
       </c>
       <c r="H65" s="0">
-        <v>20.492318441200375</v>
+        <v>20.528520638478124</v>
       </c>
       <c r="I65" s="0">
-        <v>1.2423184412003749</v>
+        <v>1.278520638478124</v>
       </c>
       <c r="J65" s="0">
-        <v>1.2423184412003749</v>
+        <v>1.278520638478124</v>
       </c>
       <c r="K65" s="0" t="b">
         <v>1</v>
@@ -3300,28 +3300,28 @@
         <v>69</v>
       </c>
       <c r="C66" s="0">
-        <v>886.21339999999998</v>
+        <v>672.91949999999997</v>
       </c>
       <c r="D66" s="0">
         <v>23.5</v>
       </c>
       <c r="E66" s="0">
-        <v>23.412502649490733</v>
+        <v>20.971199148829047</v>
       </c>
       <c r="F66" s="0">
-        <v>-0.08749735050926688</v>
+        <v>-2.5288008511709528</v>
       </c>
       <c r="G66" s="0">
-        <v>0.08749735050926688</v>
+        <v>2.5288008511709528</v>
       </c>
       <c r="H66" s="0">
-        <v>22.912502649490733</v>
+        <v>20.471199148829047</v>
       </c>
       <c r="I66" s="0">
-        <v>-0.58749735050926688</v>
+        <v>-3.0288008511709528</v>
       </c>
       <c r="J66" s="0">
-        <v>0.58749735050926688</v>
+        <v>3.0288008511709528</v>
       </c>
       <c r="K66" s="0" t="b">
         <v>0</v>
@@ -3344,28 +3344,28 @@
         <v>69</v>
       </c>
       <c r="C67" s="0">
-        <v>768.54010000000005</v>
+        <v>637.33479999999997</v>
       </c>
       <c r="D67" s="0">
         <v>21.5</v>
       </c>
       <c r="E67" s="0">
-        <v>20.089038635377594</v>
+        <v>20.309632814620933</v>
       </c>
       <c r="F67" s="0">
-        <v>-1.4109613646224055</v>
+        <v>-1.1903671853790669</v>
       </c>
       <c r="G67" s="0">
-        <v>1.4109613646224055</v>
+        <v>1.1903671853790669</v>
       </c>
       <c r="H67" s="0">
-        <v>19.589038635377594</v>
+        <v>19.809632814620933</v>
       </c>
       <c r="I67" s="0">
-        <v>-1.9109613646224055</v>
+        <v>-1.6903671853790669</v>
       </c>
       <c r="J67" s="0">
-        <v>1.9109613646224055</v>
+        <v>1.6903671853790669</v>
       </c>
       <c r="K67" s="0" t="b">
         <v>0</v>
@@ -3388,28 +3388,28 @@
         <v>69</v>
       </c>
       <c r="C68" s="0">
-        <v>1074.7814000000001</v>
+        <v>879.03800000000001</v>
       </c>
       <c r="D68" s="0">
         <v>19</v>
       </c>
       <c r="E68" s="0">
-        <v>28.967961936420327</v>
+        <v>25.660706819621439</v>
       </c>
       <c r="F68" s="0">
-        <v>9.9679619364203269</v>
+        <v>6.6607068196214385</v>
       </c>
       <c r="G68" s="0">
-        <v>9.9679619364203269</v>
+        <v>6.6607068196214385</v>
       </c>
       <c r="H68" s="0">
-        <v>28.467961936420327</v>
+        <v>25.160706819621439</v>
       </c>
       <c r="I68" s="0">
-        <v>9.4679619364203269</v>
+        <v>6.1607068196214385</v>
       </c>
       <c r="J68" s="0">
-        <v>9.4679619364203269</v>
+        <v>6.1607068196214385</v>
       </c>
       <c r="K68" s="0" t="b">
         <v>1</v>
@@ -3470,16 +3470,16 @@
         <v>85</v>
       </c>
       <c r="B2" s="0">
-        <v>1.321</v>
+        <v>1.313</v>
       </c>
       <c r="C2" s="0">
-        <v>1.885</v>
+        <v>1.7569999999999999</v>
       </c>
       <c r="D2" s="0">
-        <v>0.10100000000000001</v>
+        <v>0.122</v>
       </c>
       <c r="E2" s="0">
-        <v>0.056000000000000001</v>
+        <v>0.042999999999999997</v>
       </c>
       <c r="F2" s="0"/>
       <c r="G2" s="0"/>
@@ -3489,22 +3489,22 @@
         <v>86</v>
       </c>
       <c r="B3" s="0">
-        <v>0.057000000000000002</v>
+        <v>0.042000000000000003</v>
       </c>
       <c r="C3" s="0">
-        <v>0.14299999999999999</v>
+        <v>0.058000000000000003</v>
       </c>
       <c r="D3" s="0">
-        <v>0.045999999999999999</v>
+        <v>0.039</v>
       </c>
       <c r="E3" s="0">
-        <v>0.055</v>
+        <v>0.067000000000000004</v>
       </c>
       <c r="F3" s="0">
-        <v>4.7999999999999998</v>
+        <v>4.2000000000000002</v>
       </c>
       <c r="G3" s="0">
-        <v>1.7</v>
+        <v>2.1000000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -3523,18 +3523,18 @@
         <v>88</v>
       </c>
       <c r="B5" s="0">
-        <v>1.3560000000000001</v>
+        <v>1.337</v>
       </c>
       <c r="C5" s="0"/>
       <c r="D5" s="0"/>
       <c r="E5" s="0">
-        <v>-0.44400000000000001</v>
+        <v>-0.45700000000000002</v>
       </c>
       <c r="F5" s="0">
-        <v>49.700000000000003</v>
+        <v>50.700000000000003</v>
       </c>
       <c r="G5" s="0">
-        <v>41.5</v>
+        <v>41.299999999999997</v>
       </c>
     </row>
     <row r="6">
@@ -3542,16 +3542,16 @@
         <v>89</v>
       </c>
       <c r="B6" s="0">
-        <v>1.476</v>
+        <v>1.474</v>
       </c>
       <c r="C6" s="0">
         <v>1.8260000000000001</v>
       </c>
       <c r="D6" s="0">
-        <v>0.039</v>
+        <v>0.035999999999999997</v>
       </c>
       <c r="E6" s="0">
-        <v>0.0040000000000000001</v>
+        <v>0.0030000000000000001</v>
       </c>
       <c r="F6" s="0"/>
       <c r="G6" s="0"/>
@@ -3561,12 +3561,12 @@
         <v>90</v>
       </c>
       <c r="B7" s="0">
-        <v>1.4850000000000001</v>
+        <v>1.484</v>
       </c>
       <c r="C7" s="0"/>
       <c r="D7" s="0"/>
       <c r="E7" s="0">
-        <v>-0.496</v>
+        <v>-0.497</v>
       </c>
       <c r="F7" s="0">
         <v>37.299999999999997</v>
@@ -3652,7 +3652,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="true"/>
-    <col min="2" max="2" width="7.7109375" customWidth="true"/>
+    <col min="2" max="2" width="5.7109375" customWidth="true"/>
     <col min="3" max="3" width="6.7109375" customWidth="true"/>
     <col min="4" max="4" width="6.7109375" customWidth="true"/>
     <col min="5" max="5" width="4.5703125" customWidth="true"/>
@@ -3680,13 +3680,13 @@
         <v>111</v>
       </c>
       <c r="B2" s="0">
-        <v>20.760200000000001</v>
+        <v>20.739999999999999</v>
       </c>
       <c r="C2" s="0">
-        <v>0.60060000000000002</v>
+        <v>0.59970000000000001</v>
       </c>
       <c r="D2" s="0">
-        <v>34.567</v>
+        <v>34.582999999999999</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
@@ -3697,16 +3697,16 @@
         <v>112</v>
       </c>
       <c r="B3" s="0">
-        <v>0.00020000000000000001</v>
+        <v>0.00029999999999999997</v>
       </c>
       <c r="C3" s="0">
-        <v>0.00059999999999999995</v>
+        <v>0.00069999999999999999</v>
       </c>
       <c r="D3" s="0">
-        <v>0.40500000000000003</v>
+        <v>0.442</v>
       </c>
       <c r="E3" s="0">
-        <v>0.68659999999999999</v>
+        <v>0.65980000000000005</v>
       </c>
     </row>
   </sheetData>

--- a/預測結果與評估指標_kfold_mask幾何.xlsx
+++ b/預測結果與評估指標_kfold_mask幾何.xlsx
@@ -421,8 +421,8 @@
     <col min="3" max="3" width="13.42578125" customWidth="true"/>
     <col min="4" max="4" width="14.7109375" customWidth="true"/>
     <col min="5" max="5" width="14.7109375" customWidth="true"/>
-    <col min="6" max="6" width="15.5703125" customWidth="true"/>
-    <col min="7" max="7" width="15.5703125" customWidth="true"/>
+    <col min="6" max="6" width="13.7109375" customWidth="true"/>
+    <col min="7" max="7" width="14.7109375" customWidth="true"/>
     <col min="8" max="8" width="17" customWidth="true"/>
     <col min="9" max="9" width="20.5703125" customWidth="true"/>
     <col min="10" max="10" width="21.5703125" customWidth="true"/>
@@ -484,28 +484,28 @@
         <v>69</v>
       </c>
       <c r="C2" s="0">
-        <v>403.60700000000003</v>
+        <v>405.481</v>
       </c>
       <c r="D2" s="0">
         <v>23</v>
       </c>
       <c r="E2" s="0">
-        <v>20.98498961846407</v>
+        <v>19.935902928847248</v>
       </c>
       <c r="F2" s="0">
-        <v>-2.0150103815359302</v>
+        <v>-3.0640970711527515</v>
       </c>
       <c r="G2" s="0">
-        <v>2.0150103815359302</v>
+        <v>3.0640970711527515</v>
       </c>
       <c r="H2" s="0">
-        <v>20.48498961846407</v>
+        <v>19.435902928847248</v>
       </c>
       <c r="I2" s="0">
-        <v>-2.5150103815359302</v>
+        <v>-3.5640970711527515</v>
       </c>
       <c r="J2" s="0">
-        <v>2.5150103815359302</v>
+        <v>3.5640970711527515</v>
       </c>
       <c r="K2" s="0" t="b">
         <v>0</v>
@@ -528,28 +528,28 @@
         <v>69</v>
       </c>
       <c r="C3" s="0">
-        <v>605.62289999999996</v>
+        <v>605.36530000000005</v>
       </c>
       <c r="D3" s="0">
         <v>21</v>
       </c>
       <c r="E3" s="0">
-        <v>21.092996503984867</v>
+        <v>21.252511002595075</v>
       </c>
       <c r="F3" s="0">
-        <v>0.092996503984867473</v>
+        <v>0.25251100259507453</v>
       </c>
       <c r="G3" s="0">
-        <v>0.092996503984867473</v>
+        <v>0.25251100259507453</v>
       </c>
       <c r="H3" s="0">
-        <v>20.592996503984867</v>
+        <v>20.752511002595075</v>
       </c>
       <c r="I3" s="0">
-        <v>-0.40700349601513253</v>
+        <v>-0.24748899740492547</v>
       </c>
       <c r="J3" s="0">
-        <v>0.40700349601513253</v>
+        <v>0.24748899740492547</v>
       </c>
       <c r="K3" s="0" t="b">
         <v>0</v>
@@ -572,28 +572,28 @@
         <v>69</v>
       </c>
       <c r="C4" s="0">
-        <v>773.59109999999998</v>
+        <v>740.86210000000005</v>
       </c>
       <c r="D4" s="0">
         <v>23.5</v>
       </c>
       <c r="E4" s="0">
-        <v>24.148057825206287</v>
+        <v>24.272973495587049</v>
       </c>
       <c r="F4" s="0">
-        <v>0.64805782520628696</v>
+        <v>0.77297349558704909</v>
       </c>
       <c r="G4" s="0">
-        <v>0.64805782520628696</v>
+        <v>0.77297349558704909</v>
       </c>
       <c r="H4" s="0">
-        <v>23.648057825206287</v>
+        <v>23.772973495587049</v>
       </c>
       <c r="I4" s="0">
-        <v>0.14805782520628696</v>
+        <v>0.27297349558704909</v>
       </c>
       <c r="J4" s="0">
-        <v>0.14805782520628696</v>
+        <v>0.27297349558704909</v>
       </c>
       <c r="K4" s="0" t="b">
         <v>1</v>
@@ -616,28 +616,28 @@
         <v>69</v>
       </c>
       <c r="C5" s="0">
-        <v>579.42529999999999</v>
+        <v>580.86249999999996</v>
       </c>
       <c r="D5" s="0">
         <v>21</v>
       </c>
       <c r="E5" s="0">
-        <v>21.010949789759543</v>
+        <v>20.769624327526259</v>
       </c>
       <c r="F5" s="0">
-        <v>0.010949789759543194</v>
+        <v>-0.23037567247374113</v>
       </c>
       <c r="G5" s="0">
-        <v>0.010949789759543194</v>
+        <v>0.23037567247374113</v>
       </c>
       <c r="H5" s="0">
-        <v>20.510949789759543</v>
+        <v>20.269624327526259</v>
       </c>
       <c r="I5" s="0">
-        <v>-0.48905021024045681</v>
+        <v>-0.73037567247374113</v>
       </c>
       <c r="J5" s="0">
-        <v>0.48905021024045681</v>
+        <v>0.73037567247374113</v>
       </c>
       <c r="K5" s="0" t="b">
         <v>0</v>
@@ -660,28 +660,28 @@
         <v>69</v>
       </c>
       <c r="C6" s="0">
-        <v>632.08730000000003</v>
+        <v>620.73389999999995</v>
       </c>
       <c r="D6" s="0">
         <v>21.5</v>
       </c>
       <c r="E6" s="0">
-        <v>21.255370603035321</v>
+        <v>21.252510489409868</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.24462939696467956</v>
+        <v>-0.2474895105901318</v>
       </c>
       <c r="G6" s="0">
-        <v>0.24462939696467956</v>
+        <v>0.2474895105901318</v>
       </c>
       <c r="H6" s="0">
-        <v>20.755370603035321</v>
+        <v>20.752510489409868</v>
       </c>
       <c r="I6" s="0">
-        <v>-0.74462939696467956</v>
+        <v>-0.7474895105901318</v>
       </c>
       <c r="J6" s="0">
-        <v>0.74462939696467956</v>
+        <v>0.7474895105901318</v>
       </c>
       <c r="K6" s="0" t="b">
         <v>0</v>
@@ -704,28 +704,28 @@
         <v>69</v>
       </c>
       <c r="C7" s="0">
-        <v>720.98979999999995</v>
+        <v>711.67399999999998</v>
       </c>
       <c r="D7" s="0">
         <v>22</v>
       </c>
       <c r="E7" s="0">
-        <v>21.03196546052645</v>
+        <v>21.505718855212212</v>
       </c>
       <c r="F7" s="0">
-        <v>-0.96803453947354967</v>
+        <v>-0.49428114478778795</v>
       </c>
       <c r="G7" s="0">
-        <v>0.96803453947354967</v>
+        <v>0.49428114478778795</v>
       </c>
       <c r="H7" s="0">
-        <v>20.53196546052645</v>
+        <v>21.005718855212212</v>
       </c>
       <c r="I7" s="0">
-        <v>-1.4680345394735497</v>
+        <v>-0.99428114478778795</v>
       </c>
       <c r="J7" s="0">
-        <v>1.4680345394735497</v>
+        <v>0.99428114478778795</v>
       </c>
       <c r="K7" s="0" t="b">
         <v>0</v>
@@ -748,28 +748,28 @@
         <v>69</v>
       </c>
       <c r="C8" s="0">
-        <v>758.05489999999998</v>
+        <v>757.66719999999998</v>
       </c>
       <c r="D8" s="0">
         <v>25</v>
       </c>
       <c r="E8" s="0">
-        <v>24.043822955457799</v>
+        <v>25.365430369600638</v>
       </c>
       <c r="F8" s="0">
-        <v>-0.95617704454220132</v>
+        <v>0.36543036960063802</v>
       </c>
       <c r="G8" s="0">
-        <v>0.95617704454220132</v>
+        <v>0.36543036960063802</v>
       </c>
       <c r="H8" s="0">
-        <v>23.543822955457799</v>
+        <v>24.865430369600638</v>
       </c>
       <c r="I8" s="0">
-        <v>-1.4561770445422013</v>
+        <v>-0.13456963039936198</v>
       </c>
       <c r="J8" s="0">
-        <v>1.4561770445422013</v>
+        <v>0.13456963039936198</v>
       </c>
       <c r="K8" s="0" t="b">
         <v>0</v>
@@ -792,31 +792,31 @@
         <v>69</v>
       </c>
       <c r="C9" s="0">
-        <v>400.07780000000002</v>
+        <v>390.43310000000002</v>
       </c>
       <c r="D9" s="0">
         <v>20.5</v>
       </c>
       <c r="E9" s="0">
-        <v>20.07924866119598</v>
+        <v>21.252518179721982</v>
       </c>
       <c r="F9" s="0">
-        <v>-0.42075133880402049</v>
+        <v>0.75251817972198154</v>
       </c>
       <c r="G9" s="0">
-        <v>0.42075133880402049</v>
+        <v>0.75251817972198154</v>
       </c>
       <c r="H9" s="0">
-        <v>19.57924866119598</v>
+        <v>20.752518179721982</v>
       </c>
       <c r="I9" s="0">
-        <v>-0.92075133880402049</v>
+        <v>0.25251817972198154</v>
       </c>
       <c r="J9" s="0">
-        <v>0.92075133880402049</v>
+        <v>0.25251817972198154</v>
       </c>
       <c r="K9" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="0">
         <v>2</v>
@@ -836,28 +836,28 @@
         <v>69</v>
       </c>
       <c r="C10" s="0">
-        <v>1283.9973</v>
+        <v>1263.4103</v>
       </c>
       <c r="D10" s="0">
         <v>21</v>
       </c>
       <c r="E10" s="0">
-        <v>20.627113766277876</v>
+        <v>21.252489030057379</v>
       </c>
       <c r="F10" s="0">
-        <v>-0.37288623372212371</v>
+        <v>0.25248903005737944</v>
       </c>
       <c r="G10" s="0">
-        <v>0.37288623372212371</v>
+        <v>0.25248903005737944</v>
       </c>
       <c r="H10" s="0">
-        <v>20.127113766277876</v>
+        <v>20.752489030057379</v>
       </c>
       <c r="I10" s="0">
-        <v>-0.87288623372212371</v>
+        <v>-0.24751096994262056</v>
       </c>
       <c r="J10" s="0">
-        <v>0.87288623372212371</v>
+        <v>0.24751096994262056</v>
       </c>
       <c r="K10" s="0" t="b">
         <v>0</v>
@@ -880,28 +880,28 @@
         <v>69</v>
       </c>
       <c r="C11" s="0">
-        <v>317.95030000000003</v>
+        <v>319.74869999999999</v>
       </c>
       <c r="D11" s="0">
         <v>18</v>
       </c>
       <c r="E11" s="0">
-        <v>20.972418057343077</v>
+        <v>19.644754579282829</v>
       </c>
       <c r="F11" s="0">
-        <v>2.9724180573430772</v>
+        <v>1.6447545792828287</v>
       </c>
       <c r="G11" s="0">
-        <v>2.9724180573430772</v>
+        <v>1.6447545792828287</v>
       </c>
       <c r="H11" s="0">
-        <v>20.472418057343077</v>
+        <v>19.144754579282829</v>
       </c>
       <c r="I11" s="0">
-        <v>2.4724180573430772</v>
+        <v>1.1447545792828286</v>
       </c>
       <c r="J11" s="0">
-        <v>2.4724180573430772</v>
+        <v>1.1447545792828286</v>
       </c>
       <c r="K11" s="0" t="b">
         <v>1</v>
@@ -924,28 +924,28 @@
         <v>69</v>
       </c>
       <c r="C12" s="0">
-        <v>750.11170000000004</v>
+        <v>718.36379999999997</v>
       </c>
       <c r="D12" s="0">
         <v>25</v>
       </c>
       <c r="E12" s="0">
-        <v>23.872563626712871</v>
+        <v>23.463836719190645</v>
       </c>
       <c r="F12" s="0">
-        <v>-1.1274363732871286</v>
+        <v>-1.5361632808093546</v>
       </c>
       <c r="G12" s="0">
-        <v>1.1274363732871286</v>
+        <v>1.5361632808093546</v>
       </c>
       <c r="H12" s="0">
-        <v>23.372563626712871</v>
+        <v>22.963836719190645</v>
       </c>
       <c r="I12" s="0">
-        <v>-1.6274363732871286</v>
+        <v>-2.0361632808093546</v>
       </c>
       <c r="J12" s="0">
-        <v>1.6274363732871286</v>
+        <v>2.0361632808093546</v>
       </c>
       <c r="K12" s="0" t="b">
         <v>0</v>
@@ -968,28 +968,28 @@
         <v>69</v>
       </c>
       <c r="C13" s="0">
-        <v>675.26099999999997</v>
+        <v>669.91160000000002</v>
       </c>
       <c r="D13" s="0">
         <v>22.5</v>
       </c>
       <c r="E13" s="0">
-        <v>21.672327173166902</v>
+        <v>21.452739801485873</v>
       </c>
       <c r="F13" s="0">
-        <v>-0.82767282683309773</v>
+        <v>-1.0472601985141274</v>
       </c>
       <c r="G13" s="0">
-        <v>0.82767282683309773</v>
+        <v>1.0472601985141274</v>
       </c>
       <c r="H13" s="0">
-        <v>21.172327173166902</v>
+        <v>20.952739801485873</v>
       </c>
       <c r="I13" s="0">
-        <v>-1.3276728268330977</v>
+        <v>-1.5472601985141274</v>
       </c>
       <c r="J13" s="0">
-        <v>1.3276728268330977</v>
+        <v>1.5472601985141274</v>
       </c>
       <c r="K13" s="0" t="b">
         <v>0</v>
@@ -1012,28 +1012,28 @@
         <v>69</v>
       </c>
       <c r="C14" s="0">
-        <v>674.45989999999995</v>
+        <v>672.01459999999997</v>
       </c>
       <c r="D14" s="0">
         <v>20.5</v>
       </c>
       <c r="E14" s="0">
-        <v>21.337548916327187</v>
+        <v>21.385279439864107</v>
       </c>
       <c r="F14" s="0">
-        <v>0.83754891632718653</v>
+        <v>0.88527943986410662</v>
       </c>
       <c r="G14" s="0">
-        <v>0.83754891632718653</v>
+        <v>0.88527943986410662</v>
       </c>
       <c r="H14" s="0">
-        <v>20.837548916327187</v>
+        <v>20.885279439864107</v>
       </c>
       <c r="I14" s="0">
-        <v>0.33754891632718653</v>
+        <v>0.38527943986410662</v>
       </c>
       <c r="J14" s="0">
-        <v>0.33754891632718653</v>
+        <v>0.38527943986410662</v>
       </c>
       <c r="K14" s="0" t="b">
         <v>1</v>
@@ -1056,28 +1056,28 @@
         <v>69</v>
       </c>
       <c r="C15" s="0">
-        <v>583.64300000000003</v>
+        <v>585.0598</v>
       </c>
       <c r="D15" s="0">
         <v>19.5</v>
       </c>
       <c r="E15" s="0">
-        <v>20.066072873466098</v>
+        <v>20.004821829554743</v>
       </c>
       <c r="F15" s="0">
-        <v>0.5660728734660978</v>
+        <v>0.50482182955474286</v>
       </c>
       <c r="G15" s="0">
-        <v>0.5660728734660978</v>
+        <v>0.50482182955474286</v>
       </c>
       <c r="H15" s="0">
-        <v>19.566072873466098</v>
+        <v>19.504821829554743</v>
       </c>
       <c r="I15" s="0">
-        <v>0.066072873466097804</v>
+        <v>0.0048218295547428625</v>
       </c>
       <c r="J15" s="0">
-        <v>0.066072873466097804</v>
+        <v>0.0048218295547428625</v>
       </c>
       <c r="K15" s="0" t="b">
         <v>1</v>
@@ -1100,28 +1100,28 @@
         <v>69</v>
       </c>
       <c r="C16" s="0">
-        <v>617.06880000000001</v>
+        <v>618.17600000000004</v>
       </c>
       <c r="D16" s="0">
         <v>19.5</v>
       </c>
       <c r="E16" s="0">
-        <v>21.162821885280515</v>
+        <v>21.252510574822662</v>
       </c>
       <c r="F16" s="0">
-        <v>1.6628218852805148</v>
+        <v>1.7525105748226615</v>
       </c>
       <c r="G16" s="0">
-        <v>1.6628218852805148</v>
+        <v>1.7525105748226615</v>
       </c>
       <c r="H16" s="0">
-        <v>20.662821885280515</v>
+        <v>20.752510574822662</v>
       </c>
       <c r="I16" s="0">
-        <v>1.1628218852805148</v>
+        <v>1.2525105748226615</v>
       </c>
       <c r="J16" s="0">
-        <v>1.1628218852805148</v>
+        <v>1.2525105748226615</v>
       </c>
       <c r="K16" s="0" t="b">
         <v>1</v>
@@ -1144,28 +1144,28 @@
         <v>69</v>
       </c>
       <c r="C17" s="0">
-        <v>1130.2846</v>
+        <v>1122.4987000000001</v>
       </c>
       <c r="D17" s="0">
         <v>18.5</v>
       </c>
       <c r="E17" s="0">
-        <v>18.406758654163408</v>
+        <v>18.713583829867734</v>
       </c>
       <c r="F17" s="0">
-        <v>-0.09324134583659216</v>
+        <v>0.2135838298677335</v>
       </c>
       <c r="G17" s="0">
-        <v>0.09324134583659216</v>
+        <v>0.2135838298677335</v>
       </c>
       <c r="H17" s="0">
-        <v>17.906758654163408</v>
+        <v>18.213583829867734</v>
       </c>
       <c r="I17" s="0">
-        <v>-0.59324134583659216</v>
+        <v>-0.2864161701322665</v>
       </c>
       <c r="J17" s="0">
-        <v>0.59324134583659216</v>
+        <v>0.2864161701322665</v>
       </c>
       <c r="K17" s="0" t="b">
         <v>0</v>
@@ -1188,28 +1188,28 @@
         <v>69</v>
       </c>
       <c r="C18" s="0">
-        <v>1452.2846</v>
+        <v>1459.4197999999999</v>
       </c>
       <c r="D18" s="0">
         <v>23.75</v>
       </c>
       <c r="E18" s="0">
-        <v>22.173720357696652</v>
+        <v>22.602545121541702</v>
       </c>
       <c r="F18" s="0">
-        <v>-1.5762796423033478</v>
+        <v>-1.1474548784582979</v>
       </c>
       <c r="G18" s="0">
-        <v>1.5762796423033478</v>
+        <v>1.1474548784582979</v>
       </c>
       <c r="H18" s="0">
-        <v>21.673720357696652</v>
+        <v>22.102545121541702</v>
       </c>
       <c r="I18" s="0">
-        <v>-2.0762796423033478</v>
+        <v>-1.6474548784582979</v>
       </c>
       <c r="J18" s="0">
-        <v>2.0762796423033478</v>
+        <v>1.6474548784582979</v>
       </c>
       <c r="K18" s="0" t="b">
         <v>0</v>
@@ -1232,28 +1232,28 @@
         <v>69</v>
       </c>
       <c r="C19" s="0">
-        <v>668.60829999999999</v>
+        <v>667.94280000000003</v>
       </c>
       <c r="D19" s="0">
         <v>22.25</v>
       </c>
       <c r="E19" s="0">
-        <v>20.866965531298369</v>
+        <v>20.943416280369192</v>
       </c>
       <c r="F19" s="0">
-        <v>-1.3830344687016307</v>
+        <v>-1.3065837196308081</v>
       </c>
       <c r="G19" s="0">
-        <v>1.3830344687016307</v>
+        <v>1.3065837196308081</v>
       </c>
       <c r="H19" s="0">
-        <v>20.366965531298369</v>
+        <v>20.443416280369192</v>
       </c>
       <c r="I19" s="0">
-        <v>-1.8830344687016307</v>
+        <v>-1.8065837196308081</v>
       </c>
       <c r="J19" s="0">
-        <v>1.8830344687016307</v>
+        <v>1.8065837196308081</v>
       </c>
       <c r="K19" s="0" t="b">
         <v>0</v>
@@ -1276,28 +1276,28 @@
         <v>69</v>
       </c>
       <c r="C20" s="0">
-        <v>750.32280000000003</v>
+        <v>755.404</v>
       </c>
       <c r="D20" s="0">
         <v>25.5</v>
       </c>
       <c r="E20" s="0">
-        <v>21.036328859161373</v>
+        <v>21.709009888626955</v>
       </c>
       <c r="F20" s="0">
-        <v>-4.4636711408386276</v>
+        <v>-3.7909901113730449</v>
       </c>
       <c r="G20" s="0">
-        <v>4.4636711408386276</v>
+        <v>3.7909901113730449</v>
       </c>
       <c r="H20" s="0">
-        <v>20.536328859161373</v>
+        <v>21.209009888626955</v>
       </c>
       <c r="I20" s="0">
-        <v>-4.9636711408386276</v>
+        <v>-4.2909901113730449</v>
       </c>
       <c r="J20" s="0">
-        <v>4.9636711408386276</v>
+        <v>4.2909901113730449</v>
       </c>
       <c r="K20" s="0" t="b">
         <v>0</v>
@@ -1320,28 +1320,28 @@
         <v>69</v>
       </c>
       <c r="C21" s="0">
-        <v>345.22919999999999</v>
+        <v>344.29160000000002</v>
       </c>
       <c r="D21" s="0">
         <v>22.5</v>
       </c>
       <c r="E21" s="0">
-        <v>19.827445989184444</v>
+        <v>19.657141624086218</v>
       </c>
       <c r="F21" s="0">
-        <v>-2.6725540108155563</v>
+        <v>-2.8428583759137815</v>
       </c>
       <c r="G21" s="0">
-        <v>2.6725540108155563</v>
+        <v>2.8428583759137815</v>
       </c>
       <c r="H21" s="0">
-        <v>19.327445989184444</v>
+        <v>19.157141624086218</v>
       </c>
       <c r="I21" s="0">
-        <v>-3.1725540108155563</v>
+        <v>-3.3428583759137816</v>
       </c>
       <c r="J21" s="0">
-        <v>3.1725540108155563</v>
+        <v>3.3428583759137816</v>
       </c>
       <c r="K21" s="0" t="b">
         <v>0</v>
@@ -1364,28 +1364,28 @@
         <v>69</v>
       </c>
       <c r="C22" s="0">
-        <v>622.22630000000004</v>
+        <v>613.17560000000003</v>
       </c>
       <c r="D22" s="0">
         <v>21.5</v>
       </c>
       <c r="E22" s="0">
-        <v>20.144372708484866</v>
+        <v>20.033736719467889</v>
       </c>
       <c r="F22" s="0">
-        <v>-1.3556272915151339</v>
+        <v>-1.466263280532111</v>
       </c>
       <c r="G22" s="0">
-        <v>1.3556272915151339</v>
+        <v>1.466263280532111</v>
       </c>
       <c r="H22" s="0">
-        <v>19.644372708484866</v>
+        <v>19.533736719467889</v>
       </c>
       <c r="I22" s="0">
-        <v>-1.855627291515134</v>
+        <v>-1.966263280532111</v>
       </c>
       <c r="J22" s="0">
-        <v>1.855627291515134</v>
+        <v>1.966263280532111</v>
       </c>
       <c r="K22" s="0" t="b">
         <v>0</v>
@@ -1408,28 +1408,28 @@
         <v>69</v>
       </c>
       <c r="C23" s="0">
-        <v>671.48209999999995</v>
+        <v>674.47910000000002</v>
       </c>
       <c r="D23" s="0">
         <v>20</v>
       </c>
       <c r="E23" s="0">
-        <v>21.247165178907721</v>
+        <v>21.474266173852705</v>
       </c>
       <c r="F23" s="0">
-        <v>1.2471651789077214</v>
+        <v>1.4742661738527048</v>
       </c>
       <c r="G23" s="0">
-        <v>1.2471651789077214</v>
+        <v>1.4742661738527048</v>
       </c>
       <c r="H23" s="0">
-        <v>20.747165178907721</v>
+        <v>20.974266173852705</v>
       </c>
       <c r="I23" s="0">
-        <v>0.74716517890772138</v>
+        <v>0.97426617385270475</v>
       </c>
       <c r="J23" s="0">
-        <v>0.74716517890772138</v>
+        <v>0.97426617385270475</v>
       </c>
       <c r="K23" s="0" t="b">
         <v>1</v>
@@ -1452,28 +1452,28 @@
         <v>69</v>
       </c>
       <c r="C24" s="0">
-        <v>582.96010000000001</v>
+        <v>577.67240000000004</v>
       </c>
       <c r="D24" s="0">
         <v>19.5</v>
       </c>
       <c r="E24" s="0">
-        <v>20.957433177360869</v>
+        <v>21.252511927314213</v>
       </c>
       <c r="F24" s="0">
-        <v>1.4574331773608691</v>
+        <v>1.7525119273142131</v>
       </c>
       <c r="G24" s="0">
-        <v>1.4574331773608691</v>
+        <v>1.7525119273142131</v>
       </c>
       <c r="H24" s="0">
-        <v>20.457433177360869</v>
+        <v>20.752511927314213</v>
       </c>
       <c r="I24" s="0">
-        <v>0.95743317736086908</v>
+        <v>1.2525119273142131</v>
       </c>
       <c r="J24" s="0">
-        <v>0.95743317736086908</v>
+        <v>1.2525119273142131</v>
       </c>
       <c r="K24" s="0" t="b">
         <v>1</v>
@@ -1496,28 +1496,28 @@
         <v>69</v>
       </c>
       <c r="C25" s="0">
-        <v>577.6952</v>
+        <v>577.55370000000005</v>
       </c>
       <c r="D25" s="0">
         <v>18.5</v>
       </c>
       <c r="E25" s="0">
-        <v>19.998765336244446</v>
+        <v>20.215269827918604</v>
       </c>
       <c r="F25" s="0">
-        <v>1.4987653362444462</v>
+        <v>1.7152698279186041</v>
       </c>
       <c r="G25" s="0">
-        <v>1.4987653362444462</v>
+        <v>1.7152698279186041</v>
       </c>
       <c r="H25" s="0">
-        <v>19.498765336244446</v>
+        <v>19.715269827918604</v>
       </c>
       <c r="I25" s="0">
-        <v>0.99876533624444619</v>
+        <v>1.2152698279186041</v>
       </c>
       <c r="J25" s="0">
-        <v>0.99876533624444619</v>
+        <v>1.2152698279186041</v>
       </c>
       <c r="K25" s="0" t="b">
         <v>1</v>
@@ -1540,28 +1540,28 @@
         <v>69</v>
       </c>
       <c r="C26" s="0">
-        <v>689.21019999999999</v>
+        <v>688.17229999999995</v>
       </c>
       <c r="D26" s="0">
         <v>21.25</v>
       </c>
       <c r="E26" s="0">
-        <v>22.29141410040539</v>
+        <v>22.181257728060416</v>
       </c>
       <c r="F26" s="0">
-        <v>1.0414141004053903</v>
+        <v>0.93125772806041596</v>
       </c>
       <c r="G26" s="0">
-        <v>1.0414141004053903</v>
+        <v>0.93125772806041596</v>
       </c>
       <c r="H26" s="0">
-        <v>21.79141410040539</v>
+        <v>21.681257728060416</v>
       </c>
       <c r="I26" s="0">
-        <v>0.54141410040539029</v>
+        <v>0.43125772806041596</v>
       </c>
       <c r="J26" s="0">
-        <v>0.54141410040539029</v>
+        <v>0.43125772806041596</v>
       </c>
       <c r="K26" s="0" t="b">
         <v>1</v>
@@ -1584,28 +1584,28 @@
         <v>69</v>
       </c>
       <c r="C27" s="0">
-        <v>641.4787</v>
+        <v>638.71429999999998</v>
       </c>
       <c r="D27" s="0">
         <v>19.25</v>
       </c>
       <c r="E27" s="0">
-        <v>20.476669092205185</v>
+        <v>20.426243975696519</v>
       </c>
       <c r="F27" s="0">
-        <v>1.2266690922051851</v>
+        <v>1.1762439756965186</v>
       </c>
       <c r="G27" s="0">
-        <v>1.2266690922051851</v>
+        <v>1.1762439756965186</v>
       </c>
       <c r="H27" s="0">
-        <v>19.976669092205185</v>
+        <v>19.926243975696519</v>
       </c>
       <c r="I27" s="0">
-        <v>0.72666909220518505</v>
+        <v>0.67624397569651862</v>
       </c>
       <c r="J27" s="0">
-        <v>0.72666909220518505</v>
+        <v>0.67624397569651862</v>
       </c>
       <c r="K27" s="0" t="b">
         <v>1</v>
@@ -1628,28 +1628,28 @@
         <v>69</v>
       </c>
       <c r="C28" s="0">
-        <v>684.71199999999999</v>
+        <v>676.74940000000004</v>
       </c>
       <c r="D28" s="0">
         <v>21.75</v>
       </c>
       <c r="E28" s="0">
-        <v>21.026572635827932</v>
+        <v>21.316849811130677</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.72342736417206766</v>
+        <v>-0.43315018886932322</v>
       </c>
       <c r="G28" s="0">
-        <v>0.72342736417206766</v>
+        <v>0.43315018886932322</v>
       </c>
       <c r="H28" s="0">
-        <v>20.526572635827932</v>
+        <v>20.816849811130677</v>
       </c>
       <c r="I28" s="0">
-        <v>-1.2234273641720677</v>
+        <v>-0.93315018886932322</v>
       </c>
       <c r="J28" s="0">
-        <v>1.2234273641720677</v>
+        <v>0.93315018886932322</v>
       </c>
       <c r="K28" s="0" t="b">
         <v>0</v>
@@ -1672,28 +1672,28 @@
         <v>69</v>
       </c>
       <c r="C29" s="0">
-        <v>353.73129999999998</v>
+        <v>354.31049999999999</v>
       </c>
       <c r="D29" s="0">
         <v>20.75</v>
       </c>
       <c r="E29" s="0">
-        <v>20.93991176863781</v>
+        <v>20.930383311229228</v>
       </c>
       <c r="F29" s="0">
-        <v>0.18991176863780979</v>
+        <v>0.18038331122922813</v>
       </c>
       <c r="G29" s="0">
-        <v>0.18991176863780979</v>
+        <v>0.18038331122922813</v>
       </c>
       <c r="H29" s="0">
-        <v>20.43991176863781</v>
+        <v>20.430383311229228</v>
       </c>
       <c r="I29" s="0">
-        <v>-0.31008823136219021</v>
+        <v>-0.31961668877077187</v>
       </c>
       <c r="J29" s="0">
-        <v>0.31008823136219021</v>
+        <v>0.31961668877077187</v>
       </c>
       <c r="K29" s="0" t="b">
         <v>0</v>
@@ -1716,28 +1716,28 @@
         <v>69</v>
       </c>
       <c r="C30" s="0">
-        <v>683.46259999999995</v>
+        <v>683.81759999999997</v>
       </c>
       <c r="D30" s="0">
         <v>21.5</v>
       </c>
       <c r="E30" s="0">
-        <v>21.571381470138199</v>
+        <v>21.252508382944871</v>
       </c>
       <c r="F30" s="0">
-        <v>0.071381470138199177</v>
+        <v>-0.2474916170551289</v>
       </c>
       <c r="G30" s="0">
-        <v>0.071381470138199177</v>
+        <v>0.2474916170551289</v>
       </c>
       <c r="H30" s="0">
-        <v>21.071381470138199</v>
+        <v>20.752508382944871</v>
       </c>
       <c r="I30" s="0">
-        <v>-0.42861852986180082</v>
+        <v>-0.7474916170551289</v>
       </c>
       <c r="J30" s="0">
-        <v>0.42861852986180082</v>
+        <v>0.7474916170551289</v>
       </c>
       <c r="K30" s="0" t="b">
         <v>0</v>
@@ -1760,28 +1760,28 @@
         <v>69</v>
       </c>
       <c r="C31" s="0">
-        <v>1356.9842000000001</v>
+        <v>1353.5838000000001</v>
       </c>
       <c r="D31" s="0">
         <v>19.5</v>
       </c>
       <c r="E31" s="0">
-        <v>21.531804995208255</v>
+        <v>21.252486019156695</v>
       </c>
       <c r="F31" s="0">
-        <v>2.0318049952082546</v>
+        <v>1.7524860191566951</v>
       </c>
       <c r="G31" s="0">
-        <v>2.0318049952082546</v>
+        <v>1.7524860191566951</v>
       </c>
       <c r="H31" s="0">
-        <v>21.031804995208255</v>
+        <v>20.752486019156695</v>
       </c>
       <c r="I31" s="0">
-        <v>1.5318049952082546</v>
+        <v>1.2524860191566951</v>
       </c>
       <c r="J31" s="0">
-        <v>1.5318049952082546</v>
+        <v>1.2524860191566951</v>
       </c>
       <c r="K31" s="0" t="b">
         <v>1</v>
@@ -1804,28 +1804,28 @@
         <v>69</v>
       </c>
       <c r="C32" s="0">
-        <v>1312.2254</v>
+        <v>1324.2094</v>
       </c>
       <c r="D32" s="0">
         <v>19.5</v>
       </c>
       <c r="E32" s="0">
-        <v>20.967725137838141</v>
+        <v>21.252486999970955</v>
       </c>
       <c r="F32" s="0">
-        <v>1.4677251378381406</v>
+        <v>1.7524869999709551</v>
       </c>
       <c r="G32" s="0">
-        <v>1.4677251378381406</v>
+        <v>1.7524869999709551</v>
       </c>
       <c r="H32" s="0">
-        <v>20.467725137838141</v>
+        <v>20.752486999970955</v>
       </c>
       <c r="I32" s="0">
-        <v>0.96772513783814063</v>
+        <v>1.2524869999709551</v>
       </c>
       <c r="J32" s="0">
-        <v>0.96772513783814063</v>
+        <v>1.2524869999709551</v>
       </c>
       <c r="K32" s="0" t="b">
         <v>1</v>
@@ -1848,28 +1848,28 @@
         <v>69</v>
       </c>
       <c r="C33" s="0">
-        <v>1359.0623000000001</v>
+        <v>1370.5188000000001</v>
       </c>
       <c r="D33" s="0">
         <v>21</v>
       </c>
       <c r="E33" s="0">
-        <v>20.90548818667094</v>
+        <v>21.077359555980671</v>
       </c>
       <c r="F33" s="0">
-        <v>-0.094511813329059891</v>
+        <v>0.077359555980670791</v>
       </c>
       <c r="G33" s="0">
-        <v>0.094511813329059891</v>
+        <v>0.077359555980670791</v>
       </c>
       <c r="H33" s="0">
-        <v>20.40548818667094</v>
+        <v>20.577359555980671</v>
       </c>
       <c r="I33" s="0">
-        <v>-0.59451181332905989</v>
+        <v>-0.42264044401932921</v>
       </c>
       <c r="J33" s="0">
-        <v>0.59451181332905989</v>
+        <v>0.42264044401932921</v>
       </c>
       <c r="K33" s="0" t="b">
         <v>0</v>
@@ -1892,28 +1892,28 @@
         <v>69</v>
       </c>
       <c r="C34" s="0">
-        <v>611.02089999999998</v>
+        <v>595.53899999999999</v>
       </c>
       <c r="D34" s="0">
         <v>20.25</v>
       </c>
       <c r="E34" s="0">
-        <v>19.926322962763244</v>
+        <v>19.980895216842527</v>
       </c>
       <c r="F34" s="0">
-        <v>-0.32367703723675589</v>
+        <v>-0.26910478315747355</v>
       </c>
       <c r="G34" s="0">
-        <v>0.32367703723675589</v>
+        <v>0.26910478315747355</v>
       </c>
       <c r="H34" s="0">
-        <v>19.426322962763244</v>
+        <v>19.480895216842527</v>
       </c>
       <c r="I34" s="0">
-        <v>-0.82367703723675589</v>
+        <v>-0.76910478315747355</v>
       </c>
       <c r="J34" s="0">
-        <v>0.82367703723675589</v>
+        <v>0.76910478315747355</v>
       </c>
       <c r="K34" s="0" t="b">
         <v>0</v>
@@ -1936,28 +1936,28 @@
         <v>69</v>
       </c>
       <c r="C35" s="0">
-        <v>623.09130000000005</v>
+        <v>620.18640000000005</v>
       </c>
       <c r="D35" s="0">
         <v>21.5</v>
       </c>
       <c r="E35" s="0">
-        <v>20.160506478160269</v>
+        <v>20.01732990580221</v>
       </c>
       <c r="F35" s="0">
-        <v>-1.3394935218397315</v>
+        <v>-1.4826700941977897</v>
       </c>
       <c r="G35" s="0">
-        <v>1.3394935218397315</v>
+        <v>1.4826700941977897</v>
       </c>
       <c r="H35" s="0">
-        <v>19.660506478160269</v>
+        <v>19.51732990580221</v>
       </c>
       <c r="I35" s="0">
-        <v>-1.8394935218397315</v>
+        <v>-1.9826700941977897</v>
       </c>
       <c r="J35" s="0">
-        <v>1.8394935218397315</v>
+        <v>1.9826700941977897</v>
       </c>
       <c r="K35" s="0" t="b">
         <v>0</v>
@@ -1980,28 +1980,28 @@
         <v>69</v>
       </c>
       <c r="C36" s="0">
-        <v>590.04459999999995</v>
+        <v>589.86860000000001</v>
       </c>
       <c r="D36" s="0">
         <v>19.5</v>
       </c>
       <c r="E36" s="0">
-        <v>20.005659223890444</v>
+        <v>20.076669425897578</v>
       </c>
       <c r="F36" s="0">
-        <v>0.5056592238904436</v>
+        <v>0.57666942589757753</v>
       </c>
       <c r="G36" s="0">
-        <v>0.5056592238904436</v>
+        <v>0.57666942589757753</v>
       </c>
       <c r="H36" s="0">
-        <v>19.505659223890444</v>
+        <v>19.576669425897578</v>
       </c>
       <c r="I36" s="0">
-        <v>0.0056592238904435987</v>
+        <v>0.076669425897577526</v>
       </c>
       <c r="J36" s="0">
-        <v>0.0056592238904435987</v>
+        <v>0.076669425897577526</v>
       </c>
       <c r="K36" s="0" t="b">
         <v>1</v>
@@ -2024,28 +2024,28 @@
         <v>69</v>
       </c>
       <c r="C37" s="0">
-        <v>724.99620000000004</v>
+        <v>724.63610000000006</v>
       </c>
       <c r="D37" s="0">
         <v>25</v>
       </c>
       <c r="E37" s="0">
-        <v>23.035895932057049</v>
+        <v>23.594223159260079</v>
       </c>
       <c r="F37" s="0">
-        <v>-1.9641040679429516</v>
+        <v>-1.4057768407399216</v>
       </c>
       <c r="G37" s="0">
-        <v>1.9641040679429516</v>
+        <v>1.4057768407399216</v>
       </c>
       <c r="H37" s="0">
-        <v>22.535895932057049</v>
+        <v>23.094223159260079</v>
       </c>
       <c r="I37" s="0">
-        <v>-2.4641040679429516</v>
+        <v>-1.9057768407399216</v>
       </c>
       <c r="J37" s="0">
-        <v>2.4641040679429516</v>
+        <v>1.9057768407399216</v>
       </c>
       <c r="K37" s="0" t="b">
         <v>0</v>
@@ -2068,28 +2068,28 @@
         <v>69</v>
       </c>
       <c r="C38" s="0">
-        <v>600.44100000000003</v>
+        <v>598.2287</v>
       </c>
       <c r="D38" s="0">
         <v>19</v>
       </c>
       <c r="E38" s="0">
-        <v>21.014064337538343</v>
+        <v>20.867302672147726</v>
       </c>
       <c r="F38" s="0">
-        <v>2.0140643375383434</v>
+        <v>1.8673026721477264</v>
       </c>
       <c r="G38" s="0">
-        <v>2.0140643375383434</v>
+        <v>1.8673026721477264</v>
       </c>
       <c r="H38" s="0">
-        <v>20.514064337538343</v>
+        <v>20.367302672147726</v>
       </c>
       <c r="I38" s="0">
-        <v>1.5140643375383434</v>
+        <v>1.3673026721477264</v>
       </c>
       <c r="J38" s="0">
-        <v>1.5140643375383434</v>
+        <v>1.3673026721477264</v>
       </c>
       <c r="K38" s="0" t="b">
         <v>1</v>
@@ -2112,28 +2112,28 @@
         <v>69</v>
       </c>
       <c r="C39" s="0">
-        <v>692.81489999999997</v>
+        <v>681.9153</v>
       </c>
       <c r="D39" s="0">
         <v>19</v>
       </c>
       <c r="E39" s="0">
-        <v>22.447322862856218</v>
+        <v>21.922122058283065</v>
       </c>
       <c r="F39" s="0">
-        <v>3.4473228628562183</v>
+        <v>2.9221220582830654</v>
       </c>
       <c r="G39" s="0">
-        <v>3.4473228628562183</v>
+        <v>2.9221220582830654</v>
       </c>
       <c r="H39" s="0">
-        <v>21.947322862856218</v>
+        <v>21.422122058283065</v>
       </c>
       <c r="I39" s="0">
-        <v>2.9473228628562183</v>
+        <v>2.4221220582830654</v>
       </c>
       <c r="J39" s="0">
-        <v>2.9473228628562183</v>
+        <v>2.4221220582830654</v>
       </c>
       <c r="K39" s="0" t="b">
         <v>1</v>
@@ -2156,28 +2156,28 @@
         <v>69</v>
       </c>
       <c r="C40" s="0">
-        <v>1193.8898999999999</v>
+        <v>1171.8478</v>
       </c>
       <c r="D40" s="0">
         <v>21</v>
       </c>
       <c r="E40" s="0">
-        <v>19.780018032000889</v>
+        <v>21.252492087335092</v>
       </c>
       <c r="F40" s="0">
-        <v>-1.2199819679991109</v>
+        <v>0.25249208733509221</v>
       </c>
       <c r="G40" s="0">
-        <v>1.2199819679991109</v>
+        <v>0.25249208733509221</v>
       </c>
       <c r="H40" s="0">
-        <v>19.280018032000889</v>
+        <v>20.752492087335092</v>
       </c>
       <c r="I40" s="0">
-        <v>-1.7199819679991109</v>
+        <v>-0.24750791266490779</v>
       </c>
       <c r="J40" s="0">
-        <v>1.7199819679991109</v>
+        <v>0.24750791266490779</v>
       </c>
       <c r="K40" s="0" t="b">
         <v>0</v>
@@ -2200,28 +2200,28 @@
         <v>69</v>
       </c>
       <c r="C41" s="0">
-        <v>666.36320000000001</v>
+        <v>665.75360000000001</v>
       </c>
       <c r="D41" s="0">
         <v>20.5</v>
       </c>
       <c r="E41" s="0">
-        <v>21.467409019029652</v>
+        <v>21.252508986128436</v>
       </c>
       <c r="F41" s="0">
-        <v>0.96740901902965248</v>
+        <v>0.75250898612843642</v>
       </c>
       <c r="G41" s="0">
-        <v>0.96740901902965248</v>
+        <v>0.75250898612843642</v>
       </c>
       <c r="H41" s="0">
-        <v>20.967409019029652</v>
+        <v>20.752508986128436</v>
       </c>
       <c r="I41" s="0">
-        <v>0.46740901902965248</v>
+        <v>0.25250898612843642</v>
       </c>
       <c r="J41" s="0">
-        <v>0.46740901902965248</v>
+        <v>0.25250898612843642</v>
       </c>
       <c r="K41" s="0" t="b">
         <v>1</v>
@@ -2244,28 +2244,28 @@
         <v>69</v>
       </c>
       <c r="C42" s="0">
-        <v>340.92939999999999</v>
+        <v>343.99220000000003</v>
       </c>
       <c r="D42" s="0">
         <v>19.25</v>
       </c>
       <c r="E42" s="0">
-        <v>20.503776424720034</v>
+        <v>20.540786038830948</v>
       </c>
       <c r="F42" s="0">
-        <v>1.2537764247200336</v>
+        <v>1.290786038830948</v>
       </c>
       <c r="G42" s="0">
-        <v>1.2537764247200336</v>
+        <v>1.290786038830948</v>
       </c>
       <c r="H42" s="0">
-        <v>20.003776424720034</v>
+        <v>20.040786038830948</v>
       </c>
       <c r="I42" s="0">
-        <v>0.75377642472003359</v>
+        <v>0.790786038830948</v>
       </c>
       <c r="J42" s="0">
-        <v>0.75377642472003359</v>
+        <v>0.790786038830948</v>
       </c>
       <c r="K42" s="0" t="b">
         <v>1</v>
@@ -2288,28 +2288,28 @@
         <v>69</v>
       </c>
       <c r="C43" s="0">
-        <v>582.97400000000005</v>
+        <v>584.32039999999995</v>
       </c>
       <c r="D43" s="0">
         <v>20</v>
       </c>
       <c r="E43" s="0">
-        <v>21.011475562361106</v>
+        <v>20.788931289625833</v>
       </c>
       <c r="F43" s="0">
-        <v>1.011475562361106</v>
+        <v>0.78893128962583248</v>
       </c>
       <c r="G43" s="0">
-        <v>1.011475562361106</v>
+        <v>0.78893128962583248</v>
       </c>
       <c r="H43" s="0">
-        <v>20.511475562361106</v>
+        <v>20.288931289625833</v>
       </c>
       <c r="I43" s="0">
-        <v>0.51147556236110603</v>
+        <v>0.28893128962583248</v>
       </c>
       <c r="J43" s="0">
-        <v>0.51147556236110603</v>
+        <v>0.28893128962583248</v>
       </c>
       <c r="K43" s="0" t="b">
         <v>1</v>
@@ -2332,28 +2332,28 @@
         <v>69</v>
       </c>
       <c r="C44" s="0">
-        <v>657.05769999999996</v>
+        <v>660.15719999999999</v>
       </c>
       <c r="D44" s="0">
         <v>20</v>
       </c>
       <c r="E44" s="0">
-        <v>20.914181050969081</v>
+        <v>21.107203139576551</v>
       </c>
       <c r="F44" s="0">
-        <v>0.91418105096908065</v>
+        <v>1.1072031395765514</v>
       </c>
       <c r="G44" s="0">
-        <v>0.91418105096908065</v>
+        <v>1.1072031395765514</v>
       </c>
       <c r="H44" s="0">
-        <v>20.414181050969081</v>
+        <v>20.607203139576551</v>
       </c>
       <c r="I44" s="0">
-        <v>0.41418105096908064</v>
+        <v>0.60720313957655137</v>
       </c>
       <c r="J44" s="0">
-        <v>0.41418105096908064</v>
+        <v>0.60720313957655137</v>
       </c>
       <c r="K44" s="0" t="b">
         <v>1</v>
@@ -2376,28 +2376,28 @@
         <v>69</v>
       </c>
       <c r="C45" s="0">
-        <v>584.81910000000005</v>
+        <v>581.95590000000004</v>
       </c>
       <c r="D45" s="0">
         <v>20</v>
       </c>
       <c r="E45" s="0">
-        <v>20.000060372903125</v>
+        <v>20.159379703251702</v>
       </c>
       <c r="F45" s="0">
-        <v>6.0372903124772392e-05</v>
+        <v>0.1593797032517017</v>
       </c>
       <c r="G45" s="0">
-        <v>6.0372903124772392e-05</v>
+        <v>0.1593797032517017</v>
       </c>
       <c r="H45" s="0">
-        <v>19.500060372903125</v>
+        <v>19.659379703251702</v>
       </c>
       <c r="I45" s="0">
-        <v>-0.49993962709687523</v>
+        <v>-0.3406202967482983</v>
       </c>
       <c r="J45" s="0">
-        <v>0.49993962709687523</v>
+        <v>0.3406202967482983</v>
       </c>
       <c r="K45" s="0" t="b">
         <v>0</v>
@@ -2420,28 +2420,28 @@
         <v>69</v>
       </c>
       <c r="C46" s="0">
-        <v>1457.3396</v>
+        <v>1432.1427000000001</v>
       </c>
       <c r="D46" s="0">
         <v>22</v>
       </c>
       <c r="E46" s="0">
-        <v>22.227827773727821</v>
+        <v>22.130784189623878</v>
       </c>
       <c r="F46" s="0">
-        <v>0.22782777372782093</v>
+        <v>0.13078418962387772</v>
       </c>
       <c r="G46" s="0">
-        <v>0.22782777372782093</v>
+        <v>0.13078418962387772</v>
       </c>
       <c r="H46" s="0">
-        <v>21.727827773727821</v>
+        <v>21.630784189623878</v>
       </c>
       <c r="I46" s="0">
-        <v>-0.27217222627217907</v>
+        <v>-0.36921581037612228</v>
       </c>
       <c r="J46" s="0">
-        <v>0.27217222627217907</v>
+        <v>0.36921581037612228</v>
       </c>
       <c r="K46" s="0" t="b">
         <v>0</v>
@@ -2464,28 +2464,28 @@
         <v>69</v>
       </c>
       <c r="C47" s="0">
-        <v>1394.6958999999999</v>
+        <v>1393.6792</v>
       </c>
       <c r="D47" s="0">
         <v>22</v>
       </c>
       <c r="E47" s="0">
-        <v>21.560829214787056</v>
+        <v>21.542736545268163</v>
       </c>
       <c r="F47" s="0">
-        <v>-0.43917078521294428</v>
+        <v>-0.45726345473183727</v>
       </c>
       <c r="G47" s="0">
-        <v>0.43917078521294428</v>
+        <v>0.45726345473183727</v>
       </c>
       <c r="H47" s="0">
-        <v>21.060829214787056</v>
+        <v>21.042736545268163</v>
       </c>
       <c r="I47" s="0">
-        <v>-0.93917078521294428</v>
+        <v>-0.95726345473183727</v>
       </c>
       <c r="J47" s="0">
-        <v>0.93917078521294428</v>
+        <v>0.95726345473183727</v>
       </c>
       <c r="K47" s="0" t="b">
         <v>0</v>
@@ -2508,28 +2508,28 @@
         <v>69</v>
       </c>
       <c r="C48" s="0">
-        <v>1393.5521000000001</v>
+        <v>1418.9514999999999</v>
       </c>
       <c r="D48" s="0">
         <v>23</v>
       </c>
       <c r="E48" s="0">
-        <v>21.473763729052905</v>
+        <v>22.153569737180611</v>
       </c>
       <c r="F48" s="0">
-        <v>-1.5262362709470949</v>
+        <v>-0.84643026281938916</v>
       </c>
       <c r="G48" s="0">
-        <v>1.5262362709470949</v>
+        <v>0.84643026281938916</v>
       </c>
       <c r="H48" s="0">
-        <v>20.973763729052905</v>
+        <v>21.653569737180611</v>
       </c>
       <c r="I48" s="0">
-        <v>-2.0262362709470949</v>
+        <v>-1.3464302628193892</v>
       </c>
       <c r="J48" s="0">
-        <v>2.0262362709470949</v>
+        <v>1.3464302628193892</v>
       </c>
       <c r="K48" s="0" t="b">
         <v>0</v>
@@ -2552,28 +2552,28 @@
         <v>69</v>
       </c>
       <c r="C49" s="0">
-        <v>1328.9452000000001</v>
+        <v>1319.8444999999999</v>
       </c>
       <c r="D49" s="0">
         <v>21.75</v>
       </c>
       <c r="E49" s="0">
-        <v>20.477403014567297</v>
+        <v>20.140024852533649</v>
       </c>
       <c r="F49" s="0">
-        <v>-1.2725969854327026</v>
+        <v>-1.6099751474663506</v>
       </c>
       <c r="G49" s="0">
-        <v>1.2725969854327026</v>
+        <v>1.6099751474663506</v>
       </c>
       <c r="H49" s="0">
-        <v>19.977403014567297</v>
+        <v>19.640024852533649</v>
       </c>
       <c r="I49" s="0">
-        <v>-1.7725969854327026</v>
+        <v>-2.1099751474663506</v>
       </c>
       <c r="J49" s="0">
-        <v>1.7725969854327026</v>
+        <v>2.1099751474663506</v>
       </c>
       <c r="K49" s="0" t="b">
         <v>0</v>
@@ -2596,28 +2596,28 @@
         <v>69</v>
       </c>
       <c r="C50" s="0">
-        <v>1373.3529000000001</v>
+        <v>1370.9471000000001</v>
       </c>
       <c r="D50" s="0">
         <v>21.5</v>
       </c>
       <c r="E50" s="0">
-        <v>21.129008959458787</v>
+        <v>21.377543045902428</v>
       </c>
       <c r="F50" s="0">
-        <v>-0.37099104054121312</v>
+        <v>-0.12245695409757218</v>
       </c>
       <c r="G50" s="0">
-        <v>0.37099104054121312</v>
+        <v>0.12245695409757218</v>
       </c>
       <c r="H50" s="0">
-        <v>20.629008959458787</v>
+        <v>20.877543045902428</v>
       </c>
       <c r="I50" s="0">
-        <v>-0.87099104054121313</v>
+        <v>-0.62245695409757218</v>
       </c>
       <c r="J50" s="0">
-        <v>0.87099104054121313</v>
+        <v>0.62245695409757218</v>
       </c>
       <c r="K50" s="0" t="b">
         <v>0</v>
@@ -2640,28 +2640,28 @@
         <v>69</v>
       </c>
       <c r="C51" s="0">
-        <v>1232.3471999999999</v>
+        <v>1230.9086</v>
       </c>
       <c r="D51" s="0">
         <v>19.199999999999999</v>
       </c>
       <c r="E51" s="0">
-        <v>20.079370974948691</v>
+        <v>21.252490115291074</v>
       </c>
       <c r="F51" s="0">
-        <v>0.87937097494869221</v>
+        <v>2.0524901152910751</v>
       </c>
       <c r="G51" s="0">
-        <v>0.87937097494869221</v>
+        <v>2.0524901152910751</v>
       </c>
       <c r="H51" s="0">
-        <v>19.579370974948691</v>
+        <v>20.752490115291074</v>
       </c>
       <c r="I51" s="0">
-        <v>0.37937097494869221</v>
+        <v>1.5524901152910751</v>
       </c>
       <c r="J51" s="0">
-        <v>0.37937097494869221</v>
+        <v>1.5524901152910751</v>
       </c>
       <c r="K51" s="0" t="b">
         <v>1</v>
@@ -2684,28 +2684,28 @@
         <v>69</v>
       </c>
       <c r="C52" s="0">
-        <v>1151.9466</v>
+        <v>1142.3658</v>
       </c>
       <c r="D52" s="0">
         <v>17.5</v>
       </c>
       <c r="E52" s="0">
-        <v>19.972524371484436</v>
+        <v>20.064405478728844</v>
       </c>
       <c r="F52" s="0">
-        <v>2.4725243714844361</v>
+        <v>2.5644054787288439</v>
       </c>
       <c r="G52" s="0">
-        <v>2.4725243714844361</v>
+        <v>2.5644054787288439</v>
       </c>
       <c r="H52" s="0">
-        <v>19.472524371484436</v>
+        <v>19.564405478728844</v>
       </c>
       <c r="I52" s="0">
-        <v>1.9725243714844361</v>
+        <v>2.0644054787288439</v>
       </c>
       <c r="J52" s="0">
-        <v>1.9725243714844361</v>
+        <v>2.0644054787288439</v>
       </c>
       <c r="K52" s="0" t="b">
         <v>1</v>
@@ -2728,28 +2728,28 @@
         <v>69</v>
       </c>
       <c r="C53" s="0">
-        <v>1179.067</v>
+        <v>1183.6578999999999</v>
       </c>
       <c r="D53" s="0">
         <v>18.399999999999999</v>
       </c>
       <c r="E53" s="0">
-        <v>19.070370210915961</v>
+        <v>19.264514489172161</v>
       </c>
       <c r="F53" s="0">
-        <v>0.67037021091596216</v>
+        <v>0.86451448917216212</v>
       </c>
       <c r="G53" s="0">
-        <v>0.67037021091596216</v>
+        <v>0.86451448917216212</v>
       </c>
       <c r="H53" s="0">
-        <v>18.570370210915961</v>
+        <v>18.764514489172161</v>
       </c>
       <c r="I53" s="0">
-        <v>0.17037021091596216</v>
+        <v>0.36451448917216211</v>
       </c>
       <c r="J53" s="0">
-        <v>0.17037021091596216</v>
+        <v>0.36451448917216211</v>
       </c>
       <c r="K53" s="0" t="b">
         <v>1</v>
@@ -2772,28 +2772,28 @@
         <v>69</v>
       </c>
       <c r="C54" s="0">
-        <v>1127.4477999999999</v>
+        <v>1127.7965999999999</v>
       </c>
       <c r="D54" s="0">
         <v>19</v>
       </c>
       <c r="E54" s="0">
-        <v>21.092511877833928</v>
+        <v>19.775358098921281</v>
       </c>
       <c r="F54" s="0">
-        <v>2.0925118778339282</v>
+        <v>0.77535809892128071</v>
       </c>
       <c r="G54" s="0">
-        <v>2.0925118778339282</v>
+        <v>0.77535809892128071</v>
       </c>
       <c r="H54" s="0">
-        <v>20.592511877833928</v>
+        <v>19.275358098921281</v>
       </c>
       <c r="I54" s="0">
-        <v>1.5925118778339282</v>
+        <v>0.27535809892128071</v>
       </c>
       <c r="J54" s="0">
-        <v>1.5925118778339282</v>
+        <v>0.27535809892128071</v>
       </c>
       <c r="K54" s="0" t="b">
         <v>1</v>
@@ -2816,28 +2816,28 @@
         <v>69</v>
       </c>
       <c r="C55" s="0">
-        <v>600.82780000000002</v>
+        <v>600.21460000000002</v>
       </c>
       <c r="D55" s="0">
         <v>19.5</v>
       </c>
       <c r="E55" s="0">
-        <v>21.014121681167985</v>
+        <v>20.878576532231744</v>
       </c>
       <c r="F55" s="0">
-        <v>1.5141216811679854</v>
+        <v>1.3785765322317438</v>
       </c>
       <c r="G55" s="0">
-        <v>1.5141216811679854</v>
+        <v>1.3785765322317438</v>
       </c>
       <c r="H55" s="0">
-        <v>20.514121681167985</v>
+        <v>20.378576532231744</v>
       </c>
       <c r="I55" s="0">
-        <v>1.0141216811679854</v>
+        <v>0.87857653223174381</v>
       </c>
       <c r="J55" s="0">
-        <v>1.0141216811679854</v>
+        <v>0.87857653223174381</v>
       </c>
       <c r="K55" s="0" t="b">
         <v>1</v>
@@ -2860,28 +2860,28 @@
         <v>69</v>
       </c>
       <c r="C56" s="0">
-        <v>727.90769999999998</v>
+        <v>684.51480000000004</v>
       </c>
       <c r="D56" s="0">
         <v>20.5</v>
       </c>
       <c r="E56" s="0">
-        <v>23.616720111350517</v>
+        <v>22.02881585016128</v>
       </c>
       <c r="F56" s="0">
-        <v>3.1167201113505172</v>
+        <v>1.5288158501612799</v>
       </c>
       <c r="G56" s="0">
-        <v>3.1167201113505172</v>
+        <v>1.5288158501612799</v>
       </c>
       <c r="H56" s="0">
-        <v>23.116720111350517</v>
+        <v>21.52881585016128</v>
       </c>
       <c r="I56" s="0">
-        <v>2.6167201113505172</v>
+        <v>1.0288158501612799</v>
       </c>
       <c r="J56" s="0">
-        <v>2.6167201113505172</v>
+        <v>1.0288158501612799</v>
       </c>
       <c r="K56" s="0" t="b">
         <v>1</v>
@@ -2904,28 +2904,28 @@
         <v>69</v>
       </c>
       <c r="C57" s="0">
-        <v>646.02480000000003</v>
+        <v>632.78740000000005</v>
       </c>
       <c r="D57" s="0">
         <v>21</v>
       </c>
       <c r="E57" s="0">
-        <v>20.43088960097548</v>
+        <v>20.133522418289577</v>
       </c>
       <c r="F57" s="0">
-        <v>-0.56911039902452032</v>
+        <v>-0.86647758171042355</v>
       </c>
       <c r="G57" s="0">
-        <v>0.56911039902452032</v>
+        <v>0.86647758171042355</v>
       </c>
       <c r="H57" s="0">
-        <v>19.93088960097548</v>
+        <v>19.633522418289577</v>
       </c>
       <c r="I57" s="0">
-        <v>-1.0691103990245203</v>
+        <v>-1.3664775817104236</v>
       </c>
       <c r="J57" s="0">
-        <v>1.0691103990245203</v>
+        <v>1.3664775817104236</v>
       </c>
       <c r="K57" s="0" t="b">
         <v>0</v>
@@ -2948,28 +2948,28 @@
         <v>69</v>
       </c>
       <c r="C58" s="0">
-        <v>1120.8548000000001</v>
+        <v>1105.7334000000001</v>
       </c>
       <c r="D58" s="0">
         <v>23.5</v>
       </c>
       <c r="E58" s="0">
-        <v>18.2728288694931</v>
+        <v>18.549066402601749</v>
       </c>
       <c r="F58" s="0">
-        <v>-5.2271711305068998</v>
+        <v>-4.9509335973982509</v>
       </c>
       <c r="G58" s="0">
-        <v>5.2271711305068998</v>
+        <v>4.9509335973982509</v>
       </c>
       <c r="H58" s="0">
-        <v>17.7728288694931</v>
+        <v>18.049066402601749</v>
       </c>
       <c r="I58" s="0">
-        <v>-5.7271711305068998</v>
+        <v>-5.4509335973982509</v>
       </c>
       <c r="J58" s="0">
-        <v>5.7271711305068998</v>
+        <v>5.4509335973982509</v>
       </c>
       <c r="K58" s="0" t="b">
         <v>0</v>
@@ -2992,28 +2992,28 @@
         <v>69</v>
       </c>
       <c r="C59" s="0">
-        <v>665.77250000000004</v>
+        <v>665.27829999999995</v>
       </c>
       <c r="D59" s="0">
         <v>20.5</v>
       </c>
       <c r="E59" s="0">
-        <v>21.463780422255688</v>
+        <v>21.252509001999424</v>
       </c>
       <c r="F59" s="0">
-        <v>0.96378042225568805</v>
+        <v>0.7525090019994245</v>
       </c>
       <c r="G59" s="0">
-        <v>0.96378042225568805</v>
+        <v>0.7525090019994245</v>
       </c>
       <c r="H59" s="0">
-        <v>20.963780422255688</v>
+        <v>20.752509001999424</v>
       </c>
       <c r="I59" s="0">
-        <v>0.46378042225568805</v>
+        <v>0.2525090019994245</v>
       </c>
       <c r="J59" s="0">
-        <v>0.46378042225568805</v>
+        <v>0.2525090019994245</v>
       </c>
       <c r="K59" s="0" t="b">
         <v>1</v>
@@ -3036,28 +3036,28 @@
         <v>69</v>
       </c>
       <c r="C60" s="0">
-        <v>695.50199999999995</v>
+        <v>655.14710000000002</v>
       </c>
       <c r="D60" s="0">
         <v>21.5</v>
       </c>
       <c r="E60" s="0">
-        <v>21.028176154091835</v>
+        <v>21.194183384703763</v>
       </c>
       <c r="F60" s="0">
-        <v>-0.4718238459081654</v>
+        <v>-0.30581661529623716</v>
       </c>
       <c r="G60" s="0">
-        <v>0.4718238459081654</v>
+        <v>0.30581661529623716</v>
       </c>
       <c r="H60" s="0">
-        <v>20.528176154091835</v>
+        <v>20.694183384703763</v>
       </c>
       <c r="I60" s="0">
-        <v>-0.9718238459081654</v>
+        <v>-0.80581661529623716</v>
       </c>
       <c r="J60" s="0">
-        <v>0.9718238459081654</v>
+        <v>0.80581661529623716</v>
       </c>
       <c r="K60" s="0" t="b">
         <v>0</v>
@@ -3080,31 +3080,31 @@
         <v>69</v>
       </c>
       <c r="C61" s="0">
-        <v>639.4633</v>
+        <v>642.19590000000005</v>
       </c>
       <c r="D61" s="0">
         <v>20</v>
       </c>
       <c r="E61" s="0">
-        <v>20.435450032599146</v>
+        <v>20.503556909540404</v>
       </c>
       <c r="F61" s="0">
-        <v>0.43545003259914594</v>
+        <v>0.50355690954040355</v>
       </c>
       <c r="G61" s="0">
-        <v>0.43545003259914594</v>
+        <v>0.50355690954040355</v>
       </c>
       <c r="H61" s="0">
-        <v>19.935450032599146</v>
+        <v>20.003556909540404</v>
       </c>
       <c r="I61" s="0">
-        <v>-0.064549967400854058</v>
+        <v>0.0035569095404035522</v>
       </c>
       <c r="J61" s="0">
-        <v>0.064549967400854058</v>
+        <v>0.0035569095404035522</v>
       </c>
       <c r="K61" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="0">
         <v>4</v>
@@ -3124,28 +3124,28 @@
         <v>69</v>
       </c>
       <c r="C62" s="0">
-        <v>699.43420000000003</v>
+        <v>671.02829999999995</v>
       </c>
       <c r="D62" s="0">
         <v>23</v>
       </c>
       <c r="E62" s="0">
-        <v>22.160118870267631</v>
+        <v>21.35028856193777</v>
       </c>
       <c r="F62" s="0">
-        <v>-0.83988112973236895</v>
+        <v>-1.64971143806223</v>
       </c>
       <c r="G62" s="0">
-        <v>0.83988112973236895</v>
+        <v>1.64971143806223</v>
       </c>
       <c r="H62" s="0">
-        <v>21.660118870267631</v>
+        <v>20.85028856193777</v>
       </c>
       <c r="I62" s="0">
-        <v>-1.339881129732369</v>
+        <v>-2.14971143806223</v>
       </c>
       <c r="J62" s="0">
-        <v>1.339881129732369</v>
+        <v>2.14971143806223</v>
       </c>
       <c r="K62" s="0" t="b">
         <v>0</v>
@@ -3168,31 +3168,31 @@
         <v>69</v>
       </c>
       <c r="C63" s="0">
-        <v>683.36609999999996</v>
+        <v>658.74609999999996</v>
       </c>
       <c r="D63" s="0">
         <v>21.5</v>
       </c>
       <c r="E63" s="0">
-        <v>22.033198673861211</v>
+        <v>21.060348876394151</v>
       </c>
       <c r="F63" s="0">
-        <v>0.53319867386121089</v>
+        <v>-0.43965112360584868</v>
       </c>
       <c r="G63" s="0">
-        <v>0.53319867386121089</v>
+        <v>0.43965112360584868</v>
       </c>
       <c r="H63" s="0">
-        <v>21.533198673861211</v>
+        <v>20.560348876394151</v>
       </c>
       <c r="I63" s="0">
-        <v>0.033198673861210892</v>
+        <v>-0.93965112360584868</v>
       </c>
       <c r="J63" s="0">
-        <v>0.033198673861210892</v>
+        <v>0.93965112360584868</v>
       </c>
       <c r="K63" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" s="0">
         <v>3</v>
@@ -3212,28 +3212,28 @@
         <v>69</v>
       </c>
       <c r="C64" s="0">
-        <v>421.81869999999998</v>
+        <v>418.81540000000001</v>
       </c>
       <c r="D64" s="0">
         <v>22.5</v>
       </c>
       <c r="E64" s="0">
-        <v>20.987669544358823</v>
+        <v>19.987939243069324</v>
       </c>
       <c r="F64" s="0">
-        <v>-1.5123304556411767</v>
+        <v>-2.5120607569306763</v>
       </c>
       <c r="G64" s="0">
-        <v>1.5123304556411767</v>
+        <v>2.5120607569306763</v>
       </c>
       <c r="H64" s="0">
-        <v>20.487669544358823</v>
+        <v>19.487939243069324</v>
       </c>
       <c r="I64" s="0">
-        <v>-2.0123304556411767</v>
+        <v>-3.0120607569306763</v>
       </c>
       <c r="J64" s="0">
-        <v>2.0123304556411767</v>
+        <v>3.0120607569306763</v>
       </c>
       <c r="K64" s="0" t="b">
         <v>0</v>
@@ -3256,28 +3256,28 @@
         <v>69</v>
       </c>
       <c r="C65" s="0">
-        <v>594.92830000000004</v>
+        <v>593.42259999999999</v>
       </c>
       <c r="D65" s="0">
         <v>19.25</v>
       </c>
       <c r="E65" s="0">
-        <v>21.028520638478124</v>
+        <v>21.252511401384233</v>
       </c>
       <c r="F65" s="0">
-        <v>1.778520638478124</v>
+        <v>2.0025114013842327</v>
       </c>
       <c r="G65" s="0">
-        <v>1.778520638478124</v>
+        <v>2.0025114013842327</v>
       </c>
       <c r="H65" s="0">
-        <v>20.528520638478124</v>
+        <v>20.752511401384233</v>
       </c>
       <c r="I65" s="0">
-        <v>1.278520638478124</v>
+        <v>1.5025114013842327</v>
       </c>
       <c r="J65" s="0">
-        <v>1.278520638478124</v>
+        <v>1.5025114013842327</v>
       </c>
       <c r="K65" s="0" t="b">
         <v>1</v>
@@ -3300,28 +3300,28 @@
         <v>69</v>
       </c>
       <c r="C66" s="0">
-        <v>672.91949999999997</v>
+        <v>709.44029999999998</v>
       </c>
       <c r="D66" s="0">
         <v>23.5</v>
       </c>
       <c r="E66" s="0">
-        <v>20.971199148829047</v>
+        <v>22.733834476203203</v>
       </c>
       <c r="F66" s="0">
-        <v>-2.5288008511709528</v>
+        <v>-0.76616552379679703</v>
       </c>
       <c r="G66" s="0">
-        <v>2.5288008511709528</v>
+        <v>0.76616552379679703</v>
       </c>
       <c r="H66" s="0">
-        <v>20.471199148829047</v>
+        <v>22.233834476203203</v>
       </c>
       <c r="I66" s="0">
-        <v>-3.0288008511709528</v>
+        <v>-1.266165523796797</v>
       </c>
       <c r="J66" s="0">
-        <v>3.0288008511709528</v>
+        <v>1.266165523796797</v>
       </c>
       <c r="K66" s="0" t="b">
         <v>0</v>
@@ -3344,28 +3344,28 @@
         <v>69</v>
       </c>
       <c r="C67" s="0">
-        <v>637.33479999999997</v>
+        <v>625.83199999999999</v>
       </c>
       <c r="D67" s="0">
         <v>21.5</v>
       </c>
       <c r="E67" s="0">
-        <v>20.309632814620933</v>
+        <v>20.058344546146906</v>
       </c>
       <c r="F67" s="0">
-        <v>-1.1903671853790669</v>
+        <v>-1.4416554538530946</v>
       </c>
       <c r="G67" s="0">
-        <v>1.1903671853790669</v>
+        <v>1.4416554538530946</v>
       </c>
       <c r="H67" s="0">
-        <v>19.809632814620933</v>
+        <v>19.558344546146906</v>
       </c>
       <c r="I67" s="0">
-        <v>-1.6903671853790669</v>
+        <v>-1.9416554538530946</v>
       </c>
       <c r="J67" s="0">
-        <v>1.6903671853790669</v>
+        <v>1.9416554538530946</v>
       </c>
       <c r="K67" s="0" t="b">
         <v>0</v>
@@ -3388,28 +3388,28 @@
         <v>69</v>
       </c>
       <c r="C68" s="0">
-        <v>879.03800000000001</v>
+        <v>889.9828</v>
       </c>
       <c r="D68" s="0">
         <v>19</v>
       </c>
       <c r="E68" s="0">
-        <v>25.660706819621439</v>
+        <v>28.709795531239678</v>
       </c>
       <c r="F68" s="0">
-        <v>6.6607068196214385</v>
+        <v>9.7097955312396778</v>
       </c>
       <c r="G68" s="0">
-        <v>6.6607068196214385</v>
+        <v>9.7097955312396778</v>
       </c>
       <c r="H68" s="0">
-        <v>25.160706819621439</v>
+        <v>28.209795531239678</v>
       </c>
       <c r="I68" s="0">
-        <v>6.1607068196214385</v>
+        <v>9.2097955312396778</v>
       </c>
       <c r="J68" s="0">
-        <v>6.1607068196214385</v>
+        <v>9.2097955312396778</v>
       </c>
       <c r="K68" s="0" t="b">
         <v>1</v>
@@ -3470,16 +3470,16 @@
         <v>85</v>
       </c>
       <c r="B2" s="0">
-        <v>1.313</v>
+        <v>1.3100000000000001</v>
       </c>
       <c r="C2" s="0">
-        <v>1.7569999999999999</v>
+        <v>1.8300000000000001</v>
       </c>
       <c r="D2" s="0">
-        <v>0.122</v>
+        <v>0.126</v>
       </c>
       <c r="E2" s="0">
-        <v>0.042999999999999997</v>
+        <v>0.109</v>
       </c>
       <c r="F2" s="0"/>
       <c r="G2" s="0"/>
@@ -3489,22 +3489,22 @@
         <v>86</v>
       </c>
       <c r="B3" s="0">
-        <v>0.042000000000000003</v>
+        <v>0.048000000000000001</v>
       </c>
       <c r="C3" s="0">
-        <v>0.058000000000000003</v>
+        <v>0.13200000000000001</v>
       </c>
       <c r="D3" s="0">
-        <v>0.039</v>
+        <v>0.047</v>
       </c>
       <c r="E3" s="0">
-        <v>0.067000000000000004</v>
+        <v>0.063</v>
       </c>
       <c r="F3" s="0">
-        <v>4.2000000000000002</v>
+        <v>3.3999999999999999</v>
       </c>
       <c r="G3" s="0">
-        <v>2.1000000000000001</v>
+        <v>1.6000000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -3523,18 +3523,18 @@
         <v>88</v>
       </c>
       <c r="B5" s="0">
-        <v>1.337</v>
+        <v>1.325</v>
       </c>
       <c r="C5" s="0"/>
       <c r="D5" s="0"/>
       <c r="E5" s="0">
-        <v>-0.45700000000000002</v>
+        <v>-0.39100000000000001</v>
       </c>
       <c r="F5" s="0">
-        <v>50.700000000000003</v>
+        <v>51.299999999999997</v>
       </c>
       <c r="G5" s="0">
-        <v>41.299999999999997</v>
+        <v>43.700000000000003</v>
       </c>
     </row>
     <row r="6">
@@ -3542,13 +3542,13 @@
         <v>89</v>
       </c>
       <c r="B6" s="0">
-        <v>1.474</v>
+        <v>1.4750000000000001</v>
       </c>
       <c r="C6" s="0">
         <v>1.8260000000000001</v>
       </c>
       <c r="D6" s="0">
-        <v>0.035999999999999997</v>
+        <v>0.040000000000000001</v>
       </c>
       <c r="E6" s="0">
         <v>0.0030000000000000001</v>
@@ -3561,7 +3561,7 @@
         <v>90</v>
       </c>
       <c r="B7" s="0">
-        <v>1.484</v>
+        <v>1.4850000000000001</v>
       </c>
       <c r="C7" s="0"/>
       <c r="D7" s="0"/>
@@ -3652,7 +3652,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="true"/>
-    <col min="2" max="2" width="5.7109375" customWidth="true"/>
+    <col min="2" max="2" width="7.7109375" customWidth="true"/>
     <col min="3" max="3" width="6.7109375" customWidth="true"/>
     <col min="4" max="4" width="6.7109375" customWidth="true"/>
     <col min="5" max="5" width="4.5703125" customWidth="true"/>
@@ -3680,13 +3680,13 @@
         <v>111</v>
       </c>
       <c r="B2" s="0">
-        <v>20.739999999999999</v>
+        <v>20.7623</v>
       </c>
       <c r="C2" s="0">
-        <v>0.59970000000000001</v>
+        <v>0.59589999999999999</v>
       </c>
       <c r="D2" s="0">
-        <v>34.582999999999999</v>
+        <v>34.838999999999999</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
@@ -3703,10 +3703,10 @@
         <v>0.00069999999999999999</v>
       </c>
       <c r="D3" s="0">
-        <v>0.442</v>
+        <v>0.40500000000000003</v>
       </c>
       <c r="E3" s="0">
-        <v>0.65980000000000005</v>
+        <v>0.68669999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/預測結果與評估指標_kfold_mask幾何.xlsx
+++ b/預測結果與評估指標_kfold_mask幾何.xlsx
@@ -421,7 +421,7 @@
     <col min="3" max="3" width="13.42578125" customWidth="true"/>
     <col min="4" max="4" width="14.7109375" customWidth="true"/>
     <col min="5" max="5" width="14.7109375" customWidth="true"/>
-    <col min="6" max="6" width="13.7109375" customWidth="true"/>
+    <col min="6" max="6" width="14.42578125" customWidth="true"/>
     <col min="7" max="7" width="14.7109375" customWidth="true"/>
     <col min="8" max="8" width="17" customWidth="true"/>
     <col min="9" max="9" width="20.5703125" customWidth="true"/>
@@ -484,28 +484,28 @@
         <v>69</v>
       </c>
       <c r="C2" s="0">
-        <v>405.481</v>
+        <v>408.47719999999998</v>
       </c>
       <c r="D2" s="0">
         <v>23</v>
       </c>
       <c r="E2" s="0">
-        <v>19.935902928847248</v>
+        <v>19.876807430394937</v>
       </c>
       <c r="F2" s="0">
-        <v>-3.0640970711527515</v>
+        <v>-3.1231925696050631</v>
       </c>
       <c r="G2" s="0">
-        <v>3.0640970711527515</v>
+        <v>3.1231925696050631</v>
       </c>
       <c r="H2" s="0">
-        <v>19.435902928847248</v>
+        <v>19.376807430394937</v>
       </c>
       <c r="I2" s="0">
-        <v>-3.5640970711527515</v>
+        <v>-3.6231925696050631</v>
       </c>
       <c r="J2" s="0">
-        <v>3.5640970711527515</v>
+        <v>3.6231925696050631</v>
       </c>
       <c r="K2" s="0" t="b">
         <v>0</v>
@@ -528,28 +528,28 @@
         <v>69</v>
       </c>
       <c r="C3" s="0">
-        <v>605.36530000000005</v>
+        <v>618.74630000000002</v>
       </c>
       <c r="D3" s="0">
         <v>21</v>
       </c>
       <c r="E3" s="0">
-        <v>21.252511002595075</v>
+        <v>21.13046818935668</v>
       </c>
       <c r="F3" s="0">
-        <v>0.25251100259507453</v>
+        <v>0.13046818935668014</v>
       </c>
       <c r="G3" s="0">
-        <v>0.25251100259507453</v>
+        <v>0.13046818935668014</v>
       </c>
       <c r="H3" s="0">
-        <v>20.752511002595075</v>
+        <v>20.63046818935668</v>
       </c>
       <c r="I3" s="0">
-        <v>-0.24748899740492547</v>
+        <v>-0.36953181064331986</v>
       </c>
       <c r="J3" s="0">
-        <v>0.24748899740492547</v>
+        <v>0.36953181064331986</v>
       </c>
       <c r="K3" s="0" t="b">
         <v>0</v>
@@ -572,28 +572,28 @@
         <v>69</v>
       </c>
       <c r="C4" s="0">
-        <v>740.86210000000005</v>
+        <v>757.2885</v>
       </c>
       <c r="D4" s="0">
         <v>23.5</v>
       </c>
       <c r="E4" s="0">
-        <v>24.272973495587049</v>
+        <v>24.485119661410924</v>
       </c>
       <c r="F4" s="0">
-        <v>0.77297349558704909</v>
+        <v>0.98511966141092344</v>
       </c>
       <c r="G4" s="0">
-        <v>0.77297349558704909</v>
+        <v>0.98511966141092344</v>
       </c>
       <c r="H4" s="0">
-        <v>23.772973495587049</v>
+        <v>23.985119661410924</v>
       </c>
       <c r="I4" s="0">
-        <v>0.27297349558704909</v>
+        <v>0.48511966141092344</v>
       </c>
       <c r="J4" s="0">
-        <v>0.27297349558704909</v>
+        <v>0.48511966141092344</v>
       </c>
       <c r="K4" s="0" t="b">
         <v>1</v>
@@ -616,28 +616,28 @@
         <v>69</v>
       </c>
       <c r="C5" s="0">
-        <v>580.86249999999996</v>
+        <v>583.17809999999997</v>
       </c>
       <c r="D5" s="0">
         <v>21</v>
       </c>
       <c r="E5" s="0">
-        <v>20.769624327526259</v>
+        <v>20.699396082925546</v>
       </c>
       <c r="F5" s="0">
-        <v>-0.23037567247374113</v>
+        <v>-0.30060391707445433</v>
       </c>
       <c r="G5" s="0">
-        <v>0.23037567247374113</v>
+        <v>0.30060391707445433</v>
       </c>
       <c r="H5" s="0">
-        <v>20.269624327526259</v>
+        <v>20.199396082925546</v>
       </c>
       <c r="I5" s="0">
-        <v>-0.73037567247374113</v>
+        <v>-0.80060391707445433</v>
       </c>
       <c r="J5" s="0">
-        <v>0.73037567247374113</v>
+        <v>0.80060391707445433</v>
       </c>
       <c r="K5" s="0" t="b">
         <v>0</v>
@@ -660,28 +660,28 @@
         <v>69</v>
       </c>
       <c r="C6" s="0">
-        <v>620.73389999999995</v>
+        <v>633.10580000000004</v>
       </c>
       <c r="D6" s="0">
         <v>21.5</v>
       </c>
       <c r="E6" s="0">
-        <v>21.252510489409868</v>
+        <v>21.225185092847436</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.2474895105901318</v>
+        <v>-0.27481490715256385</v>
       </c>
       <c r="G6" s="0">
-        <v>0.2474895105901318</v>
+        <v>0.27481490715256385</v>
       </c>
       <c r="H6" s="0">
-        <v>20.752510489409868</v>
+        <v>20.725185092847436</v>
       </c>
       <c r="I6" s="0">
-        <v>-0.7474895105901318</v>
+        <v>-0.77481490715256385</v>
       </c>
       <c r="J6" s="0">
-        <v>0.7474895105901318</v>
+        <v>0.77481490715256385</v>
       </c>
       <c r="K6" s="0" t="b">
         <v>0</v>
@@ -704,28 +704,28 @@
         <v>69</v>
       </c>
       <c r="C7" s="0">
-        <v>711.67399999999998</v>
+        <v>712.21130000000005</v>
       </c>
       <c r="D7" s="0">
         <v>22</v>
       </c>
       <c r="E7" s="0">
-        <v>21.505718855212212</v>
+        <v>21.50531689861506</v>
       </c>
       <c r="F7" s="0">
-        <v>-0.49428114478778795</v>
+        <v>-0.49468310138493976</v>
       </c>
       <c r="G7" s="0">
-        <v>0.49428114478778795</v>
+        <v>0.49468310138493976</v>
       </c>
       <c r="H7" s="0">
-        <v>21.005718855212212</v>
+        <v>21.00531689861506</v>
       </c>
       <c r="I7" s="0">
-        <v>-0.99428114478778795</v>
+        <v>-0.99468310138493976</v>
       </c>
       <c r="J7" s="0">
-        <v>0.99428114478778795</v>
+        <v>0.99468310138493976</v>
       </c>
       <c r="K7" s="0" t="b">
         <v>0</v>
@@ -748,28 +748,28 @@
         <v>69</v>
       </c>
       <c r="C8" s="0">
-        <v>757.66719999999998</v>
+        <v>765.37739999999997</v>
       </c>
       <c r="D8" s="0">
         <v>25</v>
       </c>
       <c r="E8" s="0">
-        <v>25.365430369600638</v>
+        <v>25.328470805840727</v>
       </c>
       <c r="F8" s="0">
-        <v>0.36543036960063802</v>
+        <v>0.32847080584072685</v>
       </c>
       <c r="G8" s="0">
-        <v>0.36543036960063802</v>
+        <v>0.32847080584072685</v>
       </c>
       <c r="H8" s="0">
-        <v>24.865430369600638</v>
+        <v>24.828470805840727</v>
       </c>
       <c r="I8" s="0">
-        <v>-0.13456963039936198</v>
+        <v>-0.17152919415927315</v>
       </c>
       <c r="J8" s="0">
-        <v>0.13456963039936198</v>
+        <v>0.17152919415927315</v>
       </c>
       <c r="K8" s="0" t="b">
         <v>0</v>
@@ -792,31 +792,31 @@
         <v>69</v>
       </c>
       <c r="C9" s="0">
-        <v>390.43310000000002</v>
+        <v>384.85610000000003</v>
       </c>
       <c r="D9" s="0">
         <v>20.5</v>
       </c>
       <c r="E9" s="0">
-        <v>21.252518179721982</v>
+        <v>19.981883137113208</v>
       </c>
       <c r="F9" s="0">
-        <v>0.75251817972198154</v>
+        <v>-0.51811686288679226</v>
       </c>
       <c r="G9" s="0">
-        <v>0.75251817972198154</v>
+        <v>0.51811686288679226</v>
       </c>
       <c r="H9" s="0">
-        <v>20.752518179721982</v>
+        <v>19.481883137113208</v>
       </c>
       <c r="I9" s="0">
-        <v>0.25251817972198154</v>
+        <v>-1.0181168628867923</v>
       </c>
       <c r="J9" s="0">
-        <v>0.25251817972198154</v>
+        <v>1.0181168628867923</v>
       </c>
       <c r="K9" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="0">
         <v>2</v>
@@ -836,28 +836,28 @@
         <v>69</v>
       </c>
       <c r="C10" s="0">
-        <v>1263.4103</v>
+        <v>1296.7855999999999</v>
       </c>
       <c r="D10" s="0">
         <v>21</v>
       </c>
       <c r="E10" s="0">
-        <v>21.252489030057379</v>
+        <v>20.472122368558928</v>
       </c>
       <c r="F10" s="0">
-        <v>0.25248903005737944</v>
+        <v>-0.52787763144107203</v>
       </c>
       <c r="G10" s="0">
-        <v>0.25248903005737944</v>
+        <v>0.52787763144107203</v>
       </c>
       <c r="H10" s="0">
-        <v>20.752489030057379</v>
+        <v>19.972122368558928</v>
       </c>
       <c r="I10" s="0">
-        <v>-0.24751096994262056</v>
+        <v>-1.027877631441072</v>
       </c>
       <c r="J10" s="0">
-        <v>0.24751096994262056</v>
+        <v>1.027877631441072</v>
       </c>
       <c r="K10" s="0" t="b">
         <v>0</v>
@@ -880,28 +880,28 @@
         <v>69</v>
       </c>
       <c r="C11" s="0">
-        <v>319.74869999999999</v>
+        <v>320.06220000000002</v>
       </c>
       <c r="D11" s="0">
         <v>18</v>
       </c>
       <c r="E11" s="0">
-        <v>19.644754579282829</v>
+        <v>19.598761195571317</v>
       </c>
       <c r="F11" s="0">
-        <v>1.6447545792828287</v>
+        <v>1.598761195571317</v>
       </c>
       <c r="G11" s="0">
-        <v>1.6447545792828287</v>
+        <v>1.598761195571317</v>
       </c>
       <c r="H11" s="0">
-        <v>19.144754579282829</v>
+        <v>19.098761195571317</v>
       </c>
       <c r="I11" s="0">
-        <v>1.1447545792828286</v>
+        <v>1.098761195571317</v>
       </c>
       <c r="J11" s="0">
-        <v>1.1447545792828286</v>
+        <v>1.098761195571317</v>
       </c>
       <c r="K11" s="0" t="b">
         <v>1</v>
@@ -924,28 +924,28 @@
         <v>69</v>
       </c>
       <c r="C12" s="0">
-        <v>718.36379999999997</v>
+        <v>747.66359999999997</v>
       </c>
       <c r="D12" s="0">
         <v>25</v>
       </c>
       <c r="E12" s="0">
-        <v>23.463836719190645</v>
+        <v>23.929147478556089</v>
       </c>
       <c r="F12" s="0">
-        <v>-1.5361632808093546</v>
+        <v>-1.0708525214439106</v>
       </c>
       <c r="G12" s="0">
-        <v>1.5361632808093546</v>
+        <v>1.0708525214439106</v>
       </c>
       <c r="H12" s="0">
-        <v>22.963836719190645</v>
+        <v>23.429147478556089</v>
       </c>
       <c r="I12" s="0">
-        <v>-2.0361632808093546</v>
+        <v>-1.5708525214439106</v>
       </c>
       <c r="J12" s="0">
-        <v>2.0361632808093546</v>
+        <v>1.5708525214439106</v>
       </c>
       <c r="K12" s="0" t="b">
         <v>0</v>
@@ -968,28 +968,28 @@
         <v>69</v>
       </c>
       <c r="C13" s="0">
-        <v>669.91160000000002</v>
+        <v>659.65279999999996</v>
       </c>
       <c r="D13" s="0">
         <v>22.5</v>
       </c>
       <c r="E13" s="0">
-        <v>21.452739801485873</v>
+        <v>20.686910972424105</v>
       </c>
       <c r="F13" s="0">
-        <v>-1.0472601985141274</v>
+        <v>-1.8130890275758951</v>
       </c>
       <c r="G13" s="0">
-        <v>1.0472601985141274</v>
+        <v>1.8130890275758951</v>
       </c>
       <c r="H13" s="0">
-        <v>20.952739801485873</v>
+        <v>20.186910972424105</v>
       </c>
       <c r="I13" s="0">
-        <v>-1.5472601985141274</v>
+        <v>-2.3130890275758951</v>
       </c>
       <c r="J13" s="0">
-        <v>1.5472601985141274</v>
+        <v>2.3130890275758951</v>
       </c>
       <c r="K13" s="0" t="b">
         <v>0</v>
@@ -1012,28 +1012,28 @@
         <v>69</v>
       </c>
       <c r="C14" s="0">
-        <v>672.01459999999997</v>
+        <v>682.95950000000005</v>
       </c>
       <c r="D14" s="0">
         <v>20.5</v>
       </c>
       <c r="E14" s="0">
-        <v>21.385279439864107</v>
+        <v>21.374807711003058</v>
       </c>
       <c r="F14" s="0">
-        <v>0.88527943986410662</v>
+        <v>0.87480771100305788</v>
       </c>
       <c r="G14" s="0">
-        <v>0.88527943986410662</v>
+        <v>0.87480771100305788</v>
       </c>
       <c r="H14" s="0">
-        <v>20.885279439864107</v>
+        <v>20.874807711003058</v>
       </c>
       <c r="I14" s="0">
-        <v>0.38527943986410662</v>
+        <v>0.37480771100305788</v>
       </c>
       <c r="J14" s="0">
-        <v>0.38527943986410662</v>
+        <v>0.37480771100305788</v>
       </c>
       <c r="K14" s="0" t="b">
         <v>1</v>
@@ -1056,28 +1056,28 @@
         <v>69</v>
       </c>
       <c r="C15" s="0">
-        <v>585.0598</v>
+        <v>587.81489999999997</v>
       </c>
       <c r="D15" s="0">
         <v>19.5</v>
       </c>
       <c r="E15" s="0">
-        <v>20.004821829554743</v>
+        <v>20.126114527467546</v>
       </c>
       <c r="F15" s="0">
-        <v>0.50482182955474286</v>
+        <v>0.62611452746754637</v>
       </c>
       <c r="G15" s="0">
-        <v>0.50482182955474286</v>
+        <v>0.62611452746754637</v>
       </c>
       <c r="H15" s="0">
-        <v>19.504821829554743</v>
+        <v>19.626114527467546</v>
       </c>
       <c r="I15" s="0">
-        <v>0.0048218295547428625</v>
+        <v>0.12611452746754637</v>
       </c>
       <c r="J15" s="0">
-        <v>0.0048218295547428625</v>
+        <v>0.12611452746754637</v>
       </c>
       <c r="K15" s="0" t="b">
         <v>1</v>
@@ -1100,28 +1100,28 @@
         <v>69</v>
       </c>
       <c r="C16" s="0">
-        <v>618.17600000000004</v>
+        <v>624.73410000000001</v>
       </c>
       <c r="D16" s="0">
         <v>19.5</v>
       </c>
       <c r="E16" s="0">
-        <v>21.252510574822662</v>
+        <v>21.16972797048987</v>
       </c>
       <c r="F16" s="0">
-        <v>1.7525105748226615</v>
+        <v>1.6697279704898698</v>
       </c>
       <c r="G16" s="0">
-        <v>1.7525105748226615</v>
+        <v>1.6697279704898698</v>
       </c>
       <c r="H16" s="0">
-        <v>20.752510574822662</v>
+        <v>20.66972797048987</v>
       </c>
       <c r="I16" s="0">
-        <v>1.2525105748226615</v>
+        <v>1.1697279704898698</v>
       </c>
       <c r="J16" s="0">
-        <v>1.2525105748226615</v>
+        <v>1.1697279704898698</v>
       </c>
       <c r="K16" s="0" t="b">
         <v>1</v>
@@ -1144,28 +1144,28 @@
         <v>69</v>
       </c>
       <c r="C17" s="0">
-        <v>1122.4987000000001</v>
+        <v>1128.8182999999999</v>
       </c>
       <c r="D17" s="0">
         <v>18.5</v>
       </c>
       <c r="E17" s="0">
-        <v>18.713583829867734</v>
+        <v>18.627821873302949</v>
       </c>
       <c r="F17" s="0">
-        <v>0.2135838298677335</v>
+        <v>0.12782187330294903</v>
       </c>
       <c r="G17" s="0">
-        <v>0.2135838298677335</v>
+        <v>0.12782187330294903</v>
       </c>
       <c r="H17" s="0">
-        <v>18.213583829867734</v>
+        <v>18.127821873302949</v>
       </c>
       <c r="I17" s="0">
-        <v>-0.2864161701322665</v>
+        <v>-0.37217812669705097</v>
       </c>
       <c r="J17" s="0">
-        <v>0.2864161701322665</v>
+        <v>0.37217812669705097</v>
       </c>
       <c r="K17" s="0" t="b">
         <v>0</v>
@@ -1188,28 +1188,28 @@
         <v>69</v>
       </c>
       <c r="C18" s="0">
-        <v>1459.4197999999999</v>
+        <v>1473.3333</v>
       </c>
       <c r="D18" s="0">
         <v>23.75</v>
       </c>
       <c r="E18" s="0">
-        <v>22.602545121541702</v>
+        <v>22.052208822292489</v>
       </c>
       <c r="F18" s="0">
-        <v>-1.1474548784582979</v>
+        <v>-1.6977911777075114</v>
       </c>
       <c r="G18" s="0">
-        <v>1.1474548784582979</v>
+        <v>1.6977911777075114</v>
       </c>
       <c r="H18" s="0">
-        <v>22.102545121541702</v>
+        <v>21.552208822292489</v>
       </c>
       <c r="I18" s="0">
-        <v>-1.6474548784582979</v>
+        <v>-2.1977911777075114</v>
       </c>
       <c r="J18" s="0">
-        <v>1.6474548784582979</v>
+        <v>2.1977911777075114</v>
       </c>
       <c r="K18" s="0" t="b">
         <v>0</v>
@@ -1232,28 +1232,28 @@
         <v>69</v>
       </c>
       <c r="C19" s="0">
-        <v>667.94280000000003</v>
+        <v>676.57719999999995</v>
       </c>
       <c r="D19" s="0">
         <v>22.25</v>
       </c>
       <c r="E19" s="0">
-        <v>20.943416280369192</v>
+        <v>20.823454583803407</v>
       </c>
       <c r="F19" s="0">
-        <v>-1.3065837196308081</v>
+        <v>-1.4265454161965927</v>
       </c>
       <c r="G19" s="0">
-        <v>1.3065837196308081</v>
+        <v>1.4265454161965927</v>
       </c>
       <c r="H19" s="0">
-        <v>20.443416280369192</v>
+        <v>20.323454583803407</v>
       </c>
       <c r="I19" s="0">
-        <v>-1.8065837196308081</v>
+        <v>-1.9265454161965927</v>
       </c>
       <c r="J19" s="0">
-        <v>1.8065837196308081</v>
+        <v>1.9265454161965927</v>
       </c>
       <c r="K19" s="0" t="b">
         <v>0</v>
@@ -1276,28 +1276,28 @@
         <v>69</v>
       </c>
       <c r="C20" s="0">
-        <v>755.404</v>
+        <v>752.55830000000003</v>
       </c>
       <c r="D20" s="0">
         <v>25.5</v>
       </c>
       <c r="E20" s="0">
-        <v>21.709009888626955</v>
+        <v>21.748288916190074</v>
       </c>
       <c r="F20" s="0">
-        <v>-3.7909901113730449</v>
+        <v>-3.7517110838099264</v>
       </c>
       <c r="G20" s="0">
-        <v>3.7909901113730449</v>
+        <v>3.7517110838099264</v>
       </c>
       <c r="H20" s="0">
-        <v>21.209009888626955</v>
+        <v>21.248288916190074</v>
       </c>
       <c r="I20" s="0">
-        <v>-4.2909901113730449</v>
+        <v>-4.2517110838099264</v>
       </c>
       <c r="J20" s="0">
-        <v>4.2909901113730449</v>
+        <v>4.2517110838099264</v>
       </c>
       <c r="K20" s="0" t="b">
         <v>0</v>
@@ -1320,28 +1320,28 @@
         <v>69</v>
       </c>
       <c r="C21" s="0">
-        <v>344.29160000000002</v>
+        <v>349.81529999999998</v>
       </c>
       <c r="D21" s="0">
         <v>22.5</v>
       </c>
       <c r="E21" s="0">
-        <v>19.657141624086218</v>
+        <v>19.934470297937629</v>
       </c>
       <c r="F21" s="0">
-        <v>-2.8428583759137815</v>
+        <v>-2.5655297020623706</v>
       </c>
       <c r="G21" s="0">
-        <v>2.8428583759137815</v>
+        <v>2.5655297020623706</v>
       </c>
       <c r="H21" s="0">
-        <v>19.157141624086218</v>
+        <v>19.434470297937629</v>
       </c>
       <c r="I21" s="0">
-        <v>-3.3428583759137816</v>
+        <v>-3.0655297020623706</v>
       </c>
       <c r="J21" s="0">
-        <v>3.3428583759137816</v>
+        <v>3.0655297020623706</v>
       </c>
       <c r="K21" s="0" t="b">
         <v>0</v>
@@ -1364,28 +1364,28 @@
         <v>69</v>
       </c>
       <c r="C22" s="0">
-        <v>613.17560000000003</v>
+        <v>617.12260000000003</v>
       </c>
       <c r="D22" s="0">
         <v>21.5</v>
       </c>
       <c r="E22" s="0">
-        <v>20.033736719467889</v>
+        <v>19.981147539537254</v>
       </c>
       <c r="F22" s="0">
-        <v>-1.466263280532111</v>
+        <v>-1.518852460462746</v>
       </c>
       <c r="G22" s="0">
-        <v>1.466263280532111</v>
+        <v>1.518852460462746</v>
       </c>
       <c r="H22" s="0">
-        <v>19.533736719467889</v>
+        <v>19.481147539537254</v>
       </c>
       <c r="I22" s="0">
-        <v>-1.966263280532111</v>
+        <v>-2.018852460462746</v>
       </c>
       <c r="J22" s="0">
-        <v>1.966263280532111</v>
+        <v>2.018852460462746</v>
       </c>
       <c r="K22" s="0" t="b">
         <v>0</v>
@@ -1408,28 +1408,28 @@
         <v>69</v>
       </c>
       <c r="C23" s="0">
-        <v>674.47910000000002</v>
+        <v>669.44370000000004</v>
       </c>
       <c r="D23" s="0">
         <v>20</v>
       </c>
       <c r="E23" s="0">
-        <v>21.474266173852705</v>
+        <v>20.934554855582732</v>
       </c>
       <c r="F23" s="0">
-        <v>1.4742661738527048</v>
+        <v>0.9345548555827321</v>
       </c>
       <c r="G23" s="0">
-        <v>1.4742661738527048</v>
+        <v>0.9345548555827321</v>
       </c>
       <c r="H23" s="0">
-        <v>20.974266173852705</v>
+        <v>20.434554855582732</v>
       </c>
       <c r="I23" s="0">
-        <v>0.97426617385270475</v>
+        <v>0.4345548555827321</v>
       </c>
       <c r="J23" s="0">
-        <v>0.97426617385270475</v>
+        <v>0.4345548555827321</v>
       </c>
       <c r="K23" s="0" t="b">
         <v>1</v>
@@ -1452,28 +1452,28 @@
         <v>69</v>
       </c>
       <c r="C24" s="0">
-        <v>577.67240000000004</v>
+        <v>584.04089999999997</v>
       </c>
       <c r="D24" s="0">
         <v>19.5</v>
       </c>
       <c r="E24" s="0">
-        <v>21.252511927314213</v>
+        <v>20.910847675490093</v>
       </c>
       <c r="F24" s="0">
-        <v>1.7525119273142131</v>
+        <v>1.4108476754900927</v>
       </c>
       <c r="G24" s="0">
-        <v>1.7525119273142131</v>
+        <v>1.4108476754900927</v>
       </c>
       <c r="H24" s="0">
-        <v>20.752511927314213</v>
+        <v>20.410847675490093</v>
       </c>
       <c r="I24" s="0">
-        <v>1.2525119273142131</v>
+        <v>0.91084767549009271</v>
       </c>
       <c r="J24" s="0">
-        <v>1.2525119273142131</v>
+        <v>0.91084767549009271</v>
       </c>
       <c r="K24" s="0" t="b">
         <v>1</v>
@@ -1496,28 +1496,28 @@
         <v>69</v>
       </c>
       <c r="C25" s="0">
-        <v>577.55370000000005</v>
+        <v>583.09950000000003</v>
       </c>
       <c r="D25" s="0">
         <v>18.5</v>
       </c>
       <c r="E25" s="0">
-        <v>20.215269827918604</v>
+        <v>20.220297193686093</v>
       </c>
       <c r="F25" s="0">
-        <v>1.7152698279186041</v>
+        <v>1.7202971936860934</v>
       </c>
       <c r="G25" s="0">
-        <v>1.7152698279186041</v>
+        <v>1.7202971936860934</v>
       </c>
       <c r="H25" s="0">
-        <v>19.715269827918604</v>
+        <v>19.720297193686093</v>
       </c>
       <c r="I25" s="0">
-        <v>1.2152698279186041</v>
+        <v>1.2202971936860934</v>
       </c>
       <c r="J25" s="0">
-        <v>1.2152698279186041</v>
+        <v>1.2202971936860934</v>
       </c>
       <c r="K25" s="0" t="b">
         <v>1</v>
@@ -1540,28 +1540,28 @@
         <v>69</v>
       </c>
       <c r="C26" s="0">
-        <v>688.17229999999995</v>
+        <v>694.29290000000003</v>
       </c>
       <c r="D26" s="0">
         <v>21.25</v>
       </c>
       <c r="E26" s="0">
-        <v>22.181257728060416</v>
+        <v>22.158783870513805</v>
       </c>
       <c r="F26" s="0">
-        <v>0.93125772806041596</v>
+        <v>0.90878387051380471</v>
       </c>
       <c r="G26" s="0">
-        <v>0.93125772806041596</v>
+        <v>0.90878387051380471</v>
       </c>
       <c r="H26" s="0">
-        <v>21.681257728060416</v>
+        <v>21.658783870513805</v>
       </c>
       <c r="I26" s="0">
-        <v>0.43125772806041596</v>
+        <v>0.40878387051380472</v>
       </c>
       <c r="J26" s="0">
-        <v>0.43125772806041596</v>
+        <v>0.40878387051380472</v>
       </c>
       <c r="K26" s="0" t="b">
         <v>1</v>
@@ -1584,28 +1584,28 @@
         <v>69</v>
       </c>
       <c r="C27" s="0">
-        <v>638.71429999999998</v>
+        <v>645.69730000000004</v>
       </c>
       <c r="D27" s="0">
         <v>19.25</v>
       </c>
       <c r="E27" s="0">
-        <v>20.426243975696519</v>
+        <v>20.349385418484164</v>
       </c>
       <c r="F27" s="0">
-        <v>1.1762439756965186</v>
+        <v>1.0993854184841645</v>
       </c>
       <c r="G27" s="0">
-        <v>1.1762439756965186</v>
+        <v>1.0993854184841645</v>
       </c>
       <c r="H27" s="0">
-        <v>19.926243975696519</v>
+        <v>19.849385418484164</v>
       </c>
       <c r="I27" s="0">
-        <v>0.67624397569651862</v>
+        <v>0.59938541848416449</v>
       </c>
       <c r="J27" s="0">
-        <v>0.67624397569651862</v>
+        <v>0.59938541848416449</v>
       </c>
       <c r="K27" s="0" t="b">
         <v>1</v>
@@ -1628,28 +1628,28 @@
         <v>69</v>
       </c>
       <c r="C28" s="0">
-        <v>676.74940000000004</v>
+        <v>704.87890000000004</v>
       </c>
       <c r="D28" s="0">
         <v>21.75</v>
       </c>
       <c r="E28" s="0">
-        <v>21.316849811130677</v>
+        <v>21.459033692598677</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.43315018886932322</v>
+        <v>-0.29096630740132312</v>
       </c>
       <c r="G28" s="0">
-        <v>0.43315018886932322</v>
+        <v>0.29096630740132312</v>
       </c>
       <c r="H28" s="0">
-        <v>20.816849811130677</v>
+        <v>20.959033692598677</v>
       </c>
       <c r="I28" s="0">
-        <v>-0.93315018886932322</v>
+        <v>-0.79096630740132312</v>
       </c>
       <c r="J28" s="0">
-        <v>0.93315018886932322</v>
+        <v>0.79096630740132312</v>
       </c>
       <c r="K28" s="0" t="b">
         <v>0</v>
@@ -1672,28 +1672,28 @@
         <v>69</v>
       </c>
       <c r="C29" s="0">
-        <v>354.31049999999999</v>
+        <v>353.71350000000001</v>
       </c>
       <c r="D29" s="0">
         <v>20.75</v>
       </c>
       <c r="E29" s="0">
-        <v>20.930383311229228</v>
+        <v>20.80707788312321</v>
       </c>
       <c r="F29" s="0">
-        <v>0.18038331122922813</v>
+        <v>0.057077883123209716</v>
       </c>
       <c r="G29" s="0">
-        <v>0.18038331122922813</v>
+        <v>0.057077883123209716</v>
       </c>
       <c r="H29" s="0">
-        <v>20.430383311229228</v>
+        <v>20.30707788312321</v>
       </c>
       <c r="I29" s="0">
-        <v>-0.31961668877077187</v>
+        <v>-0.44292211687679028</v>
       </c>
       <c r="J29" s="0">
-        <v>0.31961668877077187</v>
+        <v>0.44292211687679028</v>
       </c>
       <c r="K29" s="0" t="b">
         <v>0</v>
@@ -1716,28 +1716,28 @@
         <v>69</v>
       </c>
       <c r="C30" s="0">
-        <v>683.81759999999997</v>
+        <v>688.96929999999998</v>
       </c>
       <c r="D30" s="0">
         <v>21.5</v>
       </c>
       <c r="E30" s="0">
-        <v>21.252508382944871</v>
+        <v>21.605310008619753</v>
       </c>
       <c r="F30" s="0">
-        <v>-0.2474916170551289</v>
+        <v>0.10531000861975315</v>
       </c>
       <c r="G30" s="0">
-        <v>0.2474916170551289</v>
+        <v>0.10531000861975315</v>
       </c>
       <c r="H30" s="0">
-        <v>20.752508382944871</v>
+        <v>21.105310008619753</v>
       </c>
       <c r="I30" s="0">
-        <v>-0.7474916170551289</v>
+        <v>-0.39468999138024685</v>
       </c>
       <c r="J30" s="0">
-        <v>0.7474916170551289</v>
+        <v>0.39468999138024685</v>
       </c>
       <c r="K30" s="0" t="b">
         <v>0</v>
@@ -1760,28 +1760,28 @@
         <v>69</v>
       </c>
       <c r="C31" s="0">
-        <v>1353.5838000000001</v>
+        <v>1374.7736</v>
       </c>
       <c r="D31" s="0">
         <v>19.5</v>
       </c>
       <c r="E31" s="0">
-        <v>21.252486019156695</v>
+        <v>21.540673203631165</v>
       </c>
       <c r="F31" s="0">
-        <v>1.7524860191566951</v>
+        <v>2.0406732036311652</v>
       </c>
       <c r="G31" s="0">
-        <v>1.7524860191566951</v>
+        <v>2.0406732036311652</v>
       </c>
       <c r="H31" s="0">
-        <v>20.752486019156695</v>
+        <v>21.040673203631165</v>
       </c>
       <c r="I31" s="0">
-        <v>1.2524860191566951</v>
+        <v>1.5406732036311652</v>
       </c>
       <c r="J31" s="0">
-        <v>1.2524860191566951</v>
+        <v>1.5406732036311652</v>
       </c>
       <c r="K31" s="0" t="b">
         <v>1</v>
@@ -1804,28 +1804,28 @@
         <v>69</v>
       </c>
       <c r="C32" s="0">
-        <v>1324.2094</v>
+        <v>1328.4146000000001</v>
       </c>
       <c r="D32" s="0">
         <v>19.5</v>
       </c>
       <c r="E32" s="0">
-        <v>21.252486999970955</v>
+        <v>20.890900825226876</v>
       </c>
       <c r="F32" s="0">
-        <v>1.7524869999709551</v>
+        <v>1.3909008252268755</v>
       </c>
       <c r="G32" s="0">
-        <v>1.7524869999709551</v>
+        <v>1.3909008252268755</v>
       </c>
       <c r="H32" s="0">
-        <v>20.752486999970955</v>
+        <v>20.390900825226876</v>
       </c>
       <c r="I32" s="0">
-        <v>1.2524869999709551</v>
+        <v>0.89090082522687553</v>
       </c>
       <c r="J32" s="0">
-        <v>1.2524869999709551</v>
+        <v>0.89090082522687553</v>
       </c>
       <c r="K32" s="0" t="b">
         <v>1</v>
@@ -1848,31 +1848,31 @@
         <v>69</v>
       </c>
       <c r="C33" s="0">
-        <v>1370.5188000000001</v>
+        <v>1401.6427000000001</v>
       </c>
       <c r="D33" s="0">
         <v>21</v>
       </c>
       <c r="E33" s="0">
-        <v>21.077359555980671</v>
+        <v>21.538708079073523</v>
       </c>
       <c r="F33" s="0">
-        <v>0.077359555980670791</v>
+        <v>0.53870807907352258</v>
       </c>
       <c r="G33" s="0">
-        <v>0.077359555980670791</v>
+        <v>0.53870807907352258</v>
       </c>
       <c r="H33" s="0">
-        <v>20.577359555980671</v>
+        <v>21.038708079073523</v>
       </c>
       <c r="I33" s="0">
-        <v>-0.42264044401932921</v>
+        <v>0.038708079073522583</v>
       </c>
       <c r="J33" s="0">
-        <v>0.42264044401932921</v>
+        <v>0.038708079073522583</v>
       </c>
       <c r="K33" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="0">
         <v>1</v>
@@ -1892,28 +1892,28 @@
         <v>69</v>
       </c>
       <c r="C34" s="0">
-        <v>595.53899999999999</v>
+        <v>604.36569999999995</v>
       </c>
       <c r="D34" s="0">
         <v>20.25</v>
       </c>
       <c r="E34" s="0">
-        <v>19.980895216842527</v>
+        <v>19.94044075149877</v>
       </c>
       <c r="F34" s="0">
-        <v>-0.26910478315747355</v>
+        <v>-0.3095592485012304</v>
       </c>
       <c r="G34" s="0">
-        <v>0.26910478315747355</v>
+        <v>0.3095592485012304</v>
       </c>
       <c r="H34" s="0">
-        <v>19.480895216842527</v>
+        <v>19.44044075149877</v>
       </c>
       <c r="I34" s="0">
-        <v>-0.76910478315747355</v>
+        <v>-0.8095592485012304</v>
       </c>
       <c r="J34" s="0">
-        <v>0.76910478315747355</v>
+        <v>0.8095592485012304</v>
       </c>
       <c r="K34" s="0" t="b">
         <v>0</v>
@@ -1936,28 +1936,28 @@
         <v>69</v>
       </c>
       <c r="C35" s="0">
-        <v>620.18640000000005</v>
+        <v>621.61170000000004</v>
       </c>
       <c r="D35" s="0">
         <v>21.5</v>
       </c>
       <c r="E35" s="0">
-        <v>20.01732990580221</v>
+        <v>19.961539518561541</v>
       </c>
       <c r="F35" s="0">
-        <v>-1.4826700941977897</v>
+        <v>-1.5384604814384595</v>
       </c>
       <c r="G35" s="0">
-        <v>1.4826700941977897</v>
+        <v>1.5384604814384595</v>
       </c>
       <c r="H35" s="0">
-        <v>19.51732990580221</v>
+        <v>19.461539518561541</v>
       </c>
       <c r="I35" s="0">
-        <v>-1.9826700941977897</v>
+        <v>-2.0384604814384595</v>
       </c>
       <c r="J35" s="0">
-        <v>1.9826700941977897</v>
+        <v>2.0384604814384595</v>
       </c>
       <c r="K35" s="0" t="b">
         <v>0</v>
@@ -1980,28 +1980,28 @@
         <v>69</v>
       </c>
       <c r="C36" s="0">
-        <v>589.86860000000001</v>
+        <v>597.18910000000005</v>
       </c>
       <c r="D36" s="0">
         <v>19.5</v>
       </c>
       <c r="E36" s="0">
-        <v>20.076669425897578</v>
+        <v>20.058686435952748</v>
       </c>
       <c r="F36" s="0">
-        <v>0.57666942589757753</v>
+        <v>0.55868643595274747</v>
       </c>
       <c r="G36" s="0">
-        <v>0.57666942589757753</v>
+        <v>0.55868643595274747</v>
       </c>
       <c r="H36" s="0">
-        <v>19.576669425897578</v>
+        <v>19.558686435952748</v>
       </c>
       <c r="I36" s="0">
-        <v>0.076669425897577526</v>
+        <v>0.058686435952747473</v>
       </c>
       <c r="J36" s="0">
-        <v>0.076669425897577526</v>
+        <v>0.058686435952747473</v>
       </c>
       <c r="K36" s="0" t="b">
         <v>1</v>
@@ -2024,28 +2024,28 @@
         <v>69</v>
       </c>
       <c r="C37" s="0">
-        <v>724.63610000000006</v>
+        <v>738.8483</v>
       </c>
       <c r="D37" s="0">
         <v>25</v>
       </c>
       <c r="E37" s="0">
-        <v>23.594223159260079</v>
+        <v>23.727991021643032</v>
       </c>
       <c r="F37" s="0">
-        <v>-1.4057768407399216</v>
+        <v>-1.2720089783569684</v>
       </c>
       <c r="G37" s="0">
-        <v>1.4057768407399216</v>
+        <v>1.2720089783569684</v>
       </c>
       <c r="H37" s="0">
-        <v>23.094223159260079</v>
+        <v>23.227991021643032</v>
       </c>
       <c r="I37" s="0">
-        <v>-1.9057768407399216</v>
+        <v>-1.7720089783569684</v>
       </c>
       <c r="J37" s="0">
-        <v>1.9057768407399216</v>
+        <v>1.7720089783569684</v>
       </c>
       <c r="K37" s="0" t="b">
         <v>0</v>
@@ -2068,28 +2068,28 @@
         <v>69</v>
       </c>
       <c r="C38" s="0">
-        <v>598.2287</v>
+        <v>595.78989999999999</v>
       </c>
       <c r="D38" s="0">
         <v>19</v>
       </c>
       <c r="E38" s="0">
-        <v>20.867302672147726</v>
+        <v>20.773333448706271</v>
       </c>
       <c r="F38" s="0">
-        <v>1.8673026721477264</v>
+        <v>1.7733334487062713</v>
       </c>
       <c r="G38" s="0">
-        <v>1.8673026721477264</v>
+        <v>1.7733334487062713</v>
       </c>
       <c r="H38" s="0">
-        <v>20.367302672147726</v>
+        <v>20.273333448706271</v>
       </c>
       <c r="I38" s="0">
-        <v>1.3673026721477264</v>
+        <v>1.2733334487062713</v>
       </c>
       <c r="J38" s="0">
-        <v>1.3673026721477264</v>
+        <v>1.2733334487062713</v>
       </c>
       <c r="K38" s="0" t="b">
         <v>1</v>
@@ -2112,28 +2112,28 @@
         <v>69</v>
       </c>
       <c r="C39" s="0">
-        <v>681.9153</v>
+        <v>698.92719999999997</v>
       </c>
       <c r="D39" s="0">
         <v>19</v>
       </c>
       <c r="E39" s="0">
-        <v>21.922122058283065</v>
+        <v>22.369257022863131</v>
       </c>
       <c r="F39" s="0">
-        <v>2.9221220582830654</v>
+        <v>3.3692570228631311</v>
       </c>
       <c r="G39" s="0">
-        <v>2.9221220582830654</v>
+        <v>3.3692570228631311</v>
       </c>
       <c r="H39" s="0">
-        <v>21.422122058283065</v>
+        <v>21.869257022863131</v>
       </c>
       <c r="I39" s="0">
-        <v>2.4221220582830654</v>
+        <v>2.8692570228631311</v>
       </c>
       <c r="J39" s="0">
-        <v>2.4221220582830654</v>
+        <v>2.8692570228631311</v>
       </c>
       <c r="K39" s="0" t="b">
         <v>1</v>
@@ -2156,28 +2156,28 @@
         <v>69</v>
       </c>
       <c r="C40" s="0">
-        <v>1171.8478</v>
+        <v>1170.2615000000001</v>
       </c>
       <c r="D40" s="0">
         <v>21</v>
       </c>
       <c r="E40" s="0">
-        <v>21.252492087335092</v>
+        <v>19.480663031910598</v>
       </c>
       <c r="F40" s="0">
-        <v>0.25249208733509221</v>
+        <v>-1.5193369680894016</v>
       </c>
       <c r="G40" s="0">
-        <v>0.25249208733509221</v>
+        <v>1.5193369680894016</v>
       </c>
       <c r="H40" s="0">
-        <v>20.752492087335092</v>
+        <v>18.980663031910598</v>
       </c>
       <c r="I40" s="0">
-        <v>-0.24750791266490779</v>
+        <v>-2.0193369680894016</v>
       </c>
       <c r="J40" s="0">
-        <v>0.24750791266490779</v>
+        <v>2.0193369680894016</v>
       </c>
       <c r="K40" s="0" t="b">
         <v>0</v>
@@ -2200,28 +2200,28 @@
         <v>69</v>
       </c>
       <c r="C41" s="0">
-        <v>665.75360000000001</v>
+        <v>672.51900000000001</v>
       </c>
       <c r="D41" s="0">
         <v>20.5</v>
       </c>
       <c r="E41" s="0">
-        <v>21.252508986128436</v>
+        <v>21.492563040114238</v>
       </c>
       <c r="F41" s="0">
-        <v>0.75250898612843642</v>
+        <v>0.99256304011423779</v>
       </c>
       <c r="G41" s="0">
-        <v>0.75250898612843642</v>
+        <v>0.99256304011423779</v>
       </c>
       <c r="H41" s="0">
-        <v>20.752508986128436</v>
+        <v>20.992563040114238</v>
       </c>
       <c r="I41" s="0">
-        <v>0.25250898612843642</v>
+        <v>0.49256304011423779</v>
       </c>
       <c r="J41" s="0">
-        <v>0.25250898612843642</v>
+        <v>0.49256304011423779</v>
       </c>
       <c r="K41" s="0" t="b">
         <v>1</v>
@@ -2244,28 +2244,28 @@
         <v>69</v>
       </c>
       <c r="C42" s="0">
-        <v>343.99220000000003</v>
+        <v>344.02600000000001</v>
       </c>
       <c r="D42" s="0">
         <v>19.25</v>
       </c>
       <c r="E42" s="0">
-        <v>20.540786038830948</v>
+        <v>20.397172583841432</v>
       </c>
       <c r="F42" s="0">
-        <v>1.290786038830948</v>
+        <v>1.1471725838414315</v>
       </c>
       <c r="G42" s="0">
-        <v>1.290786038830948</v>
+        <v>1.1471725838414315</v>
       </c>
       <c r="H42" s="0">
-        <v>20.040786038830948</v>
+        <v>19.897172583841432</v>
       </c>
       <c r="I42" s="0">
-        <v>0.790786038830948</v>
+        <v>0.6471725838414315</v>
       </c>
       <c r="J42" s="0">
-        <v>0.790786038830948</v>
+        <v>0.6471725838414315</v>
       </c>
       <c r="K42" s="0" t="b">
         <v>1</v>
@@ -2288,28 +2288,28 @@
         <v>69</v>
       </c>
       <c r="C43" s="0">
-        <v>584.32039999999995</v>
+        <v>585.99260000000004</v>
       </c>
       <c r="D43" s="0">
         <v>20</v>
       </c>
       <c r="E43" s="0">
-        <v>20.788931289625833</v>
+        <v>20.715746595984413</v>
       </c>
       <c r="F43" s="0">
-        <v>0.78893128962583248</v>
+        <v>0.71574659598441315</v>
       </c>
       <c r="G43" s="0">
-        <v>0.78893128962583248</v>
+        <v>0.71574659598441315</v>
       </c>
       <c r="H43" s="0">
-        <v>20.288931289625833</v>
+        <v>20.215746595984413</v>
       </c>
       <c r="I43" s="0">
-        <v>0.28893128962583248</v>
+        <v>0.21574659598441315</v>
       </c>
       <c r="J43" s="0">
-        <v>0.28893128962583248</v>
+        <v>0.21574659598441315</v>
       </c>
       <c r="K43" s="0" t="b">
         <v>1</v>
@@ -2332,28 +2332,28 @@
         <v>69</v>
       </c>
       <c r="C44" s="0">
-        <v>660.15719999999999</v>
+        <v>661.50829999999996</v>
       </c>
       <c r="D44" s="0">
         <v>20</v>
       </c>
       <c r="E44" s="0">
-        <v>21.107203139576551</v>
+        <v>20.752501715589901</v>
       </c>
       <c r="F44" s="0">
-        <v>1.1072031395765514</v>
+        <v>0.75250171558990076</v>
       </c>
       <c r="G44" s="0">
-        <v>1.1072031395765514</v>
+        <v>0.75250171558990076</v>
       </c>
       <c r="H44" s="0">
-        <v>20.607203139576551</v>
+        <v>20.252501715589901</v>
       </c>
       <c r="I44" s="0">
-        <v>0.60720313957655137</v>
+        <v>0.25250171558990076</v>
       </c>
       <c r="J44" s="0">
-        <v>0.60720313957655137</v>
+        <v>0.25250171558990076</v>
       </c>
       <c r="K44" s="0" t="b">
         <v>1</v>
@@ -2376,28 +2376,28 @@
         <v>69</v>
       </c>
       <c r="C45" s="0">
-        <v>581.95590000000004</v>
+        <v>579.78219999999999</v>
       </c>
       <c r="D45" s="0">
         <v>20</v>
       </c>
       <c r="E45" s="0">
-        <v>20.159379703251702</v>
+        <v>20.267661502926195</v>
       </c>
       <c r="F45" s="0">
-        <v>0.1593797032517017</v>
+        <v>0.26766150292619528</v>
       </c>
       <c r="G45" s="0">
-        <v>0.1593797032517017</v>
+        <v>0.26766150292619528</v>
       </c>
       <c r="H45" s="0">
-        <v>19.659379703251702</v>
+        <v>19.767661502926195</v>
       </c>
       <c r="I45" s="0">
-        <v>-0.3406202967482983</v>
+        <v>-0.23233849707380472</v>
       </c>
       <c r="J45" s="0">
-        <v>0.3406202967482983</v>
+        <v>0.23233849707380472</v>
       </c>
       <c r="K45" s="0" t="b">
         <v>0</v>
@@ -2420,28 +2420,28 @@
         <v>69</v>
       </c>
       <c r="C46" s="0">
-        <v>1432.1427000000001</v>
+        <v>1450.9502</v>
       </c>
       <c r="D46" s="0">
         <v>22</v>
       </c>
       <c r="E46" s="0">
-        <v>22.130784189623878</v>
+        <v>21.832425869122467</v>
       </c>
       <c r="F46" s="0">
-        <v>0.13078418962387772</v>
+        <v>-0.16757413087753292</v>
       </c>
       <c r="G46" s="0">
-        <v>0.13078418962387772</v>
+        <v>0.16757413087753292</v>
       </c>
       <c r="H46" s="0">
-        <v>21.630784189623878</v>
+        <v>21.332425869122467</v>
       </c>
       <c r="I46" s="0">
-        <v>-0.36921581037612228</v>
+        <v>-0.66757413087753292</v>
       </c>
       <c r="J46" s="0">
-        <v>0.36921581037612228</v>
+        <v>0.66757413087753292</v>
       </c>
       <c r="K46" s="0" t="b">
         <v>0</v>
@@ -2464,28 +2464,28 @@
         <v>69</v>
       </c>
       <c r="C47" s="0">
-        <v>1393.6792</v>
+        <v>1401.4597000000001</v>
       </c>
       <c r="D47" s="0">
         <v>22</v>
       </c>
       <c r="E47" s="0">
-        <v>21.542736545268163</v>
+        <v>21.354172658447649</v>
       </c>
       <c r="F47" s="0">
-        <v>-0.45726345473183727</v>
+        <v>-0.64582734155235144</v>
       </c>
       <c r="G47" s="0">
-        <v>0.45726345473183727</v>
+        <v>0.64582734155235144</v>
       </c>
       <c r="H47" s="0">
-        <v>21.042736545268163</v>
+        <v>20.854172658447649</v>
       </c>
       <c r="I47" s="0">
-        <v>-0.95726345473183727</v>
+        <v>-1.1458273415523515</v>
       </c>
       <c r="J47" s="0">
-        <v>0.95726345473183727</v>
+        <v>1.1458273415523515</v>
       </c>
       <c r="K47" s="0" t="b">
         <v>0</v>
@@ -2508,28 +2508,28 @@
         <v>69</v>
       </c>
       <c r="C48" s="0">
-        <v>1418.9514999999999</v>
+        <v>1394.8155999999999</v>
       </c>
       <c r="D48" s="0">
         <v>23</v>
       </c>
       <c r="E48" s="0">
-        <v>22.153569737180611</v>
+        <v>21.399532823532883</v>
       </c>
       <c r="F48" s="0">
-        <v>-0.84643026281938916</v>
+        <v>-1.6004671764671166</v>
       </c>
       <c r="G48" s="0">
-        <v>0.84643026281938916</v>
+        <v>1.6004671764671166</v>
       </c>
       <c r="H48" s="0">
-        <v>21.653569737180611</v>
+        <v>20.899532823532883</v>
       </c>
       <c r="I48" s="0">
-        <v>-1.3464302628193892</v>
+        <v>-2.1004671764671166</v>
       </c>
       <c r="J48" s="0">
-        <v>1.3464302628193892</v>
+        <v>2.1004671764671166</v>
       </c>
       <c r="K48" s="0" t="b">
         <v>0</v>
@@ -2552,28 +2552,28 @@
         <v>69</v>
       </c>
       <c r="C49" s="0">
-        <v>1319.8444999999999</v>
+        <v>1329.1301000000001</v>
       </c>
       <c r="D49" s="0">
         <v>21.75</v>
       </c>
       <c r="E49" s="0">
-        <v>20.140024852533649</v>
+        <v>20.146676775870095</v>
       </c>
       <c r="F49" s="0">
-        <v>-1.6099751474663506</v>
+        <v>-1.6033232241299054</v>
       </c>
       <c r="G49" s="0">
-        <v>1.6099751474663506</v>
+        <v>1.6033232241299054</v>
       </c>
       <c r="H49" s="0">
-        <v>19.640024852533649</v>
+        <v>19.646676775870095</v>
       </c>
       <c r="I49" s="0">
-        <v>-2.1099751474663506</v>
+        <v>-2.1033232241299054</v>
       </c>
       <c r="J49" s="0">
-        <v>2.1099751474663506</v>
+        <v>2.1033232241299054</v>
       </c>
       <c r="K49" s="0" t="b">
         <v>0</v>
@@ -2596,28 +2596,28 @@
         <v>69</v>
       </c>
       <c r="C50" s="0">
-        <v>1370.9471000000001</v>
+        <v>1378.3186000000001</v>
       </c>
       <c r="D50" s="0">
         <v>21.5</v>
       </c>
       <c r="E50" s="0">
-        <v>21.377543045902428</v>
+        <v>21.301836829413126</v>
       </c>
       <c r="F50" s="0">
-        <v>-0.12245695409757218</v>
+        <v>-0.1981631705868736</v>
       </c>
       <c r="G50" s="0">
-        <v>0.12245695409757218</v>
+        <v>0.1981631705868736</v>
       </c>
       <c r="H50" s="0">
-        <v>20.877543045902428</v>
+        <v>20.801836829413126</v>
       </c>
       <c r="I50" s="0">
-        <v>-0.62245695409757218</v>
+        <v>-0.6981631705868736</v>
       </c>
       <c r="J50" s="0">
-        <v>0.62245695409757218</v>
+        <v>0.6981631705868736</v>
       </c>
       <c r="K50" s="0" t="b">
         <v>0</v>
@@ -2640,31 +2640,31 @@
         <v>69</v>
       </c>
       <c r="C51" s="0">
-        <v>1230.9086</v>
+        <v>1221.2897</v>
       </c>
       <c r="D51" s="0">
         <v>19.199999999999999</v>
       </c>
       <c r="E51" s="0">
-        <v>21.252490115291074</v>
+        <v>19.692383898283719</v>
       </c>
       <c r="F51" s="0">
-        <v>2.0524901152910751</v>
+        <v>0.49238389828371965</v>
       </c>
       <c r="G51" s="0">
-        <v>2.0524901152910751</v>
+        <v>0.49238389828371965</v>
       </c>
       <c r="H51" s="0">
-        <v>20.752490115291074</v>
+        <v>19.192383898283719</v>
       </c>
       <c r="I51" s="0">
-        <v>1.5524901152910751</v>
+        <v>-0.0076161017162803546</v>
       </c>
       <c r="J51" s="0">
-        <v>1.5524901152910751</v>
+        <v>0.0076161017162803546</v>
       </c>
       <c r="K51" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" s="0">
         <v>2</v>
@@ -2684,28 +2684,28 @@
         <v>69</v>
       </c>
       <c r="C52" s="0">
-        <v>1142.3658</v>
+        <v>1153.4326000000001</v>
       </c>
       <c r="D52" s="0">
         <v>17.5</v>
       </c>
       <c r="E52" s="0">
-        <v>20.064405478728844</v>
+        <v>19.726344198429427</v>
       </c>
       <c r="F52" s="0">
-        <v>2.5644054787288439</v>
+        <v>2.2263441984294268</v>
       </c>
       <c r="G52" s="0">
-        <v>2.5644054787288439</v>
+        <v>2.2263441984294268</v>
       </c>
       <c r="H52" s="0">
-        <v>19.564405478728844</v>
+        <v>19.226344198429427</v>
       </c>
       <c r="I52" s="0">
-        <v>2.0644054787288439</v>
+        <v>1.7263441984294268</v>
       </c>
       <c r="J52" s="0">
-        <v>2.0644054787288439</v>
+        <v>1.7263441984294268</v>
       </c>
       <c r="K52" s="0" t="b">
         <v>1</v>
@@ -2728,28 +2728,28 @@
         <v>69</v>
       </c>
       <c r="C53" s="0">
-        <v>1183.6578999999999</v>
+        <v>1196.1094000000001</v>
       </c>
       <c r="D53" s="0">
         <v>18.399999999999999</v>
       </c>
       <c r="E53" s="0">
-        <v>19.264514489172161</v>
+        <v>19.333133486736074</v>
       </c>
       <c r="F53" s="0">
-        <v>0.86451448917216212</v>
+        <v>0.93313348673607521</v>
       </c>
       <c r="G53" s="0">
-        <v>0.86451448917216212</v>
+        <v>0.93313348673607521</v>
       </c>
       <c r="H53" s="0">
-        <v>18.764514489172161</v>
+        <v>18.833133486736074</v>
       </c>
       <c r="I53" s="0">
-        <v>0.36451448917216211</v>
+        <v>0.43313348673607521</v>
       </c>
       <c r="J53" s="0">
-        <v>0.36451448917216211</v>
+        <v>0.43313348673607521</v>
       </c>
       <c r="K53" s="0" t="b">
         <v>1</v>
@@ -2772,28 +2772,28 @@
         <v>69</v>
       </c>
       <c r="C54" s="0">
-        <v>1127.7965999999999</v>
+        <v>1146.1387</v>
       </c>
       <c r="D54" s="0">
         <v>19</v>
       </c>
       <c r="E54" s="0">
-        <v>19.775358098921281</v>
+        <v>19.743575219456592</v>
       </c>
       <c r="F54" s="0">
-        <v>0.77535809892128071</v>
+        <v>0.74357521945659144</v>
       </c>
       <c r="G54" s="0">
-        <v>0.77535809892128071</v>
+        <v>0.74357521945659144</v>
       </c>
       <c r="H54" s="0">
-        <v>19.275358098921281</v>
+        <v>19.243575219456592</v>
       </c>
       <c r="I54" s="0">
-        <v>0.27535809892128071</v>
+        <v>0.24357521945659144</v>
       </c>
       <c r="J54" s="0">
-        <v>0.27535809892128071</v>
+        <v>0.24357521945659144</v>
       </c>
       <c r="K54" s="0" t="b">
         <v>1</v>
@@ -2816,28 +2816,28 @@
         <v>69</v>
       </c>
       <c r="C55" s="0">
-        <v>600.21460000000002</v>
+        <v>610.65390000000002</v>
       </c>
       <c r="D55" s="0">
         <v>19.5</v>
       </c>
       <c r="E55" s="0">
-        <v>20.878576532231744</v>
+        <v>20.862580971028347</v>
       </c>
       <c r="F55" s="0">
-        <v>1.3785765322317438</v>
+        <v>1.362580971028347</v>
       </c>
       <c r="G55" s="0">
-        <v>1.3785765322317438</v>
+        <v>1.362580971028347</v>
       </c>
       <c r="H55" s="0">
-        <v>20.378576532231744</v>
+        <v>20.362580971028347</v>
       </c>
       <c r="I55" s="0">
-        <v>0.87857653223174381</v>
+        <v>0.86258097102834697</v>
       </c>
       <c r="J55" s="0">
-        <v>0.87857653223174381</v>
+        <v>0.86258097102834697</v>
       </c>
       <c r="K55" s="0" t="b">
         <v>1</v>
@@ -2860,28 +2860,28 @@
         <v>69</v>
       </c>
       <c r="C56" s="0">
-        <v>684.51480000000004</v>
+        <v>701.03470000000004</v>
       </c>
       <c r="D56" s="0">
         <v>20.5</v>
       </c>
       <c r="E56" s="0">
-        <v>22.02881585016128</v>
+        <v>22.463587957121206</v>
       </c>
       <c r="F56" s="0">
-        <v>1.5288158501612799</v>
+        <v>1.9635879571212058</v>
       </c>
       <c r="G56" s="0">
-        <v>1.5288158501612799</v>
+        <v>1.9635879571212058</v>
       </c>
       <c r="H56" s="0">
-        <v>21.52881585016128</v>
+        <v>21.963587957121206</v>
       </c>
       <c r="I56" s="0">
-        <v>1.0288158501612799</v>
+        <v>1.4635879571212058</v>
       </c>
       <c r="J56" s="0">
-        <v>1.0288158501612799</v>
+        <v>1.4635879571212058</v>
       </c>
       <c r="K56" s="0" t="b">
         <v>1</v>
@@ -2904,28 +2904,28 @@
         <v>69</v>
       </c>
       <c r="C57" s="0">
-        <v>632.78740000000005</v>
+        <v>647.98350000000005</v>
       </c>
       <c r="D57" s="0">
         <v>21</v>
       </c>
       <c r="E57" s="0">
-        <v>20.133522418289577</v>
+        <v>20.173159301290991</v>
       </c>
       <c r="F57" s="0">
-        <v>-0.86647758171042355</v>
+        <v>-0.82684069870900956</v>
       </c>
       <c r="G57" s="0">
-        <v>0.86647758171042355</v>
+        <v>0.82684069870900956</v>
       </c>
       <c r="H57" s="0">
-        <v>19.633522418289577</v>
+        <v>19.673159301290991</v>
       </c>
       <c r="I57" s="0">
-        <v>-1.3664775817104236</v>
+        <v>-1.3268406987090096</v>
       </c>
       <c r="J57" s="0">
-        <v>1.3664775817104236</v>
+        <v>1.3268406987090096</v>
       </c>
       <c r="K57" s="0" t="b">
         <v>0</v>
@@ -2948,28 +2948,28 @@
         <v>69</v>
       </c>
       <c r="C58" s="0">
-        <v>1105.7334000000001</v>
+        <v>1095.0534</v>
       </c>
       <c r="D58" s="0">
         <v>23.5</v>
       </c>
       <c r="E58" s="0">
-        <v>18.549066402601749</v>
+        <v>18.22877460407436</v>
       </c>
       <c r="F58" s="0">
-        <v>-4.9509335973982509</v>
+        <v>-5.2712253959256401</v>
       </c>
       <c r="G58" s="0">
-        <v>4.9509335973982509</v>
+        <v>5.2712253959256401</v>
       </c>
       <c r="H58" s="0">
-        <v>18.049066402601749</v>
+        <v>17.72877460407436</v>
       </c>
       <c r="I58" s="0">
-        <v>-5.4509335973982509</v>
+        <v>-5.7712253959256401</v>
       </c>
       <c r="J58" s="0">
-        <v>5.4509335973982509</v>
+        <v>5.7712253959256401</v>
       </c>
       <c r="K58" s="0" t="b">
         <v>0</v>
@@ -2992,28 +2992,28 @@
         <v>69</v>
       </c>
       <c r="C59" s="0">
-        <v>665.27829999999995</v>
+        <v>672.01580000000001</v>
       </c>
       <c r="D59" s="0">
         <v>20.5</v>
       </c>
       <c r="E59" s="0">
-        <v>21.252509001999424</v>
+        <v>21.48911237960365</v>
       </c>
       <c r="F59" s="0">
-        <v>0.7525090019994245</v>
+        <v>0.98911237960365028</v>
       </c>
       <c r="G59" s="0">
-        <v>0.7525090019994245</v>
+        <v>0.98911237960365028</v>
       </c>
       <c r="H59" s="0">
-        <v>20.752509001999424</v>
+        <v>20.98911237960365</v>
       </c>
       <c r="I59" s="0">
-        <v>0.2525090019994245</v>
+        <v>0.48911237960365028</v>
       </c>
       <c r="J59" s="0">
-        <v>0.2525090019994245</v>
+        <v>0.48911237960365028</v>
       </c>
       <c r="K59" s="0" t="b">
         <v>1</v>
@@ -3036,28 +3036,28 @@
         <v>69</v>
       </c>
       <c r="C60" s="0">
-        <v>655.14710000000002</v>
+        <v>697.428</v>
       </c>
       <c r="D60" s="0">
         <v>21.5</v>
       </c>
       <c r="E60" s="0">
-        <v>21.194183384703763</v>
+        <v>21.411640009736829</v>
       </c>
       <c r="F60" s="0">
-        <v>-0.30581661529623716</v>
+        <v>-0.08835999026317154</v>
       </c>
       <c r="G60" s="0">
-        <v>0.30581661529623716</v>
+        <v>0.08835999026317154</v>
       </c>
       <c r="H60" s="0">
-        <v>20.694183384703763</v>
+        <v>20.911640009736829</v>
       </c>
       <c r="I60" s="0">
-        <v>-0.80581661529623716</v>
+        <v>-0.58835999026317154</v>
       </c>
       <c r="J60" s="0">
-        <v>0.80581661529623716</v>
+        <v>0.58835999026317154</v>
       </c>
       <c r="K60" s="0" t="b">
         <v>0</v>
@@ -3080,31 +3080,31 @@
         <v>69</v>
       </c>
       <c r="C61" s="0">
-        <v>642.19590000000005</v>
+        <v>648.5258</v>
       </c>
       <c r="D61" s="0">
         <v>20</v>
       </c>
       <c r="E61" s="0">
-        <v>20.503556909540404</v>
+        <v>20.405895297694641</v>
       </c>
       <c r="F61" s="0">
-        <v>0.50355690954040355</v>
+        <v>0.4058952976946415</v>
       </c>
       <c r="G61" s="0">
-        <v>0.50355690954040355</v>
+        <v>0.4058952976946415</v>
       </c>
       <c r="H61" s="0">
-        <v>20.003556909540404</v>
+        <v>19.905895297694641</v>
       </c>
       <c r="I61" s="0">
-        <v>0.0035569095404035522</v>
+        <v>-0.094104702305358501</v>
       </c>
       <c r="J61" s="0">
-        <v>0.0035569095404035522</v>
+        <v>0.094104702305358501</v>
       </c>
       <c r="K61" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="0">
         <v>4</v>
@@ -3124,28 +3124,28 @@
         <v>69</v>
       </c>
       <c r="C62" s="0">
-        <v>671.02829999999995</v>
+        <v>690.99220000000003</v>
       </c>
       <c r="D62" s="0">
         <v>23</v>
       </c>
       <c r="E62" s="0">
-        <v>21.35028856193777</v>
+        <v>21.669425536349163</v>
       </c>
       <c r="F62" s="0">
-        <v>-1.64971143806223</v>
+        <v>-1.3305744636508372</v>
       </c>
       <c r="G62" s="0">
-        <v>1.64971143806223</v>
+        <v>1.3305744636508372</v>
       </c>
       <c r="H62" s="0">
-        <v>20.85028856193777</v>
+        <v>21.169425536349163</v>
       </c>
       <c r="I62" s="0">
-        <v>-2.14971143806223</v>
+        <v>-1.8305744636508372</v>
       </c>
       <c r="J62" s="0">
-        <v>2.14971143806223</v>
+        <v>1.8305744636508372</v>
       </c>
       <c r="K62" s="0" t="b">
         <v>0</v>
@@ -3168,28 +3168,28 @@
         <v>69</v>
       </c>
       <c r="C63" s="0">
-        <v>658.74609999999996</v>
+        <v>674.3954</v>
       </c>
       <c r="D63" s="0">
         <v>21.5</v>
       </c>
       <c r="E63" s="0">
-        <v>21.060348876394151</v>
+        <v>21.262633915910033</v>
       </c>
       <c r="F63" s="0">
-        <v>-0.43965112360584868</v>
+        <v>-0.23736608408996673</v>
       </c>
       <c r="G63" s="0">
-        <v>0.43965112360584868</v>
+        <v>0.23736608408996673</v>
       </c>
       <c r="H63" s="0">
-        <v>20.560348876394151</v>
+        <v>20.762633915910033</v>
       </c>
       <c r="I63" s="0">
-        <v>-0.93965112360584868</v>
+        <v>-0.73736608408996673</v>
       </c>
       <c r="J63" s="0">
-        <v>0.93965112360584868</v>
+        <v>0.73736608408996673</v>
       </c>
       <c r="K63" s="0" t="b">
         <v>0</v>
@@ -3212,28 +3212,28 @@
         <v>69</v>
       </c>
       <c r="C64" s="0">
-        <v>418.81540000000001</v>
+        <v>427.42320000000001</v>
       </c>
       <c r="D64" s="0">
         <v>22.5</v>
       </c>
       <c r="E64" s="0">
-        <v>19.987939243069324</v>
+        <v>19.947571765597996</v>
       </c>
       <c r="F64" s="0">
-        <v>-2.5120607569306763</v>
+        <v>-2.5524282344020044</v>
       </c>
       <c r="G64" s="0">
-        <v>2.5120607569306763</v>
+        <v>2.5524282344020044</v>
       </c>
       <c r="H64" s="0">
-        <v>19.487939243069324</v>
+        <v>19.447571765597996</v>
       </c>
       <c r="I64" s="0">
-        <v>-3.0120607569306763</v>
+        <v>-3.0524282344020044</v>
       </c>
       <c r="J64" s="0">
-        <v>3.0120607569306763</v>
+        <v>3.0524282344020044</v>
       </c>
       <c r="K64" s="0" t="b">
         <v>0</v>
@@ -3256,28 +3256,28 @@
         <v>69</v>
       </c>
       <c r="C65" s="0">
-        <v>593.42259999999999</v>
+        <v>597.84789999999998</v>
       </c>
       <c r="D65" s="0">
         <v>19.25</v>
       </c>
       <c r="E65" s="0">
-        <v>21.252511401384233</v>
+        <v>20.996477545935281</v>
       </c>
       <c r="F65" s="0">
-        <v>2.0025114013842327</v>
+        <v>1.7464775459352815</v>
       </c>
       <c r="G65" s="0">
-        <v>2.0025114013842327</v>
+        <v>1.7464775459352815</v>
       </c>
       <c r="H65" s="0">
-        <v>20.752511401384233</v>
+        <v>20.496477545935281</v>
       </c>
       <c r="I65" s="0">
-        <v>1.5025114013842327</v>
+        <v>1.2464775459352815</v>
       </c>
       <c r="J65" s="0">
-        <v>1.5025114013842327</v>
+        <v>1.2464775459352815</v>
       </c>
       <c r="K65" s="0" t="b">
         <v>1</v>
@@ -3300,28 +3300,28 @@
         <v>69</v>
       </c>
       <c r="C66" s="0">
-        <v>709.44029999999998</v>
+        <v>710.17049999999995</v>
       </c>
       <c r="D66" s="0">
         <v>23.5</v>
       </c>
       <c r="E66" s="0">
-        <v>22.733834476203203</v>
+        <v>22.151109395977482</v>
       </c>
       <c r="F66" s="0">
-        <v>-0.76616552379679703</v>
+        <v>-1.3488906040225181</v>
       </c>
       <c r="G66" s="0">
-        <v>0.76616552379679703</v>
+        <v>1.3488906040225181</v>
       </c>
       <c r="H66" s="0">
-        <v>22.233834476203203</v>
+        <v>21.651109395977482</v>
       </c>
       <c r="I66" s="0">
-        <v>-1.266165523796797</v>
+        <v>-1.8488906040225181</v>
       </c>
       <c r="J66" s="0">
-        <v>1.266165523796797</v>
+        <v>1.8488906040225181</v>
       </c>
       <c r="K66" s="0" t="b">
         <v>0</v>
@@ -3344,28 +3344,28 @@
         <v>69</v>
       </c>
       <c r="C67" s="0">
-        <v>625.83199999999999</v>
+        <v>639.05380000000002</v>
       </c>
       <c r="D67" s="0">
         <v>21.5</v>
       </c>
       <c r="E67" s="0">
-        <v>20.058344546146906</v>
+        <v>20.061404842616319</v>
       </c>
       <c r="F67" s="0">
-        <v>-1.4416554538530946</v>
+        <v>-1.4385951573836806</v>
       </c>
       <c r="G67" s="0">
-        <v>1.4416554538530946</v>
+        <v>1.4385951573836806</v>
       </c>
       <c r="H67" s="0">
-        <v>19.558344546146906</v>
+        <v>19.561404842616319</v>
       </c>
       <c r="I67" s="0">
-        <v>-1.9416554538530946</v>
+        <v>-1.9385951573836806</v>
       </c>
       <c r="J67" s="0">
-        <v>1.9416554538530946</v>
+        <v>1.9385951573836806</v>
       </c>
       <c r="K67" s="0" t="b">
         <v>0</v>
@@ -3388,28 +3388,28 @@
         <v>69</v>
       </c>
       <c r="C68" s="0">
-        <v>889.9828</v>
+        <v>892.07839999999999</v>
       </c>
       <c r="D68" s="0">
         <v>19</v>
       </c>
       <c r="E68" s="0">
-        <v>28.709795531239678</v>
+        <v>31.224565937655505</v>
       </c>
       <c r="F68" s="0">
-        <v>9.7097955312396778</v>
+        <v>12.224565937655505</v>
       </c>
       <c r="G68" s="0">
-        <v>9.7097955312396778</v>
+        <v>12.224565937655505</v>
       </c>
       <c r="H68" s="0">
-        <v>28.209795531239678</v>
+        <v>30.724565937655505</v>
       </c>
       <c r="I68" s="0">
-        <v>9.2097955312396778</v>
+        <v>11.724565937655505</v>
       </c>
       <c r="J68" s="0">
-        <v>9.2097955312396778</v>
+        <v>11.724565937655505</v>
       </c>
       <c r="K68" s="0" t="b">
         <v>1</v>
@@ -3470,16 +3470,16 @@
         <v>85</v>
       </c>
       <c r="B2" s="0">
-        <v>1.3100000000000001</v>
+        <v>1.3480000000000001</v>
       </c>
       <c r="C2" s="0">
-        <v>1.8300000000000001</v>
+        <v>1.996</v>
       </c>
       <c r="D2" s="0">
-        <v>0.126</v>
+        <v>0.086999999999999994</v>
       </c>
       <c r="E2" s="0">
-        <v>0.109</v>
+        <v>0.047</v>
       </c>
       <c r="F2" s="0"/>
       <c r="G2" s="0"/>
@@ -3489,19 +3489,19 @@
         <v>86</v>
       </c>
       <c r="B3" s="0">
-        <v>0.048000000000000001</v>
+        <v>0.056000000000000001</v>
       </c>
       <c r="C3" s="0">
-        <v>0.13200000000000001</v>
+        <v>0.215</v>
       </c>
       <c r="D3" s="0">
-        <v>0.047</v>
+        <v>0.049000000000000002</v>
       </c>
       <c r="E3" s="0">
-        <v>0.063</v>
+        <v>0.084000000000000005</v>
       </c>
       <c r="F3" s="0">
-        <v>3.3999999999999999</v>
+        <v>4.2999999999999998</v>
       </c>
       <c r="G3" s="0">
         <v>1.6000000000000001</v>
@@ -3523,18 +3523,18 @@
         <v>88</v>
       </c>
       <c r="B5" s="0">
-        <v>1.325</v>
+        <v>1.3660000000000001</v>
       </c>
       <c r="C5" s="0"/>
       <c r="D5" s="0"/>
       <c r="E5" s="0">
-        <v>-0.39100000000000001</v>
+        <v>-0.45300000000000001</v>
       </c>
       <c r="F5" s="0">
-        <v>51.299999999999997</v>
+        <v>50.100000000000001</v>
       </c>
       <c r="G5" s="0">
-        <v>43.700000000000003</v>
+        <v>39.299999999999997</v>
       </c>
     </row>
     <row r="6">
@@ -3542,16 +3542,16 @@
         <v>89</v>
       </c>
       <c r="B6" s="0">
-        <v>1.4750000000000001</v>
+        <v>1.474</v>
       </c>
       <c r="C6" s="0">
         <v>1.8260000000000001</v>
       </c>
       <c r="D6" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="E6" s="0">
-        <v>0.0030000000000000001</v>
+        <v>0.002</v>
       </c>
       <c r="F6" s="0"/>
       <c r="G6" s="0"/>
@@ -3566,7 +3566,7 @@
       <c r="C7" s="0"/>
       <c r="D7" s="0"/>
       <c r="E7" s="0">
-        <v>-0.497</v>
+        <v>-0.498</v>
       </c>
       <c r="F7" s="0">
         <v>37.299999999999997</v>
@@ -3652,7 +3652,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="true"/>
-    <col min="2" max="2" width="7.7109375" customWidth="true"/>
+    <col min="2" max="2" width="6.7109375" customWidth="true"/>
     <col min="3" max="3" width="6.7109375" customWidth="true"/>
     <col min="4" max="4" width="6.7109375" customWidth="true"/>
     <col min="5" max="5" width="4.5703125" customWidth="true"/>
@@ -3680,13 +3680,13 @@
         <v>111</v>
       </c>
       <c r="B2" s="0">
-        <v>20.7623</v>
+        <v>20.751999999999999</v>
       </c>
       <c r="C2" s="0">
-        <v>0.59589999999999999</v>
+        <v>0.59840000000000004</v>
       </c>
       <c r="D2" s="0">
-        <v>34.838999999999999</v>
+        <v>34.679000000000002</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
@@ -3703,10 +3703,10 @@
         <v>0.00069999999999999999</v>
       </c>
       <c r="D3" s="0">
-        <v>0.40500000000000003</v>
+        <v>0.42199999999999999</v>
       </c>
       <c r="E3" s="0">
-        <v>0.68669999999999998</v>
+        <v>0.67459999999999998</v>
       </c>
     </row>
   </sheetData>
